--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23877647-ACDA-4477-A20B-D557DB321CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF63DCC-7B09-432B-BCD1-46276DF80967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11957" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11814" uniqueCount="1676">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -4963,9 +4963,6 @@
     <t>3,18,10</t>
   </si>
   <si>
-    <t xml:space="preserve">100 кп + 200 вольный стиль </t>
-  </si>
-  <si>
     <t>2,50,48</t>
   </si>
   <si>
@@ -5063,6 +5060,9 @@
   </si>
   <si>
     <t>Оларь Ю.С.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2 в.г.</t>
   </si>
 </sst>
 </file>
@@ -5128,7 +5128,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5153,12 +5153,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -5172,7 +5166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5278,28 +5272,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5307,6 +5283,21 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5612,7 +5603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1CF7402-0FC7-412B-8BC0-4F6910F9A220}">
-  <dimension ref="A1:W1020"/>
+  <dimension ref="A1:W987"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.9" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="0.140625" style="2" hidden="1" customWidth="1"/>
@@ -5635,26 +5626,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="41" t="s">
         <v>1407</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
       <c r="J1" s="18"/>
     </row>
     <row r="2" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="30"/>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="42" t="s">
         <v>860</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="30"/>
@@ -5683,14 +5674,14 @@
     </row>
     <row r="4" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="30"/>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="42" t="s">
         <v>859</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="30"/>
@@ -5781,7 +5772,7 @@
       <c r="C9" s="18">
         <v>1</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="37" t="s">
         <v>205</v>
       </c>
       <c r="E9" s="10">
@@ -5814,7 +5805,7 @@
       <c r="C10" s="18">
         <v>2</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="37" t="s">
         <v>797</v>
       </c>
       <c r="E10" s="10">
@@ -5847,7 +5838,7 @@
       <c r="C11" s="18">
         <v>3</v>
       </c>
-      <c r="D11" s="38" t="s">
+      <c r="D11" s="37" t="s">
         <v>210</v>
       </c>
       <c r="E11" s="10">
@@ -6056,7 +6047,7 @@
       <c r="C18" s="18">
         <v>1</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="37" t="s">
         <v>220</v>
       </c>
       <c r="E18" s="10">
@@ -6089,7 +6080,7 @@
       <c r="C19" s="18">
         <v>2</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="37" t="s">
         <v>754</v>
       </c>
       <c r="E19" s="18">
@@ -6122,7 +6113,7 @@
       <c r="C20" s="18">
         <v>3</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="37" t="s">
         <v>763</v>
       </c>
       <c r="E20" s="18">
@@ -6496,7 +6487,7 @@
       <c r="C32" s="18">
         <v>1</v>
       </c>
-      <c r="D32" s="38" t="s">
+      <c r="D32" s="37" t="s">
         <v>290</v>
       </c>
       <c r="E32" s="10">
@@ -6527,7 +6518,7 @@
       <c r="C33" s="18">
         <v>2</v>
       </c>
-      <c r="D33" s="38" t="s">
+      <c r="D33" s="37" t="s">
         <v>764</v>
       </c>
       <c r="E33" s="18">
@@ -6560,7 +6551,7 @@
       <c r="C34" s="18">
         <v>3</v>
       </c>
-      <c r="D34" s="38" t="s">
+      <c r="D34" s="37" t="s">
         <v>758</v>
       </c>
       <c r="E34" s="10">
@@ -7182,7 +7173,7 @@
       <c r="C55" s="5">
         <v>2</v>
       </c>
-      <c r="D55" s="38" t="s">
+      <c r="D55" s="37" t="s">
         <v>69</v>
       </c>
       <c r="E55" s="10">
@@ -7213,7 +7204,7 @@
       <c r="C56" s="4">
         <v>3</v>
       </c>
-      <c r="D56" s="38" t="s">
+      <c r="D56" s="37" t="s">
         <v>293</v>
       </c>
       <c r="E56" s="10">
@@ -7244,7 +7235,7 @@
       <c r="C57" s="5">
         <v>4</v>
       </c>
-      <c r="D57" s="38" t="s">
+      <c r="D57" s="37" t="s">
         <v>281</v>
       </c>
       <c r="E57" s="10">
@@ -8265,7 +8256,7 @@
       <c r="C95" s="18">
         <v>1</v>
       </c>
-      <c r="D95" s="38" t="s">
+      <c r="D95" s="37" t="s">
         <v>230</v>
       </c>
       <c r="E95" s="10">
@@ -8298,7 +8289,7 @@
       <c r="C96" s="10">
         <v>2</v>
       </c>
-      <c r="D96" s="38" t="s">
+      <c r="D96" s="37" t="s">
         <v>256</v>
       </c>
       <c r="E96" s="10">
@@ -8331,7 +8322,7 @@
       <c r="C97" s="18">
         <v>3</v>
       </c>
-      <c r="D97" s="38" t="s">
+      <c r="D97" s="37" t="s">
         <v>224</v>
       </c>
       <c r="E97" s="10">
@@ -8710,7 +8701,7 @@
     </row>
     <row r="109" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C109" s="4"/>
-      <c r="D109" s="38" t="s">
+      <c r="D109" s="37" t="s">
         <v>1007</v>
       </c>
       <c r="E109" s="4"/>
@@ -8726,7 +8717,7 @@
       <c r="C110" s="10">
         <v>1</v>
       </c>
-      <c r="D110" s="38" t="s">
+      <c r="D110" s="37" t="s">
         <v>732</v>
       </c>
       <c r="E110" s="18">
@@ -8759,7 +8750,7 @@
       <c r="C111" s="10">
         <v>2</v>
       </c>
-      <c r="D111" s="38" t="s">
+      <c r="D111" s="37" t="s">
         <v>260</v>
       </c>
       <c r="E111" s="18">
@@ -8792,7 +8783,7 @@
       <c r="C112" s="10">
         <v>3</v>
       </c>
-      <c r="D112" s="38" t="s">
+      <c r="D112" s="37" t="s">
         <v>234</v>
       </c>
       <c r="E112" s="10">
@@ -9014,7 +9005,7 @@
       <c r="K118" s="4" t="s">
         <v>791</v>
       </c>
-      <c r="L118" s="40"/>
+      <c r="L118" s="43"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -9047,7 +9038,7 @@
       <c r="K119" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="L119" s="40"/>
+      <c r="L119" s="43"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -9080,7 +9071,7 @@
       <c r="K120" s="4" t="s">
         <v>742</v>
       </c>
-      <c r="L120" s="40"/>
+      <c r="L120" s="43"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -9906,7 +9897,7 @@
       <c r="C147" s="10">
         <v>1</v>
       </c>
-      <c r="D147" s="38" t="s">
+      <c r="D147" s="37" t="s">
         <v>305</v>
       </c>
       <c r="E147" s="10">
@@ -9937,7 +9928,7 @@
       <c r="C148" s="10">
         <v>2</v>
       </c>
-      <c r="D148" s="38" t="s">
+      <c r="D148" s="37" t="s">
         <v>312</v>
       </c>
       <c r="E148" s="10">
@@ -9968,7 +9959,7 @@
       <c r="C149" s="10">
         <v>3</v>
       </c>
-      <c r="D149" s="38" t="s">
+      <c r="D149" s="37" t="s">
         <v>309</v>
       </c>
       <c r="E149" s="10">
@@ -11264,7 +11255,7 @@
       <c r="C193" s="10">
         <v>1</v>
       </c>
-      <c r="D193" s="38" t="s">
+      <c r="D193" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E193" s="10">
@@ -11295,7 +11286,7 @@
       <c r="C194" s="10">
         <v>2</v>
       </c>
-      <c r="D194" s="38" t="s">
+      <c r="D194" s="37" t="s">
         <v>303</v>
       </c>
       <c r="E194" s="10">
@@ -11326,7 +11317,7 @@
       <c r="C195" s="10">
         <v>3</v>
       </c>
-      <c r="D195" s="38" t="s">
+      <c r="D195" s="37" t="s">
         <v>361</v>
       </c>
       <c r="E195" s="18">
@@ -12421,7 +12412,7 @@
       <c r="C236" s="18">
         <v>1</v>
       </c>
-      <c r="D236" s="38" t="s">
+      <c r="D236" s="37" t="s">
         <v>200</v>
       </c>
       <c r="E236" s="10">
@@ -12453,7 +12444,7 @@
       <c r="C237" s="18">
         <v>2</v>
       </c>
-      <c r="D237" s="38" t="s">
+      <c r="D237" s="37" t="s">
         <v>797</v>
       </c>
       <c r="E237" s="10">
@@ -12485,7 +12476,7 @@
       <c r="C238" s="18">
         <v>3</v>
       </c>
-      <c r="D238" s="38" t="s">
+      <c r="D238" s="37" t="s">
         <v>215</v>
       </c>
       <c r="E238" s="18">
@@ -12639,7 +12630,7 @@
     </row>
     <row r="243" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="18"/>
-      <c r="D243" s="38" t="s">
+      <c r="D243" s="37" t="s">
         <v>1007</v>
       </c>
       <c r="E243" s="10"/>
@@ -12661,7 +12652,7 @@
       <c r="C244" s="18">
         <v>1</v>
       </c>
-      <c r="D244" s="38" t="s">
+      <c r="D244" s="37" t="s">
         <v>754</v>
       </c>
       <c r="E244" s="18">
@@ -12690,7 +12681,7 @@
       <c r="C245" s="18">
         <v>2</v>
       </c>
-      <c r="D245" s="38" t="s">
+      <c r="D245" s="37" t="s">
         <v>763</v>
       </c>
       <c r="E245" s="18">
@@ -12719,7 +12710,7 @@
       <c r="C246" s="18">
         <v>3</v>
       </c>
-      <c r="D246" s="38" t="s">
+      <c r="D246" s="37" t="s">
         <v>761</v>
       </c>
       <c r="E246" s="18">
@@ -12938,7 +12929,7 @@
     </row>
     <row r="253" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="18"/>
-      <c r="D253" s="38" t="s">
+      <c r="D253" s="37" t="s">
         <v>1058</v>
       </c>
       <c r="E253" s="18"/>
@@ -12956,7 +12947,7 @@
       <c r="C254" s="18">
         <v>1</v>
       </c>
-      <c r="D254" s="38" t="s">
+      <c r="D254" s="37" t="s">
         <v>758</v>
       </c>
       <c r="E254" s="10">
@@ -12988,7 +12979,7 @@
       <c r="C255" s="18">
         <v>2</v>
       </c>
-      <c r="D255" s="38" t="s">
+      <c r="D255" s="37" t="s">
         <v>764</v>
       </c>
       <c r="E255" s="18">
@@ -13020,7 +13011,7 @@
       <c r="C256" s="18">
         <v>3</v>
       </c>
-      <c r="D256" s="38" t="s">
+      <c r="D256" s="37" t="s">
         <v>290</v>
       </c>
       <c r="E256" s="10">
@@ -13345,7 +13336,7 @@
     </row>
     <row r="267" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C267" s="18"/>
-      <c r="D267" s="38" t="s">
+      <c r="D267" s="37" t="s">
         <v>1158</v>
       </c>
       <c r="E267" s="10"/>
@@ -13363,7 +13354,7 @@
       <c r="C268" s="18">
         <v>1</v>
       </c>
-      <c r="D268" s="38" t="s">
+      <c r="D268" s="37" t="s">
         <v>299</v>
       </c>
       <c r="E268" s="10">
@@ -13393,7 +13384,7 @@
       <c r="C269" s="18">
         <v>2</v>
       </c>
-      <c r="D269" s="38" t="s">
+      <c r="D269" s="37" t="s">
         <v>281</v>
       </c>
       <c r="E269" s="10">
@@ -13423,7 +13414,7 @@
       <c r="C270" s="18">
         <v>3</v>
       </c>
-      <c r="D270" s="38" t="s">
+      <c r="D270" s="37" t="s">
         <v>69</v>
       </c>
       <c r="E270" s="10">
@@ -13995,7 +13986,7 @@
       <c r="C292" s="18">
         <v>1</v>
       </c>
-      <c r="D292" s="38" t="s">
+      <c r="D292" s="37" t="s">
         <v>837</v>
       </c>
       <c r="E292" s="10">
@@ -14027,7 +14018,7 @@
       <c r="C293" s="18">
         <v>2</v>
       </c>
-      <c r="D293" s="38" t="s">
+      <c r="D293" s="37" t="s">
         <v>269</v>
       </c>
       <c r="E293" s="18">
@@ -14059,7 +14050,7 @@
       <c r="C294" s="18">
         <v>3</v>
       </c>
-      <c r="D294" s="38" t="s">
+      <c r="D294" s="37" t="s">
         <v>238</v>
       </c>
       <c r="E294" s="10">
@@ -14293,7 +14284,7 @@
     </row>
     <row r="302" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C302" s="18"/>
-      <c r="D302" s="38" t="s">
+      <c r="D302" s="37" t="s">
         <v>1007</v>
       </c>
       <c r="E302" s="10"/>
@@ -14311,7 +14302,7 @@
       <c r="C303" s="18">
         <v>1</v>
       </c>
-      <c r="D303" s="38" t="s">
+      <c r="D303" s="37" t="s">
         <v>732</v>
       </c>
       <c r="E303" s="18">
@@ -14343,7 +14334,7 @@
       <c r="C304" s="18">
         <v>2</v>
       </c>
-      <c r="D304" s="38" t="s">
+      <c r="D304" s="37" t="s">
         <v>234</v>
       </c>
       <c r="E304" s="10">
@@ -14375,7 +14366,7 @@
       <c r="C305" s="18">
         <v>3</v>
       </c>
-      <c r="D305" s="38" t="s">
+      <c r="D305" s="37" t="s">
         <v>443</v>
       </c>
       <c r="E305" s="18">
@@ -15107,7 +15098,7 @@
     </row>
     <row r="328" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C328" s="18"/>
-      <c r="D328" s="38" t="s">
+      <c r="D328" s="37" t="s">
         <v>1058</v>
       </c>
       <c r="E328" s="18"/>
@@ -15125,7 +15116,7 @@
       <c r="C329" s="18">
         <v>1</v>
       </c>
-      <c r="D329" s="38" t="s">
+      <c r="D329" s="37" t="s">
         <v>20</v>
       </c>
       <c r="E329" s="10">
@@ -15155,7 +15146,7 @@
       <c r="C330" s="18">
         <v>2</v>
       </c>
-      <c r="D330" s="38" t="s">
+      <c r="D330" s="37" t="s">
         <v>425</v>
       </c>
       <c r="E330" s="10">
@@ -15185,7 +15176,7 @@
       <c r="C331" s="18">
         <v>3</v>
       </c>
-      <c r="D331" s="38" t="s">
+      <c r="D331" s="37" t="s">
         <v>16</v>
       </c>
       <c r="E331" s="10">
@@ -16051,7 +16042,7 @@
       <c r="C362" s="18">
         <v>1</v>
       </c>
-      <c r="D362" s="38" t="s">
+      <c r="D362" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E362" s="10">
@@ -16081,7 +16072,7 @@
       <c r="C363" s="18">
         <v>2</v>
       </c>
-      <c r="D363" s="38" t="s">
+      <c r="D363" s="37" t="s">
         <v>303</v>
       </c>
       <c r="E363" s="10">
@@ -16111,7 +16102,7 @@
       <c r="C364" s="18">
         <v>3</v>
       </c>
-      <c r="D364" s="38" t="s">
+      <c r="D364" s="37" t="s">
         <v>361</v>
       </c>
       <c r="E364" s="18">
@@ -16914,7 +16905,7 @@
       <c r="C397" s="18">
         <v>1</v>
       </c>
-      <c r="D397" s="38" t="s">
+      <c r="D397" s="37" t="s">
         <v>754</v>
       </c>
       <c r="E397" s="18">
@@ -16946,7 +16937,7 @@
       <c r="C398" s="18">
         <v>2</v>
       </c>
-      <c r="D398" s="38" t="s">
+      <c r="D398" s="37" t="s">
         <v>763</v>
       </c>
       <c r="E398" s="18">
@@ -16978,7 +16969,7 @@
       <c r="C399" s="18">
         <v>3</v>
       </c>
-      <c r="D399" s="38" t="s">
+      <c r="D399" s="37" t="s">
         <v>274</v>
       </c>
       <c r="E399" s="10">
@@ -17352,7 +17343,7 @@
     </row>
     <row r="411" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C411" s="18"/>
-      <c r="D411" s="38" t="s">
+      <c r="D411" s="37" t="s">
         <v>1058</v>
       </c>
       <c r="E411" s="10"/>
@@ -17370,7 +17361,7 @@
       <c r="C412" s="18">
         <v>1</v>
       </c>
-      <c r="D412" s="38" t="s">
+      <c r="D412" s="37" t="s">
         <v>758</v>
       </c>
       <c r="E412" s="10">
@@ -17402,7 +17393,7 @@
       <c r="C413" s="18">
         <v>2</v>
       </c>
-      <c r="D413" s="38" t="s">
+      <c r="D413" s="37" t="s">
         <v>764</v>
       </c>
       <c r="E413" s="18">
@@ -17434,7 +17425,7 @@
       <c r="C414" s="18">
         <v>3</v>
       </c>
-      <c r="D414" s="38" t="s">
+      <c r="D414" s="37" t="s">
         <v>295</v>
       </c>
       <c r="E414" s="10">
@@ -17973,7 +17964,7 @@
       <c r="C433" s="5">
         <v>1</v>
       </c>
-      <c r="D433" s="38" t="s">
+      <c r="D433" s="37" t="s">
         <v>200</v>
       </c>
       <c r="E433" s="10">
@@ -18005,7 +17996,7 @@
       <c r="C434" s="5">
         <v>2</v>
       </c>
-      <c r="D434" s="38" t="s">
+      <c r="D434" s="37" t="s">
         <v>205</v>
       </c>
       <c r="E434" s="10">
@@ -18037,7 +18028,7 @@
       <c r="C435" s="5">
         <v>3</v>
       </c>
-      <c r="D435" s="38" t="s">
+      <c r="D435" s="37" t="s">
         <v>210</v>
       </c>
       <c r="E435" s="10">
@@ -18861,7 +18852,7 @@
       <c r="C467" s="18">
         <v>1</v>
       </c>
-      <c r="D467" s="38" t="s">
+      <c r="D467" s="37" t="s">
         <v>234</v>
       </c>
       <c r="E467" s="10">
@@ -18893,7 +18884,7 @@
       <c r="C468" s="18">
         <v>2</v>
       </c>
-      <c r="D468" s="38" t="s">
+      <c r="D468" s="37" t="s">
         <v>732</v>
       </c>
       <c r="E468" s="18">
@@ -18925,7 +18916,7 @@
       <c r="C469" s="18">
         <v>3</v>
       </c>
-      <c r="D469" s="38" t="s">
+      <c r="D469" s="37" t="s">
         <v>260</v>
       </c>
       <c r="E469" s="18">
@@ -19884,7 +19875,7 @@
       <c r="C501" s="18">
         <v>1</v>
       </c>
-      <c r="D501" s="38" t="s">
+      <c r="D501" s="37" t="s">
         <v>309</v>
       </c>
       <c r="E501" s="10">
@@ -19897,7 +19888,7 @@
       <c r="H501" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="I501" s="39" t="s">
+      <c r="I501" s="38" t="s">
         <v>1057</v>
       </c>
       <c r="J501" s="10" t="s">
@@ -19914,7 +19905,7 @@
       <c r="C502" s="18">
         <v>2</v>
       </c>
-      <c r="D502" s="38" t="s">
+      <c r="D502" s="37" t="s">
         <v>425</v>
       </c>
       <c r="E502" s="10">
@@ -19944,7 +19935,7 @@
       <c r="C503" s="18">
         <v>3</v>
       </c>
-      <c r="D503" s="38" t="s">
+      <c r="D503" s="37" t="s">
         <v>310</v>
       </c>
       <c r="E503" s="10">
@@ -21294,7 +21285,7 @@
       <c r="O550" s="2"/>
     </row>
     <row r="551" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D551" s="38" t="s">
+      <c r="D551" s="37" t="s">
         <v>1016</v>
       </c>
       <c r="E551" s="4"/>
@@ -21313,7 +21304,7 @@
       <c r="C552" s="18">
         <v>1</v>
       </c>
-      <c r="D552" s="38" t="s">
+      <c r="D552" s="37" t="s">
         <v>1015</v>
       </c>
       <c r="E552" s="10"/>
@@ -21338,7 +21329,7 @@
       <c r="C553" s="18">
         <v>2</v>
       </c>
-      <c r="D553" s="38" t="s">
+      <c r="D553" s="37" t="s">
         <v>1013</v>
       </c>
       <c r="E553" s="10"/>
@@ -21363,7 +21354,7 @@
       <c r="C554" s="18">
         <v>3</v>
       </c>
-      <c r="D554" s="38" t="s">
+      <c r="D554" s="37" t="s">
         <v>1011</v>
       </c>
       <c r="E554" s="10"/>
@@ -21424,7 +21415,7 @@
       <c r="O556" s="2"/>
     </row>
     <row r="557" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D557" s="38" t="s">
+      <c r="D557" s="37" t="s">
         <v>1007</v>
       </c>
       <c r="E557" s="4"/>
@@ -21443,7 +21434,7 @@
       <c r="C558" s="18">
         <v>1</v>
       </c>
-      <c r="D558" s="38" t="s">
+      <c r="D558" s="37" t="s">
         <v>1006</v>
       </c>
       <c r="E558" s="10"/>
@@ -21468,7 +21459,7 @@
       <c r="C559" s="18">
         <v>2</v>
       </c>
-      <c r="D559" s="38" t="s">
+      <c r="D559" s="37" t="s">
         <v>1004</v>
       </c>
       <c r="E559" s="10"/>
@@ -21493,7 +21484,7 @@
       <c r="C560" s="18">
         <v>3</v>
       </c>
-      <c r="D560" s="38" t="s">
+      <c r="D560" s="37" t="s">
         <v>1002</v>
       </c>
       <c r="E560" s="10"/>
@@ -21594,25 +21585,25 @@
       <c r="K566" s="4"/>
     </row>
     <row r="567" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D567" s="42" t="s">
+      <c r="D567" s="41" t="s">
         <v>1407</v>
       </c>
-      <c r="E567" s="42"/>
-      <c r="F567" s="42"/>
-      <c r="G567" s="42"/>
-      <c r="H567" s="42"/>
-      <c r="I567" s="42"/>
+      <c r="E567" s="41"/>
+      <c r="F567" s="41"/>
+      <c r="G567" s="41"/>
+      <c r="H567" s="41"/>
+      <c r="I567" s="41"/>
       <c r="J567" s="18"/>
     </row>
     <row r="568" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D568" s="41" t="s">
+      <c r="D568" s="42" t="s">
         <v>860</v>
       </c>
-      <c r="E568" s="41"/>
-      <c r="F568" s="41"/>
-      <c r="G568" s="41"/>
-      <c r="H568" s="41"/>
-      <c r="I568" s="41"/>
+      <c r="E568" s="42"/>
+      <c r="F568" s="42"/>
+      <c r="G568" s="42"/>
+      <c r="H568" s="42"/>
+      <c r="I568" s="42"/>
       <c r="J568" s="3"/>
       <c r="K568" s="3"/>
       <c r="N568" s="2"/>
@@ -21635,14 +21626,14 @@
       <c r="O569" s="2"/>
     </row>
     <row r="570" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D570" s="41" t="s">
+      <c r="D570" s="42" t="s">
         <v>898</v>
       </c>
-      <c r="E570" s="41"/>
-      <c r="F570" s="41"/>
-      <c r="G570" s="41"/>
-      <c r="H570" s="41"/>
-      <c r="I570" s="41"/>
+      <c r="E570" s="42"/>
+      <c r="F570" s="42"/>
+      <c r="G570" s="42"/>
+      <c r="H570" s="42"/>
+      <c r="I570" s="42"/>
       <c r="J570" s="3"/>
       <c r="K570" s="3"/>
       <c r="N570" s="2"/>
@@ -21708,7 +21699,7 @@
       <c r="C574" s="18">
         <v>1</v>
       </c>
-      <c r="D574" s="38" t="s">
+      <c r="D574" s="37" t="s">
         <v>205</v>
       </c>
       <c r="E574" s="10">
@@ -21739,7 +21730,7 @@
       <c r="C575" s="18">
         <v>2</v>
       </c>
-      <c r="D575" s="38" t="s">
+      <c r="D575" s="37" t="s">
         <v>797</v>
       </c>
       <c r="E575" s="10">
@@ -21770,7 +21761,7 @@
       <c r="C576" s="18">
         <v>3</v>
       </c>
-      <c r="D576" s="38" t="s">
+      <c r="D576" s="37" t="s">
         <v>200</v>
       </c>
       <c r="E576" s="10">
@@ -21949,7 +21940,7 @@
       <c r="A582" s="5"/>
       <c r="B582" s="5"/>
       <c r="C582" s="18"/>
-      <c r="D582" s="38" t="s">
+      <c r="D582" s="37" t="s">
         <v>1007</v>
       </c>
       <c r="E582" s="10"/>
@@ -21957,7 +21948,7 @@
       <c r="G582" s="18"/>
       <c r="H582" s="18"/>
       <c r="I582" s="10"/>
-      <c r="J582" s="39"/>
+      <c r="J582" s="38"/>
       <c r="K582" s="10"/>
       <c r="N582" s="2"/>
       <c r="O582" s="2"/>
@@ -21968,7 +21959,7 @@
       <c r="C583" s="18">
         <v>1</v>
       </c>
-      <c r="D583" s="38" t="s">
+      <c r="D583" s="37" t="s">
         <v>754</v>
       </c>
       <c r="E583" s="18">
@@ -22001,7 +21992,7 @@
       <c r="C584" s="18">
         <v>2</v>
       </c>
-      <c r="D584" s="45" t="s">
+      <c r="D584" s="39" t="s">
         <v>220</v>
       </c>
       <c r="E584" s="15">
@@ -22034,7 +22025,7 @@
       <c r="C585" s="18">
         <v>3</v>
       </c>
-      <c r="D585" s="38" t="s">
+      <c r="D585" s="37" t="s">
         <v>813</v>
       </c>
       <c r="E585" s="10">
@@ -22305,15 +22296,15 @@
     </row>
     <row r="594" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C594" s="18"/>
-      <c r="D594" s="38" t="s">
+      <c r="D594" s="37" t="s">
         <v>1058</v>
       </c>
       <c r="E594" s="18"/>
       <c r="F594" s="18"/>
       <c r="G594" s="10"/>
       <c r="H594" s="10"/>
-      <c r="I594" s="39"/>
-      <c r="J594" s="39"/>
+      <c r="I594" s="38"/>
+      <c r="J594" s="38"/>
       <c r="K594" s="10"/>
       <c r="N594" s="2"/>
       <c r="O594" s="2"/>
@@ -22322,7 +22313,7 @@
       <c r="C595" s="18">
         <v>1</v>
       </c>
-      <c r="D595" s="38" t="s">
+      <c r="D595" s="37" t="s">
         <v>295</v>
       </c>
       <c r="E595" s="10">
@@ -22338,7 +22329,7 @@
       <c r="I595" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="J595" s="39" t="s">
+      <c r="J595" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K595" s="10" t="s">
@@ -22351,7 +22342,7 @@
       <c r="C596" s="18">
         <v>2</v>
       </c>
-      <c r="D596" s="38" t="s">
+      <c r="D596" s="37" t="s">
         <v>764</v>
       </c>
       <c r="E596" s="18">
@@ -22369,7 +22360,7 @@
       <c r="I596" s="10" t="s">
         <v>1428</v>
       </c>
-      <c r="J596" s="39" t="s">
+      <c r="J596" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K596" s="10" t="s">
@@ -22382,7 +22373,7 @@
       <c r="C597" s="18">
         <v>3</v>
       </c>
-      <c r="D597" s="38" t="s">
+      <c r="D597" s="37" t="s">
         <v>286</v>
       </c>
       <c r="E597" s="10">
@@ -22398,7 +22389,7 @@
       <c r="I597" s="18" t="s">
         <v>1232</v>
       </c>
-      <c r="J597" s="39" t="s">
+      <c r="J597" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K597" s="10" t="s">
@@ -22854,7 +22845,7 @@
     </row>
     <row r="614" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C614" s="18"/>
-      <c r="D614" s="38" t="s">
+      <c r="D614" s="37" t="s">
         <v>1158</v>
       </c>
       <c r="E614" s="10"/>
@@ -22871,7 +22862,7 @@
       <c r="C615" s="18">
         <v>1</v>
       </c>
-      <c r="D615" s="45" t="s">
+      <c r="D615" s="39" t="s">
         <v>293</v>
       </c>
       <c r="E615" s="15">
@@ -22884,10 +22875,10 @@
       <c r="H615" s="15" t="s">
         <v>847</v>
       </c>
-      <c r="I615" s="46" t="s">
+      <c r="I615" s="40" t="s">
         <v>1440</v>
       </c>
-      <c r="J615" s="39" t="s">
+      <c r="J615" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K615" s="15" t="s">
@@ -22900,7 +22891,7 @@
       <c r="C616" s="18">
         <v>2</v>
       </c>
-      <c r="D616" s="38" t="s">
+      <c r="D616" s="37" t="s">
         <v>297</v>
       </c>
       <c r="E616" s="10">
@@ -22916,7 +22907,7 @@
       <c r="I616" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="J616" s="39" t="s">
+      <c r="J616" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K616" s="10" t="s">
@@ -22929,7 +22920,7 @@
       <c r="C617" s="18">
         <v>3</v>
       </c>
-      <c r="D617" s="38" t="s">
+      <c r="D617" s="37" t="s">
         <v>336</v>
       </c>
       <c r="E617" s="10">
@@ -22945,7 +22936,7 @@
       <c r="I617" s="18" t="s">
         <v>1441</v>
       </c>
-      <c r="J617" s="39" t="s">
+      <c r="J617" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K617" s="10" t="s">
@@ -23292,7 +23283,7 @@
       <c r="C632" s="18">
         <v>1</v>
       </c>
-      <c r="D632" s="38" t="s">
+      <c r="D632" s="37" t="s">
         <v>230</v>
       </c>
       <c r="E632" s="10">
@@ -23321,7 +23312,7 @@
       <c r="C633" s="18">
         <v>2</v>
       </c>
-      <c r="D633" s="38" t="s">
+      <c r="D633" s="37" t="s">
         <v>828</v>
       </c>
       <c r="E633" s="10">
@@ -23350,7 +23341,7 @@
       <c r="C634" s="18">
         <v>4</v>
       </c>
-      <c r="D634" s="38" t="s">
+      <c r="D634" s="37" t="s">
         <v>832</v>
       </c>
       <c r="E634" s="10">
@@ -23559,14 +23550,14 @@
     </row>
     <row r="641" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C641" s="18"/>
-      <c r="D641" s="38" t="s">
+      <c r="D641" s="37" t="s">
         <v>1458</v>
       </c>
       <c r="E641" s="18"/>
       <c r="F641" s="18"/>
       <c r="G641" s="10"/>
       <c r="H641" s="10"/>
-      <c r="I641" s="39"/>
+      <c r="I641" s="38"/>
       <c r="J641" s="18"/>
       <c r="K641" s="10"/>
       <c r="N641" s="2"/>
@@ -23576,7 +23567,7 @@
       <c r="C642" s="18">
         <v>1</v>
       </c>
-      <c r="D642" s="38" t="s">
+      <c r="D642" s="37" t="s">
         <v>732</v>
       </c>
       <c r="E642" s="18">
@@ -23607,7 +23598,7 @@
       <c r="C643" s="18">
         <v>2</v>
       </c>
-      <c r="D643" s="38" t="s">
+      <c r="D643" s="37" t="s">
         <v>260</v>
       </c>
       <c r="E643" s="18">
@@ -23638,7 +23629,7 @@
       <c r="C644" s="18">
         <v>3</v>
       </c>
-      <c r="D644" s="38" t="s">
+      <c r="D644" s="37" t="s">
         <v>262</v>
       </c>
       <c r="E644" s="10">
@@ -24272,7 +24263,7 @@
     </row>
     <row r="665" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C665" s="18"/>
-      <c r="D665" s="38" t="s">
+      <c r="D665" s="37" t="s">
         <v>1058</v>
       </c>
       <c r="E665" s="18"/>
@@ -24289,7 +24280,7 @@
       <c r="C666" s="18">
         <v>1</v>
       </c>
-      <c r="D666" s="38" t="s">
+      <c r="D666" s="37" t="s">
         <v>309</v>
       </c>
       <c r="E666" s="10">
@@ -24318,7 +24309,7 @@
       <c r="C667" s="18">
         <v>2</v>
       </c>
-      <c r="D667" s="38" t="s">
+      <c r="D667" s="37" t="s">
         <v>314</v>
       </c>
       <c r="E667" s="10">
@@ -24347,7 +24338,7 @@
       <c r="C668" s="18">
         <v>3</v>
       </c>
-      <c r="D668" s="38" t="s">
+      <c r="D668" s="37" t="s">
         <v>310</v>
       </c>
       <c r="E668" s="10">
@@ -25139,7 +25130,7 @@
     </row>
     <row r="699" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C699" s="18"/>
-      <c r="D699" s="38" t="s">
+      <c r="D699" s="37" t="s">
         <v>1158</v>
       </c>
       <c r="E699" s="10"/>
@@ -25155,7 +25146,7 @@
       <c r="C700" s="18">
         <v>1</v>
       </c>
-      <c r="D700" s="38" t="s">
+      <c r="D700" s="37" t="s">
         <v>361</v>
       </c>
       <c r="E700" s="18">
@@ -25183,7 +25174,7 @@
       <c r="C701" s="18">
         <v>2</v>
       </c>
-      <c r="D701" s="38" t="s">
+      <c r="D701" s="37" t="s">
         <v>303</v>
       </c>
       <c r="E701" s="10">
@@ -25211,7 +25202,7 @@
       <c r="C702" s="18">
         <v>3</v>
       </c>
-      <c r="D702" s="38" t="s">
+      <c r="D702" s="37" t="s">
         <v>21</v>
       </c>
       <c r="E702" s="10">
@@ -25548,7 +25539,7 @@
       <c r="C717" s="18">
         <v>1</v>
       </c>
-      <c r="D717" s="38" t="s">
+      <c r="D717" s="37" t="s">
         <v>804</v>
       </c>
       <c r="E717" s="10">
@@ -25578,7 +25569,7 @@
       <c r="C718" s="18">
         <v>2</v>
       </c>
-      <c r="D718" s="38" t="s">
+      <c r="D718" s="37" t="s">
         <v>200</v>
       </c>
       <c r="E718" s="10">
@@ -25608,7 +25599,7 @@
       <c r="C719" s="18">
         <v>2</v>
       </c>
-      <c r="D719" s="38" t="s">
+      <c r="D719" s="37" t="s">
         <v>797</v>
       </c>
       <c r="E719" s="10">
@@ -25811,7 +25802,7 @@
     </row>
     <row r="726" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C726" s="18"/>
-      <c r="D726" s="38" t="s">
+      <c r="D726" s="37" t="s">
         <v>1007</v>
       </c>
       <c r="E726" s="10"/>
@@ -25819,7 +25810,7 @@
       <c r="G726" s="18"/>
       <c r="H726" s="18"/>
       <c r="I726" s="18"/>
-      <c r="J726" s="39"/>
+      <c r="J726" s="38"/>
       <c r="K726" s="10"/>
       <c r="O726" s="2"/>
     </row>
@@ -25827,7 +25818,7 @@
       <c r="C727" s="18">
         <v>1</v>
       </c>
-      <c r="D727" s="38" t="s">
+      <c r="D727" s="37" t="s">
         <v>220</v>
       </c>
       <c r="E727" s="10">
@@ -25857,7 +25848,7 @@
       <c r="C728" s="18">
         <v>2</v>
       </c>
-      <c r="D728" s="38" t="s">
+      <c r="D728" s="37" t="s">
         <v>754</v>
       </c>
       <c r="E728" s="18">
@@ -25887,7 +25878,7 @@
       <c r="C729" s="18">
         <v>3</v>
       </c>
-      <c r="D729" s="38" t="s">
+      <c r="D729" s="37" t="s">
         <v>757</v>
       </c>
       <c r="E729" s="10">
@@ -26213,7 +26204,7 @@
     </row>
     <row r="740" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C740" s="18"/>
-      <c r="D740" s="38" t="s">
+      <c r="D740" s="37" t="s">
         <v>1058</v>
       </c>
       <c r="E740" s="18"/>
@@ -26229,7 +26220,7 @@
       <c r="C741" s="18">
         <v>1</v>
       </c>
-      <c r="D741" s="38" t="s">
+      <c r="D741" s="37" t="s">
         <v>758</v>
       </c>
       <c r="E741" s="10">
@@ -26259,7 +26250,7 @@
       <c r="C742" s="18">
         <v>2</v>
       </c>
-      <c r="D742" s="38" t="s">
+      <c r="D742" s="37" t="s">
         <v>764</v>
       </c>
       <c r="E742" s="18">
@@ -26289,7 +26280,7 @@
       <c r="C743" s="18">
         <v>3</v>
       </c>
-      <c r="D743" s="38" t="s">
+      <c r="D743" s="37" t="s">
         <v>75</v>
       </c>
       <c r="E743" s="10">
@@ -26305,7 +26296,7 @@
       <c r="I743" s="10" t="s">
         <v>1512</v>
       </c>
-      <c r="J743" s="39" t="s">
+      <c r="J743" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K743" s="10" t="s">
@@ -26767,7 +26758,7 @@
     </row>
     <row r="761" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C761" s="18"/>
-      <c r="D761" s="38" t="s">
+      <c r="D761" s="37" t="s">
         <v>1158</v>
       </c>
       <c r="E761" s="10"/>
@@ -26782,7 +26773,7 @@
       <c r="C762" s="18">
         <v>1</v>
       </c>
-      <c r="D762" s="38" t="s">
+      <c r="D762" s="37" t="s">
         <v>293</v>
       </c>
       <c r="E762" s="10">
@@ -26825,7 +26816,7 @@
       <c r="I763" s="18" t="s">
         <v>1522</v>
       </c>
-      <c r="J763" s="39" t="s">
+      <c r="J763" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K763" s="18" t="s">
@@ -26836,7 +26827,7 @@
       <c r="C764" s="18">
         <v>3</v>
       </c>
-      <c r="D764" s="38" t="s">
+      <c r="D764" s="37" t="s">
         <v>297</v>
       </c>
       <c r="E764" s="10">
@@ -26852,7 +26843,7 @@
       <c r="I764" s="10" t="s">
         <v>1523</v>
       </c>
-      <c r="J764" s="39" t="s">
+      <c r="J764" s="38" t="s">
         <v>1019</v>
       </c>
       <c r="K764" s="10" t="s">
@@ -27718,7 +27709,7 @@
       <c r="C800" s="18">
         <v>1</v>
       </c>
-      <c r="D800" s="38" t="s">
+      <c r="D800" s="37" t="s">
         <v>256</v>
       </c>
       <c r="E800" s="10">
@@ -27748,7 +27739,7 @@
       <c r="C801" s="18">
         <v>2</v>
       </c>
-      <c r="D801" s="38" t="s">
+      <c r="D801" s="37" t="s">
         <v>230</v>
       </c>
       <c r="E801" s="10">
@@ -27778,7 +27769,7 @@
       <c r="C802" s="18">
         <v>3</v>
       </c>
-      <c r="D802" s="38" t="s">
+      <c r="D802" s="37" t="s">
         <v>828</v>
       </c>
       <c r="E802" s="10">
@@ -28064,7 +28055,7 @@
     </row>
     <row r="812" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C812" s="18"/>
-      <c r="D812" s="38" t="s">
+      <c r="D812" s="37" t="s">
         <v>1007</v>
       </c>
       <c r="E812" s="10"/>
@@ -28080,7 +28071,7 @@
       <c r="C813" s="18">
         <v>1</v>
       </c>
-      <c r="D813" s="38" t="s">
+      <c r="D813" s="37" t="s">
         <v>260</v>
       </c>
       <c r="E813" s="18">
@@ -28110,7 +28101,7 @@
       <c r="C814" s="18">
         <v>2</v>
       </c>
-      <c r="D814" s="38" t="s">
+      <c r="D814" s="37" t="s">
         <v>732</v>
       </c>
       <c r="E814" s="18">
@@ -28140,7 +28131,7 @@
       <c r="C815" s="18">
         <v>3</v>
       </c>
-      <c r="D815" s="38" t="s">
+      <c r="D815" s="37" t="s">
         <v>823</v>
       </c>
       <c r="E815" s="10">
@@ -28990,47 +28981,66 @@
       <c r="O843" s="2"/>
     </row>
     <row r="844" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D844" s="16"/>
-      <c r="G844" s="4"/>
-      <c r="H844" s="4"/>
-      <c r="I844" s="4"/>
-      <c r="J844" s="4"/>
-      <c r="K844" s="4"/>
+      <c r="C844" s="18"/>
+      <c r="D844" s="37" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E844" s="18"/>
+      <c r="F844" s="18"/>
+      <c r="G844" s="10"/>
+      <c r="H844" s="10"/>
+      <c r="I844" s="10"/>
+      <c r="J844" s="10"/>
+      <c r="K844" s="10"/>
       <c r="O844" s="2"/>
     </row>
     <row r="845" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C845" s="18"/>
-      <c r="D845" s="38" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E845" s="18"/>
-      <c r="F845" s="18"/>
-      <c r="G845" s="10"/>
-      <c r="H845" s="10"/>
-      <c r="I845" s="10"/>
-      <c r="J845" s="10"/>
-      <c r="K845" s="10"/>
+      <c r="C845" s="18">
+        <v>1</v>
+      </c>
+      <c r="D845" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="E845" s="10">
+        <v>2016</v>
+      </c>
+      <c r="F845" s="10"/>
+      <c r="G845" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="H845" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="I845" s="18" t="s">
+        <v>1580</v>
+      </c>
+      <c r="J845" s="18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K845" s="10" t="s">
+        <v>278</v>
+      </c>
       <c r="O845" s="2"/>
     </row>
     <row r="846" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C846" s="18">
-        <v>1</v>
-      </c>
-      <c r="D846" s="38" t="s">
-        <v>305</v>
+        <v>2</v>
+      </c>
+      <c r="D846" s="37" t="s">
+        <v>309</v>
       </c>
       <c r="E846" s="10">
         <v>2016</v>
       </c>
-      <c r="F846" s="10"/>
+      <c r="F846" s="18"/>
       <c r="G846" s="10" t="s">
         <v>846</v>
       </c>
       <c r="H846" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="I846" s="18" t="s">
-        <v>1580</v>
+      <c r="I846" s="38" t="s">
+        <v>1282</v>
       </c>
       <c r="J846" s="18" t="s">
         <v>1019</v>
@@ -29042,191 +29052,190 @@
     </row>
     <row r="847" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C847" s="18">
-        <v>2</v>
-      </c>
-      <c r="D847" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="E847" s="10">
+        <v>3</v>
+      </c>
+      <c r="D847" s="39" t="s">
+        <v>312</v>
+      </c>
+      <c r="E847" s="15">
         <v>2016</v>
       </c>
-      <c r="F847" s="18"/>
-      <c r="G847" s="10" t="s">
+      <c r="F847" s="34"/>
+      <c r="G847" s="15" t="s">
         <v>846</v>
       </c>
-      <c r="H847" s="10" t="s">
+      <c r="H847" s="15" t="s">
         <v>847</v>
       </c>
-      <c r="I847" s="39" t="s">
-        <v>1282</v>
+      <c r="I847" s="15" t="s">
+        <v>1377</v>
       </c>
       <c r="J847" s="18" t="s">
         <v>1019</v>
       </c>
-      <c r="K847" s="10" t="s">
+      <c r="K847" s="15" t="s">
         <v>278</v>
       </c>
       <c r="O847" s="2"/>
     </row>
     <row r="848" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C848" s="18">
-        <v>3</v>
-      </c>
-      <c r="D848" s="45" t="s">
-        <v>312</v>
-      </c>
-      <c r="E848" s="15">
+      <c r="C848" s="5">
+        <v>4</v>
+      </c>
+      <c r="D848" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E848" s="4">
         <v>2016</v>
       </c>
-      <c r="F848" s="34"/>
-      <c r="G848" s="15" t="s">
-        <v>846</v>
-      </c>
-      <c r="H848" s="15" t="s">
-        <v>847</v>
-      </c>
-      <c r="I848" s="15" t="s">
-        <v>1377</v>
-      </c>
-      <c r="J848" s="18" t="s">
+      <c r="F848" s="4"/>
+      <c r="G848" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H848" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I848" s="4" t="s">
+        <v>1581</v>
+      </c>
+      <c r="J848" s="5" t="s">
         <v>1019</v>
       </c>
-      <c r="K848" s="15" t="s">
-        <v>278</v>
+      <c r="K848" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="O848" s="2"/>
     </row>
     <row r="849" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C849" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D849" s="16" t="s">
-        <v>20</v>
+        <v>425</v>
       </c>
       <c r="E849" s="4">
         <v>2016</v>
       </c>
       <c r="F849" s="4"/>
-      <c r="G849" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H849" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I849" s="4" t="s">
-        <v>1581</v>
+      <c r="G849" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="H849" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="I849" s="5" t="s">
+        <v>1569</v>
       </c>
       <c r="J849" s="5" t="s">
         <v>1019</v>
       </c>
       <c r="K849" s="4" t="s">
-        <v>191</v>
+        <v>412</v>
       </c>
       <c r="O849" s="2"/>
     </row>
     <row r="850" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C850" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D850" s="16" t="s">
-        <v>425</v>
+        <v>25</v>
       </c>
       <c r="E850" s="4">
         <v>2016</v>
       </c>
       <c r="F850" s="4"/>
-      <c r="G850" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="H850" s="5" t="s">
+      <c r="G850" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H850" s="4" t="s">
         <v>845</v>
       </c>
       <c r="I850" s="5" t="s">
-        <v>1569</v>
+        <v>1582</v>
       </c>
       <c r="J850" s="5" t="s">
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="K850" s="4" t="s">
-        <v>412</v>
+        <v>191</v>
       </c>
       <c r="O850" s="2"/>
     </row>
     <row r="851" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C851" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D851" s="16" t="s">
-        <v>25</v>
+        <v>314</v>
       </c>
       <c r="E851" s="4">
         <v>2016</v>
       </c>
-      <c r="F851" s="4"/>
+      <c r="F851" s="18"/>
       <c r="G851" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H851" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I851" s="5" t="s">
-        <v>1582</v>
+        <v>847</v>
+      </c>
+      <c r="I851" s="11" t="s">
+        <v>1281</v>
       </c>
       <c r="J851" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K851" s="4" t="s">
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="O851" s="2"/>
     </row>
     <row r="852" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C852" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D852" s="16" t="s">
-        <v>314</v>
+        <v>31</v>
       </c>
       <c r="E852" s="4">
         <v>2016</v>
       </c>
-      <c r="F852" s="18"/>
+      <c r="F852" s="4"/>
       <c r="G852" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H852" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I852" s="11" t="s">
-        <v>1281</v>
+        <v>845</v>
+      </c>
+      <c r="I852" s="5" t="s">
+        <v>1583</v>
       </c>
       <c r="J852" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K852" s="4" t="s">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="O852" s="2"/>
     </row>
     <row r="853" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C853" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D853" s="16" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E853" s="4">
         <v>2016</v>
       </c>
-      <c r="F853" s="4"/>
       <c r="G853" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H853" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I853" s="5" t="s">
-        <v>1583</v>
+      <c r="I853" s="6" t="s">
+        <v>1584</v>
       </c>
       <c r="J853" s="5" t="s">
         <v>1043</v>
@@ -29238,93 +29247,94 @@
     </row>
     <row r="854" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C854" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D854" s="16" t="s">
-        <v>14</v>
+        <v>310</v>
       </c>
       <c r="E854" s="4">
         <v>2016</v>
       </c>
+      <c r="F854" s="4"/>
       <c r="G854" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H854" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I854" s="6" t="s">
-        <v>1584</v>
+        <v>847</v>
+      </c>
+      <c r="I854" s="4" t="s">
+        <v>1585</v>
       </c>
       <c r="J854" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K854" s="4" t="s">
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="O854" s="2"/>
     </row>
     <row r="855" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C855" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D855" s="16" t="s">
-        <v>310</v>
+        <v>26</v>
       </c>
       <c r="E855" s="4">
         <v>2016</v>
       </c>
       <c r="F855" s="4"/>
       <c r="G855" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H855" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I855" s="4" t="s">
-        <v>1585</v>
+        <v>845</v>
+      </c>
+      <c r="I855" s="5" t="s">
+        <v>1586</v>
       </c>
       <c r="J855" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K855" s="4" t="s">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="O855" s="2"/>
     </row>
     <row r="856" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C856" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D856" s="16" t="s">
-        <v>26</v>
+        <v>307</v>
       </c>
       <c r="E856" s="4">
         <v>2016</v>
       </c>
       <c r="F856" s="4"/>
       <c r="G856" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H856" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I856" s="5" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="J856" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K856" s="4" t="s">
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="O856" s="2"/>
     </row>
     <row r="857" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C857" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D857" s="16" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="E857" s="4">
         <v>2016</v>
@@ -29337,7 +29347,7 @@
         <v>847</v>
       </c>
       <c r="I857" s="5" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="J857" s="5" t="s">
         <v>1043</v>
@@ -29349,38 +29359,38 @@
     </row>
     <row r="858" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C858" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D858" s="16" t="s">
-        <v>316</v>
+        <v>16</v>
       </c>
       <c r="E858" s="4">
         <v>2016</v>
       </c>
       <c r="F858" s="4"/>
       <c r="G858" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H858" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I858" s="5" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="J858" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K858" s="4" t="s">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="O858" s="2"/>
     </row>
     <row r="859" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C859" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D859" s="16" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E859" s="4">
         <v>2016</v>
@@ -29393,7 +29403,7 @@
         <v>845</v>
       </c>
       <c r="I859" s="5" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="J859" s="5" t="s">
         <v>1043</v>
@@ -29405,10 +29415,10 @@
     </row>
     <row r="860" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C860" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D860" s="16" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E860" s="4">
         <v>2016</v>
@@ -29421,7 +29431,7 @@
         <v>845</v>
       </c>
       <c r="I860" s="5" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="J860" s="5" t="s">
         <v>1043</v>
@@ -29433,40 +29443,39 @@
     </row>
     <row r="861" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C861" s="5">
-        <v>16</v>
-      </c>
-      <c r="D861" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E861" s="4">
+        <v>17</v>
+      </c>
+      <c r="D861" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="E861" s="5">
         <v>2016</v>
       </c>
-      <c r="F861" s="4"/>
       <c r="G861" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H861" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I861" s="5" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="J861" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K861" s="4" t="s">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="O861" s="2"/>
     </row>
     <row r="862" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C862" s="5">
-        <v>17</v>
-      </c>
-      <c r="D862" s="27" t="s">
-        <v>399</v>
-      </c>
-      <c r="E862" s="5">
+        <v>18</v>
+      </c>
+      <c r="D862" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="E862" s="4">
         <v>2016</v>
       </c>
       <c r="G862" s="4" t="s">
@@ -29476,24 +29485,24 @@
         <v>847</v>
       </c>
       <c r="I862" s="5" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="J862" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K862" s="4" t="s">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="O862" s="2"/>
     </row>
     <row r="863" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C863" s="5">
-        <v>18</v>
-      </c>
-      <c r="D863" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E863" s="4">
+        <v>19</v>
+      </c>
+      <c r="D863" s="27" t="s">
+        <v>380</v>
+      </c>
+      <c r="E863" s="5">
         <v>2016</v>
       </c>
       <c r="G863" s="4" t="s">
@@ -29503,22 +29512,22 @@
         <v>847</v>
       </c>
       <c r="I863" s="5" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="J863" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K863" s="4" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
       <c r="O863" s="2"/>
     </row>
     <row r="864" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C864" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D864" s="27" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="E864" s="5">
         <v>2016</v>
@@ -29530,7 +29539,7 @@
         <v>847</v>
       </c>
       <c r="I864" s="5" t="s">
-        <v>1594</v>
+        <v>183</v>
       </c>
       <c r="J864" s="5" t="s">
         <v>1043</v>
@@ -29542,14 +29551,15 @@
     </row>
     <row r="865" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C865" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D865" s="27" t="s">
-        <v>394</v>
-      </c>
-      <c r="E865" s="5">
+        <v>385</v>
+      </c>
+      <c r="E865" s="4">
         <v>2016</v>
       </c>
+      <c r="F865" s="4"/>
       <c r="G865" s="4" t="s">
         <v>846</v>
       </c>
@@ -29557,7 +29567,7 @@
         <v>847</v>
       </c>
       <c r="I865" s="5" t="s">
-        <v>183</v>
+        <v>1595</v>
       </c>
       <c r="J865" s="5" t="s">
         <v>1043</v>
@@ -29569,93 +29579,93 @@
     </row>
     <row r="866" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C866" s="5">
-        <v>21</v>
-      </c>
-      <c r="D866" s="27" t="s">
-        <v>385</v>
+        <v>22</v>
+      </c>
+      <c r="D866" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="E866" s="4">
         <v>2016</v>
       </c>
-      <c r="F866" s="4"/>
       <c r="G866" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H866" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I866" s="5" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="J866" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K866" s="4" t="s">
-        <v>325</v>
+        <v>191</v>
       </c>
       <c r="O866" s="2"/>
     </row>
     <row r="867" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C867" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D867" s="16" t="s">
-        <v>17</v>
+        <v>318</v>
       </c>
       <c r="E867" s="4">
         <v>2016</v>
       </c>
+      <c r="F867" s="4"/>
       <c r="G867" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H867" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I867" s="5" t="s">
-        <v>1596</v>
+        <v>1177</v>
       </c>
       <c r="J867" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K867" s="4" t="s">
-        <v>191</v>
+        <v>278</v>
       </c>
       <c r="O867" s="2"/>
     </row>
     <row r="868" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C868" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D868" s="16" t="s">
-        <v>318</v>
+        <v>51</v>
       </c>
       <c r="E868" s="4">
         <v>2016</v>
       </c>
       <c r="F868" s="4"/>
       <c r="G868" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H868" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I868" s="5" t="s">
-        <v>1177</v>
+        <v>376</v>
       </c>
       <c r="J868" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K868" s="4" t="s">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="O868" s="2"/>
     </row>
     <row r="869" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C869" s="5">
+        <v>25</v>
+      </c>
+      <c r="D869" s="16" t="s">
         <v>24</v>
-      </c>
-      <c r="D869" s="16" t="s">
-        <v>51</v>
       </c>
       <c r="E869" s="4">
         <v>2016</v>
@@ -29668,7 +29678,7 @@
         <v>845</v>
       </c>
       <c r="I869" s="5" t="s">
-        <v>376</v>
+        <v>1597</v>
       </c>
       <c r="J869" s="5" t="s">
         <v>1043</v>
@@ -29680,10 +29690,10 @@
     </row>
     <row r="870" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C870" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D870" s="16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E870" s="4">
         <v>2016</v>
@@ -29695,8 +29705,8 @@
       <c r="H870" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I870" s="5" t="s">
-        <v>1597</v>
+      <c r="I870" s="4" t="s">
+        <v>1598</v>
       </c>
       <c r="J870" s="5" t="s">
         <v>1043</v>
@@ -29708,10 +29718,10 @@
     </row>
     <row r="871" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C871" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D871" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E871" s="4">
         <v>2016</v>
@@ -29723,8 +29733,8 @@
       <c r="H871" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I871" s="4" t="s">
-        <v>1598</v>
+      <c r="I871" s="6" t="s">
+        <v>1442</v>
       </c>
       <c r="J871" s="5" t="s">
         <v>1043</v>
@@ -29736,23 +29746,22 @@
     </row>
     <row r="872" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C872" s="5">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D872" s="16" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E872" s="4">
         <v>2016</v>
       </c>
-      <c r="F872" s="4"/>
       <c r="G872" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H872" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I872" s="6" t="s">
-        <v>1442</v>
+      <c r="I872" s="4" t="s">
+        <v>1599</v>
       </c>
       <c r="J872" s="5" t="s">
         <v>1043</v>
@@ -29764,66 +29773,63 @@
     </row>
     <row r="873" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C873" s="5">
-        <v>28</v>
-      </c>
-      <c r="D873" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E873" s="4">
+        <v>29</v>
+      </c>
+      <c r="D873" s="27" t="s">
+        <v>390</v>
+      </c>
+      <c r="E873" s="5">
         <v>2016</v>
       </c>
       <c r="G873" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H873" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I873" s="4" t="s">
-        <v>1599</v>
-      </c>
-      <c r="J873" s="5" t="s">
-        <v>1043</v>
+        <v>847</v>
+      </c>
+      <c r="I873" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="K873" s="4" t="s">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="O873" s="2"/>
     </row>
     <row r="874" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C874" s="5">
-        <v>29</v>
-      </c>
-      <c r="D874" s="27" t="s">
-        <v>390</v>
-      </c>
-      <c r="E874" s="5">
+        <v>30</v>
+      </c>
+      <c r="D874" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E874" s="4">
         <v>2016</v>
       </c>
+      <c r="F874" s="4"/>
       <c r="G874" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H874" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I874" s="5" t="s">
-        <v>62</v>
+        <v>1600</v>
       </c>
       <c r="K874" s="4" t="s">
-        <v>325</v>
+        <v>191</v>
       </c>
       <c r="O874" s="2"/>
     </row>
     <row r="875" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C875" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D875" s="16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E875" s="4">
         <v>2016</v>
       </c>
-      <c r="F875" s="4"/>
       <c r="G875" s="4" t="s">
         <v>844</v>
       </c>
@@ -29831,7 +29837,7 @@
         <v>845</v>
       </c>
       <c r="I875" s="5" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="K875" s="4" t="s">
         <v>191</v>
@@ -29840,14 +29846,15 @@
     </row>
     <row r="876" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C876" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D876" s="16" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E876" s="4">
         <v>2016</v>
       </c>
+      <c r="F876" s="4"/>
       <c r="G876" s="4" t="s">
         <v>844</v>
       </c>
@@ -29855,7 +29862,7 @@
         <v>845</v>
       </c>
       <c r="I876" s="5" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="K876" s="4" t="s">
         <v>191</v>
@@ -29864,59 +29871,59 @@
     </row>
     <row r="877" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C877" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D877" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="E877" s="4">
+        <v>404</v>
+      </c>
+      <c r="E877" s="5">
         <v>2016</v>
       </c>
-      <c r="F877" s="4"/>
       <c r="G877" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H877" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I877" s="5" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="K877" s="4" t="s">
-        <v>191</v>
+        <v>325</v>
       </c>
       <c r="O877" s="2"/>
     </row>
     <row r="878" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C878" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D878" s="16" t="s">
-        <v>404</v>
-      </c>
-      <c r="E878" s="5">
+        <v>54</v>
+      </c>
+      <c r="E878" s="4">
         <v>2016</v>
       </c>
+      <c r="F878" s="4"/>
       <c r="G878" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H878" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I878" s="5" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="K878" s="4" t="s">
-        <v>325</v>
+        <v>191</v>
       </c>
       <c r="O878" s="2"/>
     </row>
     <row r="879" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C879" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D879" s="16" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="E879" s="4">
         <v>2016</v>
@@ -29929,7 +29936,7 @@
         <v>845</v>
       </c>
       <c r="I879" s="5" t="s">
-        <v>1604</v>
+        <v>1254</v>
       </c>
       <c r="K879" s="4" t="s">
         <v>191</v>
@@ -29938,10 +29945,10 @@
     </row>
     <row r="880" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C880" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D880" s="16" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E880" s="4">
         <v>2016</v>
@@ -29954,7 +29961,7 @@
         <v>845</v>
       </c>
       <c r="I880" s="5" t="s">
-        <v>1254</v>
+        <v>1605</v>
       </c>
       <c r="K880" s="4" t="s">
         <v>191</v>
@@ -29963,15 +29970,14 @@
     </row>
     <row r="881" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C881" s="5">
-        <v>36</v>
-      </c>
-      <c r="D881" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E881" s="4">
+        <v>37</v>
+      </c>
+      <c r="D881" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E881" s="5">
         <v>2016</v>
       </c>
-      <c r="F881" s="4"/>
       <c r="G881" s="4" t="s">
         <v>844</v>
       </c>
@@ -29979,7 +29985,7 @@
         <v>845</v>
       </c>
       <c r="I881" s="5" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="K881" s="4" t="s">
         <v>191</v>
@@ -29988,12 +29994,12 @@
     </row>
     <row r="882" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C882" s="5">
-        <v>37</v>
-      </c>
-      <c r="D882" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="E882" s="5">
+        <v>38</v>
+      </c>
+      <c r="D882" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E882" s="4">
         <v>2016</v>
       </c>
       <c r="G882" s="4" t="s">
@@ -30002,9 +30008,10 @@
       <c r="H882" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I882" s="5" t="s">
-        <v>1606</v>
-      </c>
+      <c r="I882" s="4" t="s">
+        <v>1607</v>
+      </c>
+      <c r="J882" s="4"/>
       <c r="K882" s="4" t="s">
         <v>191</v>
       </c>
@@ -30012,14 +30019,15 @@
     </row>
     <row r="883" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C883" s="5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D883" s="16" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="E883" s="4">
         <v>2016</v>
       </c>
+      <c r="F883" s="4"/>
       <c r="G883" s="4" t="s">
         <v>844</v>
       </c>
@@ -30027,7 +30035,7 @@
         <v>845</v>
       </c>
       <c r="I883" s="4" t="s">
-        <v>1607</v>
+        <v>1094</v>
       </c>
       <c r="J883" s="4"/>
       <c r="K883" s="4" t="s">
@@ -30037,15 +30045,14 @@
     </row>
     <row r="884" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C884" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D884" s="16" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="E884" s="4">
         <v>2016</v>
       </c>
-      <c r="F884" s="4"/>
       <c r="G884" s="4" t="s">
         <v>844</v>
       </c>
@@ -30053,7 +30060,7 @@
         <v>845</v>
       </c>
       <c r="I884" s="4" t="s">
-        <v>1094</v>
+        <v>1059</v>
       </c>
       <c r="J884" s="4"/>
       <c r="K884" s="4" t="s">
@@ -30062,209 +30069,227 @@
       <c r="O884" s="2"/>
     </row>
     <row r="885" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C885" s="5">
-        <v>40</v>
-      </c>
-      <c r="D885" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E885" s="4">
-        <v>2016</v>
-      </c>
-      <c r="G885" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H885" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I885" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="J885" s="4"/>
-      <c r="K885" s="4" t="s">
+      <c r="C885" s="18"/>
+      <c r="D885" s="37" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E885" s="10"/>
+      <c r="F885" s="18"/>
+      <c r="G885" s="10"/>
+      <c r="H885" s="10"/>
+      <c r="I885" s="10"/>
+      <c r="J885" s="10"/>
+      <c r="K885" s="10"/>
+      <c r="M885" s="2"/>
+      <c r="N885" s="2"/>
+      <c r="O885" s="2"/>
+    </row>
+    <row r="886" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C886" s="18">
+        <v>1</v>
+      </c>
+      <c r="D886" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="E886" s="10">
+        <v>2017</v>
+      </c>
+      <c r="F886" s="10"/>
+      <c r="G886" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="H886" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="I886" s="10" t="s">
+        <v>1608</v>
+      </c>
+      <c r="J886" s="18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K886" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="M886" s="31"/>
+      <c r="N886" s="32"/>
+      <c r="O886" s="32"/>
+      <c r="P886" s="11"/>
+      <c r="Q886" s="11"/>
+      <c r="R886" s="11"/>
+      <c r="S886" s="11"/>
+    </row>
+    <row r="887" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C887" s="18">
+        <v>2</v>
+      </c>
+      <c r="D887" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="E887" s="10">
+        <v>2017</v>
+      </c>
+      <c r="F887" s="18"/>
+      <c r="G887" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="H887" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="I887" s="18" t="s">
+        <v>1609</v>
+      </c>
+      <c r="J887" s="18" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K887" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="O885" s="2"/>
-    </row>
-    <row r="886" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D886" s="16"/>
-      <c r="E886" s="4"/>
-      <c r="G886" s="4"/>
-      <c r="H886" s="4"/>
-      <c r="I886" s="4"/>
-      <c r="J886" s="4"/>
-      <c r="K886" s="4"/>
-      <c r="M886" s="2"/>
-      <c r="N886" s="2"/>
-      <c r="O886" s="2"/>
-    </row>
-    <row r="887" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C887" s="18"/>
-      <c r="D887" s="38" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E887" s="10"/>
-      <c r="F887" s="18"/>
-      <c r="G887" s="10"/>
-      <c r="H887" s="10"/>
-      <c r="I887" s="10"/>
-      <c r="J887" s="10"/>
-      <c r="K887" s="10"/>
-      <c r="M887" s="2"/>
-      <c r="N887" s="2"/>
       <c r="O887" s="2"/>
     </row>
     <row r="888" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C888" s="18">
-        <v>1</v>
-      </c>
-      <c r="D888" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="E888" s="10">
+        <v>3</v>
+      </c>
+      <c r="D888" s="26" t="s">
+        <v>698</v>
+      </c>
+      <c r="E888" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="F888" s="18"/>
+      <c r="G888" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="H888" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="I888" s="18" t="s">
+        <v>1610</v>
+      </c>
+      <c r="J888" s="18" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K888" s="18" t="s">
+        <v>610</v>
+      </c>
+      <c r="O888" s="2"/>
+    </row>
+    <row r="889" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C889" s="5">
+        <v>4</v>
+      </c>
+      <c r="D889" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="E889" s="5">
         <v>2017</v>
       </c>
-      <c r="F888" s="10"/>
-      <c r="G888" s="10" t="s">
+      <c r="G889" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="H888" s="10" t="s">
+      <c r="H889" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="I888" s="10" t="s">
-        <v>1608</v>
-      </c>
-      <c r="J888" s="18" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K888" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="M888" s="31"/>
-      <c r="N888" s="32"/>
-      <c r="O888" s="32"/>
-      <c r="P888" s="11"/>
-      <c r="Q888" s="11"/>
-      <c r="R888" s="11"/>
-      <c r="S888" s="11"/>
-    </row>
-    <row r="889" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C889" s="18">
-        <v>2</v>
-      </c>
-      <c r="D889" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E889" s="10">
-        <v>2017</v>
-      </c>
-      <c r="F889" s="18"/>
-      <c r="G889" s="10" t="s">
-        <v>844</v>
-      </c>
-      <c r="H889" s="10" t="s">
-        <v>845</v>
-      </c>
-      <c r="I889" s="18" t="s">
-        <v>1609</v>
-      </c>
-      <c r="J889" s="18" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K889" s="10" t="s">
+      <c r="I889" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J889" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K889" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="O889" s="2"/>
+    </row>
+    <row r="890" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C890" s="5">
+        <v>5</v>
+      </c>
+      <c r="D890" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E890" s="4">
+        <v>2018</v>
+      </c>
+      <c r="F890" s="4"/>
+      <c r="G890" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H890" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I890" s="5" t="s">
+        <v>1611</v>
+      </c>
+      <c r="J890" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K890" s="4" t="s">
         <v>191</v>
-      </c>
-      <c r="O889" s="2"/>
-    </row>
-    <row r="890" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C890" s="18">
-        <v>3</v>
-      </c>
-      <c r="D890" s="26" t="s">
-        <v>698</v>
-      </c>
-      <c r="E890" s="18" t="s">
-        <v>607</v>
-      </c>
-      <c r="F890" s="18"/>
-      <c r="G890" s="10" t="s">
-        <v>844</v>
-      </c>
-      <c r="H890" s="10" t="s">
-        <v>845</v>
-      </c>
-      <c r="I890" s="18" t="s">
-        <v>1610</v>
-      </c>
-      <c r="J890" s="18" t="s">
-        <v>1043</v>
-      </c>
-      <c r="K890" s="18" t="s">
-        <v>610</v>
       </c>
       <c r="O890" s="2"/>
     </row>
     <row r="891" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C891" s="5">
-        <v>4</v>
-      </c>
-      <c r="D891" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="E891" s="5">
-        <v>2017</v>
+        <v>6</v>
+      </c>
+      <c r="D891" s="27" t="s">
+        <v>710</v>
+      </c>
+      <c r="E891" s="5" t="s">
+        <v>607</v>
       </c>
       <c r="G891" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H891" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I891" s="5" t="s">
-        <v>165</v>
+        <v>1612</v>
       </c>
       <c r="J891" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="K891" s="4" t="s">
-        <v>325</v>
+      <c r="K891" s="5" t="s">
+        <v>610</v>
       </c>
       <c r="O891" s="2"/>
     </row>
     <row r="892" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C892" s="5">
-        <v>5</v>
-      </c>
-      <c r="D892" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E892" s="4">
-        <v>2018</v>
-      </c>
-      <c r="F892" s="4"/>
+        <v>7</v>
+      </c>
+      <c r="D892" s="27" t="s">
+        <v>603</v>
+      </c>
+      <c r="E892" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F892" s="18"/>
       <c r="G892" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H892" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I892" s="5" t="s">
-        <v>1611</v>
+      <c r="I892" s="4" t="s">
+        <v>1613</v>
       </c>
       <c r="J892" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K892" s="4" t="s">
-        <v>191</v>
+        <v>579</v>
       </c>
       <c r="O892" s="2"/>
     </row>
     <row r="893" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C893" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D893" s="27" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E893" s="5" t="s">
         <v>607</v>
@@ -30276,7 +30301,7 @@
         <v>845</v>
       </c>
       <c r="I893" s="5" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="J893" s="5" t="s">
         <v>1043</v>
@@ -30288,124 +30313,119 @@
     </row>
     <row r="894" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C894" s="5">
-        <v>7</v>
-      </c>
-      <c r="D894" s="27" t="s">
-        <v>603</v>
-      </c>
-      <c r="E894" s="5">
+        <v>9</v>
+      </c>
+      <c r="D894" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E894" s="4">
         <v>2017</v>
       </c>
-      <c r="F894" s="18"/>
+      <c r="F894" s="4"/>
       <c r="G894" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H894" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I894" s="4" t="s">
-        <v>1613</v>
+        <v>847</v>
+      </c>
+      <c r="I894" s="5" t="s">
+        <v>1529</v>
       </c>
       <c r="J894" s="5" t="s">
         <v>1043</v>
       </c>
       <c r="K894" s="4" t="s">
-        <v>579</v>
+        <v>325</v>
       </c>
       <c r="O894" s="2"/>
     </row>
     <row r="895" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C895" s="5">
-        <v>8</v>
-      </c>
-      <c r="D895" s="27" t="s">
-        <v>706</v>
-      </c>
-      <c r="E895" s="5" t="s">
-        <v>607</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D895" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E895" s="4">
+        <v>2017</v>
+      </c>
+      <c r="F895" s="4"/>
       <c r="G895" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H895" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I895" s="5" t="s">
-        <v>1614</v>
+        <v>1303</v>
       </c>
       <c r="J895" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="K895" s="5" t="s">
-        <v>610</v>
+      <c r="K895" s="4" t="s">
+        <v>325</v>
       </c>
       <c r="O895" s="2"/>
     </row>
     <row r="896" spans="3:19" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C896" s="5">
-        <v>9</v>
-      </c>
-      <c r="D896" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="E896" s="4">
-        <v>2017</v>
-      </c>
-      <c r="F896" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="D896" s="27" t="s">
+        <v>683</v>
+      </c>
+      <c r="E896" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G896" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H896" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I896" s="5" t="s">
-        <v>1529</v>
-      </c>
-      <c r="J896" s="5" t="s">
-        <v>1043</v>
-      </c>
-      <c r="K896" s="4" t="s">
-        <v>325</v>
+        <v>175</v>
+      </c>
+      <c r="K896" s="5" t="s">
+        <v>610</v>
       </c>
       <c r="O896" s="2"/>
     </row>
     <row r="897" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C897" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D897" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="E897" s="4">
+        <v>599</v>
+      </c>
+      <c r="E897" s="5">
         <v>2017</v>
       </c>
       <c r="F897" s="4"/>
       <c r="G897" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H897" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I897" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="J897" s="5" t="s">
-        <v>1043</v>
-      </c>
+        <v>845</v>
+      </c>
+      <c r="I897" s="4" t="s">
+        <v>1615</v>
+      </c>
+      <c r="J897" s="4"/>
       <c r="K897" s="4" t="s">
-        <v>325</v>
+        <v>579</v>
       </c>
       <c r="O897" s="2"/>
     </row>
     <row r="898" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C898" s="5">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D898" s="27" t="s">
-        <v>683</v>
+        <v>904</v>
       </c>
       <c r="E898" s="5" t="s">
-        <v>607</v>
+        <v>654</v>
       </c>
       <c r="G898" s="4" t="s">
         <v>844</v>
@@ -30414,7 +30434,7 @@
         <v>845</v>
       </c>
       <c r="I898" s="5" t="s">
-        <v>175</v>
+        <v>1616</v>
       </c>
       <c r="K898" s="5" t="s">
         <v>610</v>
@@ -30423,39 +30443,37 @@
     </row>
     <row r="899" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C899" s="5">
-        <v>12</v>
-      </c>
-      <c r="D899" s="16" t="s">
-        <v>599</v>
-      </c>
-      <c r="E899" s="5">
-        <v>2017</v>
-      </c>
-      <c r="F899" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="D899" s="27" t="s">
+        <v>726</v>
+      </c>
+      <c r="E899" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G899" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H899" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I899" s="4" t="s">
-        <v>1615</v>
-      </c>
-      <c r="J899" s="4"/>
-      <c r="K899" s="4" t="s">
-        <v>579</v>
+      <c r="I899" s="5" t="s">
+        <v>1617</v>
+      </c>
+      <c r="K899" s="5" t="s">
+        <v>610</v>
       </c>
       <c r="O899" s="2"/>
     </row>
     <row r="900" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C900" s="5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D900" s="27" t="s">
-        <v>904</v>
+        <v>678</v>
       </c>
       <c r="E900" s="5" t="s">
-        <v>654</v>
+        <v>607</v>
       </c>
       <c r="G900" s="4" t="s">
         <v>844</v>
@@ -30464,7 +30482,7 @@
         <v>845</v>
       </c>
       <c r="I900" s="5" t="s">
-        <v>1616</v>
+        <v>470</v>
       </c>
       <c r="K900" s="5" t="s">
         <v>610</v>
@@ -30473,14 +30491,15 @@
     </row>
     <row r="901" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C901" s="5">
-        <v>14</v>
-      </c>
-      <c r="D901" s="27" t="s">
-        <v>726</v>
-      </c>
-      <c r="E901" s="5" t="s">
-        <v>607</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D901" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="E901" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F901" s="4"/>
       <c r="G901" s="4" t="s">
         <v>844</v>
       </c>
@@ -30488,83 +30507,84 @@
         <v>845</v>
       </c>
       <c r="I901" s="5" t="s">
-        <v>1617</v>
-      </c>
-      <c r="K901" s="5" t="s">
-        <v>610</v>
+        <v>1618</v>
+      </c>
+      <c r="K901" s="4" t="s">
+        <v>579</v>
       </c>
       <c r="O901" s="2"/>
     </row>
     <row r="902" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C902" s="5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D902" s="27" t="s">
-        <v>678</v>
-      </c>
-      <c r="E902" s="5" t="s">
-        <v>607</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="E902" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F902" s="10"/>
       <c r="G902" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H902" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I902" s="5" t="s">
-        <v>470</v>
-      </c>
-      <c r="K902" s="5" t="s">
-        <v>610</v>
+      <c r="I902" s="11" t="s">
+        <v>1183</v>
+      </c>
+      <c r="J902" s="11"/>
+      <c r="K902" s="4" t="s">
+        <v>579</v>
       </c>
       <c r="O902" s="2"/>
     </row>
     <row r="903" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C903" s="5">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D903" s="16" t="s">
-        <v>595</v>
+        <v>375</v>
       </c>
       <c r="E903" s="5">
         <v>2017</v>
       </c>
-      <c r="F903" s="4"/>
       <c r="G903" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H903" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I903" s="5" t="s">
-        <v>1618</v>
-      </c>
+        <v>847</v>
+      </c>
+      <c r="I903" s="4" t="s">
+        <v>1619</v>
+      </c>
+      <c r="J903" s="4"/>
       <c r="K903" s="4" t="s">
-        <v>579</v>
+        <v>325</v>
       </c>
       <c r="O903" s="2"/>
     </row>
     <row r="904" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C904" s="5">
-        <v>17</v>
-      </c>
-      <c r="D904" s="27" t="s">
-        <v>601</v>
+        <v>19</v>
+      </c>
+      <c r="D904" s="16" t="s">
+        <v>598</v>
       </c>
       <c r="E904" s="5">
         <v>2017</v>
       </c>
-      <c r="F904" s="10"/>
       <c r="G904" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H904" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I904" s="11" t="s">
-        <v>1183</v>
-      </c>
-      <c r="J904" s="11"/>
+      <c r="I904" s="6" t="s">
+        <v>1620</v>
+      </c>
+      <c r="J904" s="6"/>
       <c r="K904" s="4" t="s">
         <v>579</v>
       </c>
@@ -30572,38 +30592,36 @@
     </row>
     <row r="905" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C905" s="5">
-        <v>18</v>
-      </c>
-      <c r="D905" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="E905" s="5">
-        <v>2017</v>
+        <v>20</v>
+      </c>
+      <c r="D905" s="27" t="s">
+        <v>713</v>
+      </c>
+      <c r="E905" s="5" t="s">
+        <v>607</v>
       </c>
       <c r="G905" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H905" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I905" s="4" t="s">
-        <v>1619</v>
-      </c>
-      <c r="J905" s="4"/>
-      <c r="K905" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="O905" s="2"/>
+        <v>845</v>
+      </c>
+      <c r="I905" s="5" t="s">
+        <v>1534</v>
+      </c>
+      <c r="K905" s="5" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="906" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C906" s="5">
-        <v>19</v>
-      </c>
-      <c r="D906" s="16" t="s">
-        <v>598</v>
-      </c>
-      <c r="E906" s="5">
-        <v>2017</v>
+        <v>21</v>
+      </c>
+      <c r="D906" s="27" t="s">
+        <v>672</v>
+      </c>
+      <c r="E906" s="5" t="s">
+        <v>607</v>
       </c>
       <c r="G906" s="4" t="s">
         <v>844</v>
@@ -30611,21 +30629,19 @@
       <c r="H906" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I906" s="6" t="s">
-        <v>1620</v>
-      </c>
-      <c r="J906" s="6"/>
-      <c r="K906" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="O906" s="2"/>
+      <c r="I906" s="5" t="s">
+        <v>1621</v>
+      </c>
+      <c r="K906" s="5" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="907" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C907" s="5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D907" s="27" t="s">
-        <v>713</v>
+        <v>660</v>
       </c>
       <c r="E907" s="5" t="s">
         <v>607</v>
@@ -30637,7 +30653,7 @@
         <v>845</v>
       </c>
       <c r="I907" s="5" t="s">
-        <v>1534</v>
+        <v>1622</v>
       </c>
       <c r="K907" s="5" t="s">
         <v>610</v>
@@ -30645,13 +30661,13 @@
     </row>
     <row r="908" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C908" s="5">
-        <v>21</v>
-      </c>
-      <c r="D908" s="27" t="s">
-        <v>672</v>
-      </c>
-      <c r="E908" s="5" t="s">
-        <v>607</v>
+        <v>23</v>
+      </c>
+      <c r="D908" s="16" t="s">
+        <v>600</v>
+      </c>
+      <c r="E908" s="5">
+        <v>2017</v>
       </c>
       <c r="G908" s="4" t="s">
         <v>844</v>
@@ -30659,19 +30675,20 @@
       <c r="H908" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I908" s="5" t="s">
-        <v>1621</v>
-      </c>
-      <c r="K908" s="5" t="s">
-        <v>610</v>
+      <c r="I908" s="4" t="s">
+        <v>1623</v>
+      </c>
+      <c r="J908" s="4"/>
+      <c r="K908" s="4" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="909" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C909" s="5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D909" s="27" t="s">
-        <v>660</v>
+        <v>689</v>
       </c>
       <c r="E909" s="5" t="s">
         <v>607</v>
@@ -30683,7 +30700,7 @@
         <v>845</v>
       </c>
       <c r="I909" s="5" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="K909" s="5" t="s">
         <v>610</v>
@@ -30691,13 +30708,13 @@
     </row>
     <row r="910" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C910" s="5">
-        <v>23</v>
-      </c>
-      <c r="D910" s="16" t="s">
-        <v>600</v>
-      </c>
-      <c r="E910" s="5">
-        <v>2017</v>
+        <v>25</v>
+      </c>
+      <c r="D910" s="27" t="s">
+        <v>663</v>
+      </c>
+      <c r="E910" s="5" t="s">
+        <v>607</v>
       </c>
       <c r="G910" s="4" t="s">
         <v>844</v>
@@ -30705,24 +30722,24 @@
       <c r="H910" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I910" s="4" t="s">
-        <v>1623</v>
-      </c>
-      <c r="J910" s="4"/>
-      <c r="K910" s="4" t="s">
-        <v>579</v>
+      <c r="I910" s="5" t="s">
+        <v>1625</v>
+      </c>
+      <c r="K910" s="5" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="911" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C911" s="5">
-        <v>24</v>
-      </c>
-      <c r="D911" s="27" t="s">
-        <v>689</v>
-      </c>
-      <c r="E911" s="5" t="s">
-        <v>607</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D911" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="E911" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F911" s="4"/>
       <c r="G911" s="4" t="s">
         <v>844</v>
       </c>
@@ -30730,18 +30747,18 @@
         <v>845</v>
       </c>
       <c r="I911" s="5" t="s">
-        <v>1624</v>
-      </c>
-      <c r="K911" s="5" t="s">
-        <v>610</v>
+        <v>1626</v>
+      </c>
+      <c r="K911" s="4" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="912" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C912" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D912" s="27" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="E912" s="5" t="s">
         <v>607</v>
@@ -30753,7 +30770,7 @@
         <v>845</v>
       </c>
       <c r="I912" s="5" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="K912" s="5" t="s">
         <v>610</v>
@@ -30761,15 +30778,14 @@
     </row>
     <row r="913" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C913" s="5">
-        <v>26</v>
-      </c>
-      <c r="D913" s="16" t="s">
-        <v>593</v>
-      </c>
-      <c r="E913" s="5">
-        <v>2017</v>
-      </c>
-      <c r="F913" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="D913" s="27" t="s">
+        <v>669</v>
+      </c>
+      <c r="E913" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G913" s="4" t="s">
         <v>844</v>
       </c>
@@ -30777,18 +30793,18 @@
         <v>845</v>
       </c>
       <c r="I913" s="5" t="s">
-        <v>1626</v>
-      </c>
-      <c r="K913" s="4" t="s">
-        <v>579</v>
+        <v>1628</v>
+      </c>
+      <c r="K913" s="5" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="914" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C914" s="5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D914" s="27" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="E914" s="5" t="s">
         <v>607</v>
@@ -30800,7 +30816,7 @@
         <v>845</v>
       </c>
       <c r="I914" s="5" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="K914" s="5" t="s">
         <v>610</v>
@@ -30808,10 +30824,10 @@
     </row>
     <row r="915" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C915" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D915" s="27" t="s">
-        <v>669</v>
+        <v>729</v>
       </c>
       <c r="E915" s="5" t="s">
         <v>607</v>
@@ -30823,7 +30839,7 @@
         <v>845</v>
       </c>
       <c r="I915" s="5" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K915" s="5" t="s">
         <v>610</v>
@@ -30831,14 +30847,15 @@
     </row>
     <row r="916" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C916" s="5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D916" s="27" t="s">
-        <v>666</v>
-      </c>
-      <c r="E916" s="5" t="s">
-        <v>607</v>
-      </c>
+        <v>604</v>
+      </c>
+      <c r="E916" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F916" s="18"/>
       <c r="G916" s="4" t="s">
         <v>844</v>
       </c>
@@ -30846,46 +30863,47 @@
         <v>845</v>
       </c>
       <c r="I916" s="5" t="s">
-        <v>1629</v>
-      </c>
-      <c r="K916" s="5" t="s">
-        <v>610</v>
+        <v>1631</v>
+      </c>
+      <c r="K916" s="4" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="917" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C917" s="5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D917" s="27" t="s">
-        <v>729</v>
-      </c>
-      <c r="E917" s="5" t="s">
-        <v>607</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="E917" s="5">
+        <v>2017</v>
+      </c>
+      <c r="F917" s="18"/>
       <c r="G917" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H917" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I917" s="5" t="s">
-        <v>1630</v>
-      </c>
-      <c r="K917" s="5" t="s">
-        <v>610</v>
+      <c r="I917" s="4" t="s">
+        <v>1632</v>
+      </c>
+      <c r="J917" s="4"/>
+      <c r="K917" s="4" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="918" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C918" s="5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D918" s="27" t="s">
-        <v>604</v>
-      </c>
-      <c r="E918" s="5">
-        <v>2017</v>
-      </c>
-      <c r="F918" s="18"/>
+        <v>716</v>
+      </c>
+      <c r="E918" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="G918" s="4" t="s">
         <v>844</v>
       </c>
@@ -30893,43 +30911,41 @@
         <v>845</v>
       </c>
       <c r="I918" s="5" t="s">
-        <v>1631</v>
-      </c>
-      <c r="K918" s="4" t="s">
-        <v>579</v>
+        <v>1094</v>
+      </c>
+      <c r="K918" s="5" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="919" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C919" s="5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D919" s="27" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="E919" s="5">
         <v>2017</v>
       </c>
-      <c r="F919" s="18"/>
       <c r="G919" s="4" t="s">
         <v>844</v>
       </c>
       <c r="H919" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="I919" s="4" t="s">
-        <v>1632</v>
-      </c>
-      <c r="J919" s="4"/>
+      <c r="I919" s="5" t="s">
+        <v>1059</v>
+      </c>
       <c r="K919" s="4" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="920" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C920" s="5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D920" s="27" t="s">
-        <v>716</v>
+        <v>686</v>
       </c>
       <c r="E920" s="5" t="s">
         <v>607</v>
@@ -30941,7 +30957,7 @@
         <v>845</v>
       </c>
       <c r="I920" s="5" t="s">
-        <v>1094</v>
+        <v>1059</v>
       </c>
       <c r="K920" s="5" t="s">
         <v>610</v>
@@ -30949,13 +30965,13 @@
     </row>
     <row r="921" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C921" s="5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D921" s="27" t="s">
-        <v>605</v>
-      </c>
-      <c r="E921" s="5">
-        <v>2017</v>
+        <v>692</v>
+      </c>
+      <c r="E921" s="5" t="s">
+        <v>607</v>
       </c>
       <c r="G921" s="4" t="s">
         <v>844</v>
@@ -30966,16 +30982,16 @@
       <c r="I921" s="5" t="s">
         <v>1059</v>
       </c>
-      <c r="K921" s="4" t="s">
-        <v>579</v>
+      <c r="K921" s="5" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="922" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C922" s="5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D922" s="27" t="s">
-        <v>686</v>
+        <v>722</v>
       </c>
       <c r="E922" s="5" t="s">
         <v>607</v>
@@ -30994,200 +31010,239 @@
       </c>
     </row>
     <row r="923" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C923" s="5">
-        <v>36</v>
-      </c>
-      <c r="D923" s="27" t="s">
-        <v>692</v>
-      </c>
-      <c r="E923" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G923" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H923" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I923" s="5" t="s">
-        <v>1059</v>
-      </c>
-      <c r="K923" s="5" t="s">
-        <v>610</v>
-      </c>
+      <c r="G923" s="4"/>
+      <c r="H923" s="4"/>
     </row>
     <row r="924" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C924" s="5">
-        <v>37</v>
-      </c>
-      <c r="D924" s="27" t="s">
-        <v>722</v>
-      </c>
-      <c r="E924" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="G924" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H924" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I924" s="5" t="s">
-        <v>1059</v>
-      </c>
-      <c r="K924" s="5" t="s">
-        <v>610</v>
+      <c r="D924" s="24" t="s">
+        <v>905</v>
+      </c>
+      <c r="E924" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="F924" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G924" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="H924" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="I924" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="J924" s="10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="925" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D925" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E925" s="7"/>
+      <c r="F925" s="4"/>
       <c r="G925" s="4"/>
       <c r="H925" s="4"/>
+      <c r="I925" s="10"/>
     </row>
     <row r="926" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D926" s="24" t="s">
-        <v>905</v>
-      </c>
-      <c r="E926" s="10" t="s">
-        <v>861</v>
-      </c>
-      <c r="F926" s="10" t="s">
+      <c r="D926" s="27" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="927" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C927" s="18">
+        <v>1</v>
+      </c>
+      <c r="D927" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="E927" s="10">
+        <v>2014</v>
+      </c>
+      <c r="F927" s="10">
+        <v>1</v>
+      </c>
+      <c r="G927" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="H927" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="I927" s="18" t="s">
+        <v>1633</v>
+      </c>
+      <c r="J927" s="5">
+        <v>1</v>
+      </c>
+      <c r="K927" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="928" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C928" s="18">
+        <v>2</v>
+      </c>
+      <c r="D928" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="E928" s="10">
+        <v>2014</v>
+      </c>
+      <c r="F928" s="10">
+        <v>1</v>
+      </c>
+      <c r="G928" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="H928" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="I928" s="18" t="s">
+        <v>1137</v>
+      </c>
+      <c r="J928" s="5">
+        <v>2</v>
+      </c>
+      <c r="K928" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="929" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C929" s="18">
         <v>3</v>
       </c>
-      <c r="G926" s="10" t="s">
-        <v>842</v>
-      </c>
-      <c r="H926" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="I926" s="10" t="s">
-        <v>862</v>
-      </c>
-      <c r="J926" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="927" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D927" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="E927" s="7"/>
-      <c r="F927" s="4"/>
-      <c r="G927" s="4"/>
-      <c r="H927" s="4"/>
-      <c r="I927" s="10"/>
-    </row>
-    <row r="928" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D928" s="24"/>
-      <c r="E928" s="7"/>
-      <c r="F928" s="4"/>
-      <c r="G928" s="4"/>
-      <c r="H928" s="4"/>
-      <c r="I928" s="10"/>
-    </row>
-    <row r="929" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D929" s="27" t="s">
-        <v>896</v>
+      <c r="D929" s="37" t="s">
+        <v>210</v>
+      </c>
+      <c r="E929" s="10">
+        <v>2014</v>
+      </c>
+      <c r="F929" s="10">
+        <v>2</v>
+      </c>
+      <c r="G929" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="H929" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="I929" s="18" t="s">
+        <v>1634</v>
+      </c>
+      <c r="J929" s="5">
+        <v>2</v>
+      </c>
+      <c r="K929" s="10" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="930" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C930" s="18">
+      <c r="C930" s="5">
+        <v>4</v>
+      </c>
+      <c r="D930" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="E930" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F930" s="4">
         <v>1</v>
       </c>
-      <c r="D930" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="E930" s="10">
+      <c r="G930" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H930" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I930" s="5" t="s">
+        <v>1635</v>
+      </c>
+      <c r="J930" s="5">
+        <v>2</v>
+      </c>
+      <c r="K930" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="931" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C931" s="5">
+        <v>5</v>
+      </c>
+      <c r="D931" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="E931" s="4">
         <v>2014</v>
       </c>
-      <c r="F930" s="10">
-        <v>1</v>
-      </c>
-      <c r="G930" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H930" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I930" s="18" t="s">
-        <v>1633</v>
-      </c>
-      <c r="J930" s="5">
-        <v>1</v>
-      </c>
-      <c r="K930" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="931" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C931" s="18">
+      <c r="F931" s="4">
         <v>2</v>
       </c>
-      <c r="D931" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="E931" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F931" s="10">
-        <v>1</v>
-      </c>
-      <c r="G931" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H931" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I931" s="18" t="s">
-        <v>1137</v>
+      <c r="G931" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H931" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I931" s="5" t="s">
+        <v>1636</v>
       </c>
       <c r="J931" s="5">
         <v>2</v>
       </c>
-      <c r="K931" s="10" t="s">
+      <c r="K931" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="M931" s="2"/>
+      <c r="N931" s="2"/>
+      <c r="O931" s="2"/>
+    </row>
+    <row r="932" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C932" s="5">
+        <v>6</v>
+      </c>
+      <c r="D932" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="E932" s="5">
+        <v>2014</v>
+      </c>
+      <c r="F932" s="5">
+        <v>2</v>
+      </c>
+      <c r="G932" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="H932" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="I932" s="5" t="s">
+        <v>1637</v>
+      </c>
+      <c r="J932" s="5">
+        <v>3</v>
+      </c>
+      <c r="K932" s="4" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="932" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C932" s="18">
-        <v>3</v>
-      </c>
-      <c r="D932" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="E932" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F932" s="10">
-        <v>2</v>
-      </c>
-      <c r="G932" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H932" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I932" s="18" t="s">
-        <v>1634</v>
-      </c>
-      <c r="J932" s="5">
-        <v>2</v>
-      </c>
-      <c r="K932" s="10" t="s">
-        <v>194</v>
-      </c>
+      <c r="M932" s="2"/>
+      <c r="N932" s="2"/>
+      <c r="O932" s="2"/>
     </row>
     <row r="933" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C933" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D933" s="16" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="E933" s="4">
         <v>2014</v>
       </c>
       <c r="F933" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G933" s="4" t="s">
         <v>844</v>
@@ -31196,21 +31251,24 @@
         <v>845</v>
       </c>
       <c r="I933" s="5" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="J933" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K933" s="4" t="s">
         <v>791</v>
       </c>
+      <c r="M933" s="2"/>
+      <c r="N933" s="2"/>
+      <c r="O933" s="2"/>
     </row>
     <row r="934" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C934" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D934" s="16" t="s">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="E934" s="4">
         <v>2014</v>
@@ -31225,10 +31283,10 @@
         <v>845</v>
       </c>
       <c r="I934" s="5" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="J934" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K934" s="4" t="s">
         <v>791</v>
@@ -31239,31 +31297,31 @@
     </row>
     <row r="935" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C935" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D935" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="E935" s="5">
+        <v>792</v>
+      </c>
+      <c r="E935" s="4">
         <v>2014</v>
       </c>
-      <c r="F935" s="5">
+      <c r="F935" s="4">
         <v>2</v>
       </c>
       <c r="G935" s="4" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H935" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="I935" s="5" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="J935" s="5">
         <v>3</v>
       </c>
       <c r="K935" s="4" t="s">
-        <v>194</v>
+        <v>791</v>
       </c>
       <c r="M935" s="2"/>
       <c r="N935" s="2"/>
@@ -31271,386 +31329,264 @@
     </row>
     <row r="936" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C936" s="5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D936" s="16" t="s">
-        <v>789</v>
+        <v>413</v>
       </c>
       <c r="E936" s="4">
         <v>2014</v>
       </c>
-      <c r="F936" s="4">
-        <v>2</v>
-      </c>
-      <c r="G936" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H936" s="4" t="s">
+      <c r="F936" s="4"/>
+      <c r="G936" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="H936" s="5" t="s">
         <v>845</v>
       </c>
       <c r="I936" s="5" t="s">
-        <v>1638</v>
-      </c>
-      <c r="J936" s="5">
-        <v>3</v>
+        <v>1641</v>
+      </c>
+      <c r="J936" s="5" t="s">
+        <v>1019</v>
       </c>
       <c r="K936" s="4" t="s">
-        <v>791</v>
+        <v>412</v>
       </c>
       <c r="M936" s="2"/>
       <c r="N936" s="2"/>
       <c r="O936" s="2"/>
     </row>
     <row r="937" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C937" s="5">
-        <v>8</v>
-      </c>
-      <c r="D937" s="16" t="s">
-        <v>810</v>
-      </c>
-      <c r="E937" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F937" s="4">
-        <v>2</v>
-      </c>
-      <c r="G937" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H937" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I937" s="5" t="s">
-        <v>1639</v>
-      </c>
-      <c r="J937" s="5">
-        <v>3</v>
-      </c>
-      <c r="K937" s="4" t="s">
-        <v>791</v>
-      </c>
+      <c r="G937" s="4"/>
+      <c r="H937" s="4"/>
       <c r="M937" s="2"/>
       <c r="N937" s="2"/>
       <c r="O937" s="2"/>
     </row>
     <row r="938" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C938" s="5">
-        <v>9</v>
-      </c>
-      <c r="D938" s="16" t="s">
-        <v>792</v>
-      </c>
-      <c r="E938" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F938" s="4">
-        <v>2</v>
-      </c>
-      <c r="G938" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H938" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I938" s="5" t="s">
-        <v>1640</v>
-      </c>
-      <c r="J938" s="5">
-        <v>3</v>
-      </c>
-      <c r="K938" s="4" t="s">
-        <v>791</v>
-      </c>
+      <c r="D938" s="16"/>
+      <c r="E938" s="4"/>
+      <c r="F938" s="4"/>
+      <c r="G938" s="4"/>
+      <c r="H938" s="4"/>
+      <c r="I938" s="4"/>
+      <c r="J938" s="4"/>
+      <c r="K938" s="4"/>
       <c r="M938" s="2"/>
       <c r="N938" s="2"/>
       <c r="O938" s="2"/>
     </row>
     <row r="939" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C939" s="5">
-        <v>10</v>
-      </c>
-      <c r="D939" s="16" t="s">
-        <v>413</v>
-      </c>
-      <c r="E939" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F939" s="4"/>
-      <c r="G939" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="H939" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="I939" s="5" t="s">
-        <v>1641</v>
-      </c>
-      <c r="J939" s="5" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K939" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="M939" s="2"/>
-      <c r="N939" s="2"/>
-      <c r="O939" s="2"/>
-    </row>
-    <row r="940" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G940" s="4"/>
-      <c r="H940" s="4"/>
-      <c r="M940" s="2"/>
-      <c r="N940" s="2"/>
-      <c r="O940" s="2"/>
+      <c r="D939" s="24"/>
+      <c r="G939" s="4"/>
+      <c r="H939" s="4"/>
+      <c r="J939" s="6"/>
     </row>
     <row r="941" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D941" s="16"/>
-      <c r="E941" s="4"/>
-      <c r="F941" s="4"/>
-      <c r="G941" s="4"/>
-      <c r="H941" s="4"/>
-      <c r="I941" s="4"/>
-      <c r="J941" s="4"/>
-      <c r="K941" s="4"/>
-      <c r="M941" s="2"/>
-      <c r="N941" s="2"/>
-      <c r="O941" s="2"/>
+      <c r="D941" s="24" t="s">
+        <v>905</v>
+      </c>
+      <c r="E941" s="10" t="s">
+        <v>861</v>
+      </c>
+      <c r="F941" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G941" s="10" t="s">
+        <v>842</v>
+      </c>
+      <c r="H941" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="I941" s="10" t="s">
+        <v>862</v>
+      </c>
+      <c r="J941" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="K941" s="10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="942" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D942" s="24" t="s">
+        <v>891</v>
+      </c>
+      <c r="E942" s="7"/>
+      <c r="F942" s="4"/>
+      <c r="G942" s="4"/>
+      <c r="H942" s="4"/>
+      <c r="I942" s="10"/>
+      <c r="J942" s="10"/>
+      <c r="K942" s="10"/>
+    </row>
+    <row r="943" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D943" s="27" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="944" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D944" s="24" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="945" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C945" s="5">
+        <v>1</v>
+      </c>
+      <c r="D945" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="E945" s="11">
+        <v>2015</v>
+      </c>
+      <c r="F945" s="11">
+        <v>3</v>
+      </c>
+      <c r="G945" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="H945" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="I945" s="11" t="s">
         <v>1642</v>
       </c>
-      <c r="E942" s="10" t="s">
-        <v>861</v>
-      </c>
-      <c r="F942" s="10" t="s">
+      <c r="J945" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K945" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="946" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C946" s="5">
+        <v>2</v>
+      </c>
+      <c r="D946" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="E946" s="32">
+        <v>2015</v>
+      </c>
+      <c r="F946" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="G946" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="H946" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="I946" s="32" t="s">
+        <v>1643</v>
+      </c>
+      <c r="J946" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K946" s="11" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="947" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C947" s="5">
         <v>3</v>
       </c>
-      <c r="G942" s="10" t="s">
-        <v>842</v>
-      </c>
-      <c r="H942" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="I942" s="10" t="s">
-        <v>862</v>
-      </c>
-      <c r="J942" s="10"/>
-      <c r="K942" s="10" t="s">
+      <c r="D947" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="E947" s="11">
+        <v>2015</v>
+      </c>
+      <c r="F947" s="11">
+        <v>3</v>
+      </c>
+      <c r="G947" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="H947" s="11" t="s">
+        <v>847</v>
+      </c>
+      <c r="I947" s="11" t="s">
+        <v>1644</v>
+      </c>
+      <c r="J947" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K947" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="948" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D948" s="27" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="949" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C949" s="18">
         <v>1</v>
       </c>
-      <c r="M942" s="2"/>
-      <c r="N942" s="2"/>
-      <c r="O942" s="2"/>
-    </row>
-    <row r="943" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D943" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="E943" s="7"/>
-      <c r="F943" s="4"/>
-      <c r="G943" s="4"/>
-      <c r="H943" s="4"/>
-      <c r="I943" s="10"/>
-      <c r="J943" s="10"/>
-      <c r="K943" s="10"/>
-      <c r="M943" s="2"/>
-      <c r="N943" s="2"/>
-      <c r="O943" s="2"/>
-    </row>
-    <row r="944" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D944" s="27" t="s">
-        <v>896</v>
-      </c>
-      <c r="M944" s="2"/>
-      <c r="N944" s="2"/>
-      <c r="O944" s="2"/>
-    </row>
-    <row r="945" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C945" s="18">
-        <v>1</v>
-      </c>
-      <c r="D945" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="E945" s="10">
+      <c r="D949" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="E949" s="10">
         <v>2014</v>
       </c>
-      <c r="F945" s="10">
-        <v>1</v>
-      </c>
-      <c r="G945" s="10" t="s">
+      <c r="F949" s="10">
+        <v>2</v>
+      </c>
+      <c r="G949" s="10" t="s">
         <v>846</v>
       </c>
-      <c r="H945" s="10" t="s">
+      <c r="H949" s="10" t="s">
         <v>847</v>
       </c>
-      <c r="I945" s="18" t="s">
-        <v>1633</v>
-      </c>
-      <c r="J945" s="10"/>
-      <c r="K945" s="10" t="s">
+      <c r="I949" s="10" t="s">
+        <v>1645</v>
+      </c>
+      <c r="J949" s="10">
+        <v>2</v>
+      </c>
+      <c r="K949" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="950" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C950" s="18">
+        <v>2</v>
+      </c>
+      <c r="D950" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E950" s="10">
+        <v>2014</v>
+      </c>
+      <c r="F950" s="10">
+        <v>2</v>
+      </c>
+      <c r="G950" s="10" t="s">
+        <v>846</v>
+      </c>
+      <c r="H950" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="I950" s="10" t="s">
+        <v>1646</v>
+      </c>
+      <c r="J950" s="10">
+        <v>3</v>
+      </c>
+      <c r="K950" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="M945" s="2"/>
-      <c r="N945" s="2"/>
-      <c r="O945" s="2"/>
-    </row>
-    <row r="946" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C946" s="18">
-        <v>2</v>
-      </c>
-      <c r="D946" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="E946" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F946" s="10">
-        <v>1</v>
-      </c>
-      <c r="G946" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H946" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I946" s="18" t="s">
-        <v>1137</v>
-      </c>
-      <c r="J946" s="10"/>
-      <c r="K946" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="M946" s="2"/>
-      <c r="N946" s="2"/>
-      <c r="O946" s="2"/>
-    </row>
-    <row r="947" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C947" s="18">
+    </row>
+    <row r="951" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C951" s="18">
         <v>3</v>
       </c>
-      <c r="D947" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="E947" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F947" s="10">
-        <v>2</v>
-      </c>
-      <c r="G947" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H947" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I947" s="18" t="s">
-        <v>1634</v>
-      </c>
-      <c r="J947" s="10"/>
-      <c r="K947" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="M947" s="2"/>
-      <c r="N947" s="2"/>
-      <c r="O947" s="2"/>
-    </row>
-    <row r="948" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C948" s="5">
-        <v>4</v>
-      </c>
-      <c r="D948" s="16" t="s">
-        <v>797</v>
-      </c>
-      <c r="E948" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F948" s="4">
-        <v>1</v>
-      </c>
-      <c r="G948" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H948" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I948" s="5" t="s">
-        <v>1635</v>
-      </c>
-      <c r="J948" s="4"/>
-      <c r="K948" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="M948" s="2"/>
-      <c r="N948" s="2"/>
-      <c r="O948" s="2"/>
-    </row>
-    <row r="949" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C949" s="5">
-        <v>5</v>
-      </c>
-      <c r="D949" s="16" t="s">
-        <v>804</v>
-      </c>
-      <c r="E949" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F949" s="4">
-        <v>2</v>
-      </c>
-      <c r="G949" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H949" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I949" s="5" t="s">
-        <v>1636</v>
-      </c>
-      <c r="J949" s="4"/>
-      <c r="K949" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="M949" s="2"/>
-      <c r="N949" s="2"/>
-      <c r="O949" s="2"/>
-    </row>
-    <row r="950" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C950" s="5">
-        <v>6</v>
-      </c>
-      <c r="D950" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="E950" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F950" s="5">
-        <v>2</v>
-      </c>
-      <c r="G950" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H950" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I950" s="5" t="s">
-        <v>1637</v>
-      </c>
-      <c r="J950" s="6"/>
-      <c r="K950" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="M950" s="2"/>
-      <c r="N950" s="2"/>
-      <c r="O950" s="2"/>
-    </row>
-    <row r="951" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C951" s="5">
-        <v>7</v>
-      </c>
       <c r="D951" s="16" t="s">
-        <v>789</v>
+        <v>257</v>
       </c>
       <c r="E951" s="4">
         <v>2014</v>
@@ -31659,25 +31595,27 @@
         <v>2</v>
       </c>
       <c r="G951" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H951" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I951" s="5" t="s">
-        <v>1638</v>
-      </c>
-      <c r="J951" s="4"/>
+        <v>1647</v>
+      </c>
+      <c r="J951" s="10">
+        <v>3</v>
+      </c>
       <c r="K951" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="952" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C952" s="5">
-        <v>8</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="952" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C952" s="18">
+        <v>4</v>
       </c>
       <c r="D952" s="16" t="s">
-        <v>810</v>
+        <v>248</v>
       </c>
       <c r="E952" s="4">
         <v>2014</v>
@@ -31686,24 +31624,27 @@
         <v>2</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H952" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I952" s="5" t="s">
-        <v>1639</v>
+        <v>847</v>
+      </c>
+      <c r="I952" s="4" t="s">
+        <v>1648</v>
+      </c>
+      <c r="J952" s="10">
+        <v>3</v>
       </c>
       <c r="K952" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="953" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C953" s="5">
-        <v>9</v>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="953" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C953" s="18">
+        <v>5</v>
       </c>
       <c r="D953" s="16" t="s">
-        <v>792</v>
+        <v>230</v>
       </c>
       <c r="E953" s="4">
         <v>2014</v>
@@ -31712,1376 +31653,624 @@
         <v>2</v>
       </c>
       <c r="G953" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="H953" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I953" s="5" t="s">
-        <v>1640</v>
-      </c>
-      <c r="J953" s="6"/>
-      <c r="K953" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="954" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C954" s="5">
-        <v>10</v>
+        <v>847</v>
+      </c>
+      <c r="I953" s="4" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J953" s="10">
+        <v>3</v>
+      </c>
+      <c r="K953" s="10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="954" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C954" s="18">
+        <v>6</v>
       </c>
       <c r="D954" s="16" t="s">
-        <v>413</v>
+        <v>834</v>
       </c>
       <c r="E954" s="4">
         <v>2014</v>
       </c>
-      <c r="F954" s="4"/>
-      <c r="G954" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="H954" s="5" t="s">
+      <c r="F954" s="4">
+        <v>3</v>
+      </c>
+      <c r="G954" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H954" s="4" t="s">
         <v>845</v>
       </c>
       <c r="I954" s="5" t="s">
-        <v>1641</v>
-      </c>
-      <c r="J954" s="4"/>
+        <v>1650</v>
+      </c>
+      <c r="J954" s="10">
+        <v>3</v>
+      </c>
       <c r="K954" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="955" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D955" s="24"/>
-      <c r="G955" s="4"/>
-      <c r="H955" s="4"/>
-      <c r="J955" s="6"/>
-    </row>
-    <row r="957" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D957" s="24" t="s">
-        <v>905</v>
-      </c>
-      <c r="E957" s="10" t="s">
-        <v>861</v>
-      </c>
-      <c r="F957" s="10" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="955" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C955" s="18">
+        <v>7</v>
+      </c>
+      <c r="D955" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="E955" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F955" s="4">
         <v>3</v>
       </c>
-      <c r="G957" s="10" t="s">
-        <v>842</v>
-      </c>
-      <c r="H957" s="10" t="s">
-        <v>843</v>
-      </c>
-      <c r="I957" s="10" t="s">
-        <v>862</v>
-      </c>
-      <c r="J957" s="10" t="s">
+      <c r="G955" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="H955" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="I955" s="4" t="s">
+        <v>1651</v>
+      </c>
+      <c r="J955" s="10">
         <v>3</v>
       </c>
-      <c r="K957" s="10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="958" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D958" s="24" t="s">
-        <v>891</v>
-      </c>
-      <c r="E958" s="7"/>
-      <c r="F958" s="4"/>
-      <c r="G958" s="4"/>
-      <c r="H958" s="4"/>
-      <c r="I958" s="10"/>
-      <c r="J958" s="10"/>
-      <c r="K958" s="10"/>
-    </row>
-    <row r="959" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D959" s="27" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="960" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D960" s="24"/>
+      <c r="K955" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="956" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C956" s="18">
+        <v>8</v>
+      </c>
+      <c r="D956" s="16" t="s">
+        <v>828</v>
+      </c>
+      <c r="E956" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F956" s="4">
+        <v>3</v>
+      </c>
+      <c r="G956" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H956" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I956" s="5" t="s">
+        <v>1652</v>
+      </c>
+      <c r="J956" s="10">
+        <v>3</v>
+      </c>
+      <c r="K956" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="957" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C957" s="18">
+        <v>9</v>
+      </c>
+      <c r="D957" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E957" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F957" s="4">
+        <v>3</v>
+      </c>
+      <c r="G957" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="H957" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="I957" s="4" t="s">
+        <v>1653</v>
+      </c>
+      <c r="J957" s="10">
+        <v>3</v>
+      </c>
+      <c r="K957" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="958" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C958" s="18">
+        <v>10</v>
+      </c>
+      <c r="D958" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="E958" s="5">
+        <v>2014</v>
+      </c>
+      <c r="F958" s="5">
+        <v>3</v>
+      </c>
+      <c r="G958" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="H958" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="I958" s="4" t="s">
+        <v>1654</v>
+      </c>
+      <c r="J958" s="10">
+        <v>3</v>
+      </c>
+      <c r="K958" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="959" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C959" s="18">
+        <v>11</v>
+      </c>
+      <c r="D959" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="E959" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F959" s="4">
+        <v>3</v>
+      </c>
+      <c r="G959" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H959" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I959" s="5" t="s">
+        <v>1655</v>
+      </c>
+      <c r="J959" s="10">
+        <v>3</v>
+      </c>
+      <c r="K959" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="960" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C960" s="18">
+        <v>12</v>
+      </c>
+      <c r="D960" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="E960" s="4">
+        <v>2014</v>
+      </c>
+      <c r="F960" s="4">
+        <v>3</v>
+      </c>
+      <c r="G960" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H960" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I960" s="5" t="s">
+        <v>1656</v>
+      </c>
+      <c r="J960" s="10">
+        <v>3</v>
+      </c>
+      <c r="K960" s="4" t="s">
+        <v>791</v>
+      </c>
     </row>
     <row r="961" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C961" s="5">
-        <v>1</v>
+      <c r="C961" s="18">
+        <v>13</v>
       </c>
       <c r="D961" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="E961" s="11">
-        <v>2015</v>
-      </c>
-      <c r="F961" s="11">
-        <v>3</v>
-      </c>
-      <c r="G961" s="11" t="s">
-        <v>846</v>
-      </c>
-      <c r="H961" s="11" t="s">
-        <v>847</v>
-      </c>
-      <c r="I961" s="11" t="s">
-        <v>1643</v>
+        <v>840</v>
+      </c>
+      <c r="E961" s="4">
+        <v>2014</v>
+      </c>
+      <c r="G961" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H961" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I961" s="5" t="s">
+        <v>1657</v>
       </c>
       <c r="J961" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="K961" s="11" t="s">
-        <v>194</v>
+      <c r="K961" s="4" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="962" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C962" s="5">
-        <v>2</v>
+      <c r="C962" s="18">
+        <v>14</v>
       </c>
       <c r="D962" s="31" t="s">
-        <v>443</v>
-      </c>
-      <c r="E962" s="32">
-        <v>2015</v>
-      </c>
-      <c r="F962" s="32" t="s">
-        <v>430</v>
-      </c>
-      <c r="G962" s="11" t="s">
-        <v>844</v>
-      </c>
-      <c r="H962" s="11" t="s">
-        <v>845</v>
-      </c>
-      <c r="I962" s="32" t="s">
-        <v>1644</v>
+        <v>419</v>
+      </c>
+      <c r="E962" s="5">
+        <v>2014</v>
+      </c>
+      <c r="G962" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="H962" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="I962" s="4" t="s">
+        <v>1658</v>
       </c>
       <c r="J962" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="K962" s="11" t="s">
-        <v>433</v>
+      <c r="K962" s="4" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="963" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C963" s="5">
+      <c r="C963" s="18">
+        <v>15</v>
+      </c>
+      <c r="D963" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="E963" s="5">
+        <v>2014</v>
+      </c>
+      <c r="F963" s="5">
         <v>3</v>
       </c>
-      <c r="D963" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="E963" s="11">
-        <v>2015</v>
-      </c>
-      <c r="F963" s="11">
-        <v>3</v>
-      </c>
-      <c r="G963" s="11" t="s">
+      <c r="G963" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="H963" s="11" t="s">
+      <c r="H963" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="I963" s="11" t="s">
-        <v>1645</v>
+      <c r="I963" s="6" t="s">
+        <v>1659</v>
       </c>
       <c r="J963" s="11" t="s">
         <v>1019</v>
       </c>
-      <c r="K963" s="11" t="s">
+      <c r="K963" s="4" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="964" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D964" s="27" t="s">
-        <v>896</v>
+      <c r="C964" s="18">
+        <v>16</v>
+      </c>
+      <c r="D964" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="E964" s="5">
+        <v>2014</v>
+      </c>
+      <c r="G964" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="H964" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="I964" s="4" t="s">
+        <v>1660</v>
+      </c>
+      <c r="J964" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K964" s="4" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="965" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C965" s="18">
+        <v>17</v>
+      </c>
+      <c r="D965" s="31" t="s">
+        <v>841</v>
+      </c>
+      <c r="E965" s="4">
+        <v>2014</v>
+      </c>
+      <c r="G965" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H965" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I965" s="5" t="s">
+        <v>1661</v>
+      </c>
+      <c r="K965" s="4" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="966" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C966" s="18"/>
+      <c r="D966" s="16"/>
+      <c r="I966" s="4"/>
+      <c r="J966" s="4"/>
+      <c r="K966" s="4"/>
+    </row>
+    <row r="968" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D968" s="26" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="969" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D969" s="26" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="970" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D970" s="27" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="971" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C971" s="5">
         <v>1</v>
       </c>
-      <c r="D965" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="E965" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F965" s="10">
-        <v>2</v>
-      </c>
-      <c r="G965" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H965" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I965" s="10" t="s">
-        <v>1646</v>
-      </c>
-      <c r="J965" s="10">
-        <v>2</v>
-      </c>
-      <c r="K965" s="10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="966" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C966" s="18">
-        <v>2</v>
-      </c>
-      <c r="D966" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="E966" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F966" s="10">
-        <v>2</v>
-      </c>
-      <c r="G966" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H966" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I966" s="10" t="s">
-        <v>1647</v>
-      </c>
-      <c r="J966" s="10">
-        <v>3</v>
-      </c>
-      <c r="K966" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="967" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C967" s="18">
-        <v>3</v>
-      </c>
-      <c r="D967" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="E967" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F967" s="4">
-        <v>2</v>
-      </c>
-      <c r="G967" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H967" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I967" s="5" t="s">
-        <v>1648</v>
-      </c>
-      <c r="J967" s="10">
-        <v>3</v>
-      </c>
-      <c r="K967" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="968" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C968" s="18">
-        <v>4</v>
-      </c>
-      <c r="D968" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="E968" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F968" s="4">
-        <v>2</v>
-      </c>
-      <c r="G968" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H968" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I968" s="4" t="s">
-        <v>1649</v>
-      </c>
-      <c r="J968" s="10">
-        <v>3</v>
-      </c>
-      <c r="K968" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="969" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C969" s="18">
-        <v>5</v>
-      </c>
-      <c r="D969" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="E969" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F969" s="4">
-        <v>2</v>
-      </c>
-      <c r="G969" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H969" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I969" s="4" t="s">
-        <v>1650</v>
-      </c>
-      <c r="J969" s="10">
-        <v>3</v>
-      </c>
-      <c r="K969" s="10" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="970" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C970" s="18">
-        <v>6</v>
-      </c>
-      <c r="D970" s="16" t="s">
-        <v>834</v>
-      </c>
-      <c r="E970" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F970" s="4">
-        <v>3</v>
-      </c>
-      <c r="G970" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H970" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I970" s="5" t="s">
-        <v>1651</v>
-      </c>
-      <c r="J970" s="10">
-        <v>3</v>
-      </c>
-      <c r="K970" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="971" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C971" s="18">
-        <v>7</v>
-      </c>
       <c r="D971" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="E971" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F971" s="4">
-        <v>3</v>
-      </c>
+        <v>1013</v>
+      </c>
+      <c r="E971" s="4"/>
+      <c r="F971" s="4"/>
       <c r="G971" s="4" t="s">
         <v>846</v>
       </c>
       <c r="H971" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="I971" s="4" t="s">
-        <v>1652</v>
-      </c>
-      <c r="J971" s="10">
+      <c r="I971" s="1" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="972" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C972" s="5">
+        <v>2</v>
+      </c>
+      <c r="D972" s="27" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G972" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H972" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I972" s="5" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="973" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C973" s="5">
         <v>3</v>
       </c>
-      <c r="K971" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="972" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C972" s="18">
-        <v>8</v>
-      </c>
-      <c r="D972" s="16" t="s">
-        <v>828</v>
-      </c>
-      <c r="E972" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F972" s="4">
-        <v>3</v>
-      </c>
-      <c r="G972" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H972" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I972" s="5" t="s">
-        <v>1653</v>
-      </c>
-      <c r="J972" s="10">
-        <v>3</v>
-      </c>
-      <c r="K972" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="973" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C973" s="18">
-        <v>9</v>
-      </c>
       <c r="D973" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="E973" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F973" s="4">
-        <v>3</v>
-      </c>
+        <v>1015</v>
+      </c>
+      <c r="E973" s="4"/>
+      <c r="F973" s="4"/>
       <c r="G973" s="4" t="s">
         <v>846</v>
       </c>
       <c r="H973" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="I973" s="4" t="s">
-        <v>1654</v>
-      </c>
-      <c r="J973" s="10">
-        <v>3</v>
-      </c>
-      <c r="K973" s="4" t="s">
-        <v>194</v>
+      <c r="I973" s="5" t="s">
+        <v>1664</v>
       </c>
     </row>
     <row r="974" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C974" s="18">
-        <v>10</v>
+      <c r="C974" s="5">
+        <v>4</v>
       </c>
       <c r="D974" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="E974" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F974" s="5">
-        <v>3</v>
-      </c>
+        <v>1009</v>
+      </c>
+      <c r="E974" s="4"/>
+      <c r="F974" s="4"/>
       <c r="G974" s="4" t="s">
         <v>846</v>
       </c>
       <c r="H974" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="I974" s="4" t="s">
-        <v>1655</v>
-      </c>
-      <c r="J974" s="10">
+      <c r="I974" s="5" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="975" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D975" s="16"/>
+      <c r="E975" s="4"/>
+      <c r="F975" s="4"/>
+      <c r="G975" s="4"/>
+      <c r="H975" s="4"/>
+    </row>
+    <row r="976" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D976" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E976" s="2"/>
+      <c r="F976" s="2"/>
+      <c r="G976" s="2"/>
+      <c r="H976" s="2"/>
+      <c r="I976" s="1"/>
+      <c r="J976" s="1"/>
+      <c r="K976" s="1"/>
+    </row>
+    <row r="977" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C977" s="5">
+        <v>1</v>
+      </c>
+      <c r="D977" s="27" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G977" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H977" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I977" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="J977" s="4"/>
+      <c r="K977" s="4"/>
+    </row>
+    <row r="978" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C978" s="5">
+        <v>2</v>
+      </c>
+      <c r="D978" s="27" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G978" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H978" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I978" s="5" t="s">
+        <v>1667</v>
+      </c>
+      <c r="J978" s="1"/>
+      <c r="K978" s="1"/>
+    </row>
+    <row r="979" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C979" s="5">
         <v>3</v>
       </c>
-      <c r="K974" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="975" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C975" s="18">
-        <v>11</v>
-      </c>
-      <c r="D975" s="16" t="s">
-        <v>832</v>
-      </c>
-      <c r="E975" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F975" s="4">
-        <v>3</v>
-      </c>
-      <c r="G975" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H975" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I975" s="5" t="s">
-        <v>1656</v>
-      </c>
-      <c r="J975" s="10">
-        <v>3</v>
-      </c>
-      <c r="K975" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="976" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C976" s="18">
-        <v>12</v>
-      </c>
-      <c r="D976" s="16" t="s">
-        <v>837</v>
-      </c>
-      <c r="E976" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F976" s="4">
-        <v>3</v>
-      </c>
-      <c r="G976" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H976" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I976" s="5" t="s">
-        <v>1657</v>
-      </c>
-      <c r="J976" s="10">
-        <v>3</v>
-      </c>
-      <c r="K976" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="977" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C977" s="18">
-        <v>13</v>
-      </c>
-      <c r="D977" s="31" t="s">
-        <v>840</v>
-      </c>
-      <c r="E977" s="4">
-        <v>2014</v>
-      </c>
-      <c r="G977" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H977" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I977" s="5" t="s">
-        <v>1658</v>
-      </c>
-      <c r="J977" s="11" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K977" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="978" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C978" s="18">
-        <v>14</v>
-      </c>
-      <c r="D978" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="E978" s="5">
-        <v>2014</v>
-      </c>
-      <c r="G978" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="H978" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="I978" s="4" t="s">
-        <v>1659</v>
-      </c>
-      <c r="J978" s="11" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K978" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="979" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C979" s="18">
-        <v>15</v>
-      </c>
-      <c r="D979" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="E979" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F979" s="5">
-        <v>3</v>
+      <c r="D979" s="27" t="s">
+        <v>1668</v>
       </c>
       <c r="G979" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="H979" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="I979" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="J979" s="1"/>
+      <c r="K979" s="1"/>
+    </row>
+    <row r="980" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C980" s="5">
+        <v>4</v>
+      </c>
+      <c r="D980" s="16" t="s">
+        <v>1670</v>
+      </c>
+      <c r="E980" s="4"/>
+      <c r="F980" s="4"/>
+      <c r="G980" s="4" t="s">
         <v>846</v>
       </c>
-      <c r="H979" s="4" t="s">
+      <c r="H980" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="I979" s="6" t="s">
-        <v>1660</v>
-      </c>
-      <c r="J979" s="11" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K979" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="980" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C980" s="18">
-        <v>16</v>
-      </c>
-      <c r="D980" s="31" t="s">
-        <v>423</v>
-      </c>
-      <c r="E980" s="5">
-        <v>2014</v>
-      </c>
-      <c r="G980" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="H980" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="I980" s="4" t="s">
-        <v>1661</v>
-      </c>
-      <c r="J980" s="11" t="s">
-        <v>1019</v>
-      </c>
-      <c r="K980" s="4" t="s">
-        <v>412</v>
-      </c>
+      <c r="I980" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="J980" s="1"/>
+      <c r="K980" s="1"/>
     </row>
     <row r="981" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C981" s="18">
-        <v>17</v>
-      </c>
-      <c r="D981" s="31" t="s">
-        <v>841</v>
-      </c>
-      <c r="E981" s="4">
-        <v>2014</v>
-      </c>
-      <c r="G981" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H981" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I981" s="5" t="s">
-        <v>1662</v>
-      </c>
-      <c r="K981" s="4" t="s">
-        <v>791</v>
-      </c>
+      <c r="D981" s="2"/>
+      <c r="E981" s="2"/>
+      <c r="F981" s="2"/>
+      <c r="G981" s="2"/>
+      <c r="H981" s="2"/>
+      <c r="I981" s="1"/>
+      <c r="J981" s="1"/>
+      <c r="K981" s="1"/>
     </row>
     <row r="982" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C982" s="18"/>
-      <c r="D982" s="16"/>
-      <c r="I982" s="4"/>
-      <c r="J982" s="4"/>
-      <c r="K982" s="4"/>
+      <c r="D982" s="2"/>
+      <c r="E982" s="2"/>
+      <c r="F982" s="2"/>
+      <c r="G982" s="2"/>
+      <c r="H982" s="2"/>
+      <c r="I982" s="1"/>
+      <c r="J982" s="1"/>
+      <c r="K982" s="1"/>
     </row>
     <row r="983" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C983" s="18">
-        <v>1</v>
-      </c>
-      <c r="D983" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="E983" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F983" s="10">
-        <v>2</v>
-      </c>
-      <c r="G983" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H983" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I983" s="10" t="s">
-        <v>1646</v>
-      </c>
-      <c r="J983" s="10"/>
-      <c r="K983" s="10" t="s">
-        <v>221</v>
-      </c>
+      <c r="D983" s="2"/>
+      <c r="E983" s="2"/>
+      <c r="F983" s="2"/>
+      <c r="G983" s="2"/>
+      <c r="H983" s="2"/>
+      <c r="I983" s="1"/>
+      <c r="J983" s="1"/>
+      <c r="K983" s="1"/>
     </row>
     <row r="984" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C984" s="18">
-        <v>2</v>
-      </c>
-      <c r="D984" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="E984" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F984" s="10">
-        <v>2</v>
-      </c>
-      <c r="G984" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H984" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I984" s="10" t="s">
-        <v>1647</v>
-      </c>
-      <c r="J984" s="10"/>
-      <c r="K984" s="10" t="s">
-        <v>194</v>
-      </c>
+      <c r="D984" s="2"/>
+      <c r="E984" s="2"/>
+      <c r="F984" s="2"/>
+      <c r="G984" s="2"/>
+      <c r="H984" s="2"/>
+      <c r="I984" s="1"/>
+      <c r="J984" s="1"/>
+      <c r="K984" s="1"/>
     </row>
     <row r="985" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C985" s="18">
-        <v>3</v>
-      </c>
-      <c r="D985" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="E985" s="10">
-        <v>2014</v>
-      </c>
-      <c r="F985" s="10">
-        <v>2</v>
-      </c>
-      <c r="G985" s="10" t="s">
-        <v>846</v>
-      </c>
-      <c r="H985" s="10" t="s">
-        <v>847</v>
-      </c>
-      <c r="I985" s="10" t="s">
-        <v>1650</v>
-      </c>
-      <c r="J985" s="10"/>
-      <c r="K985" s="10" t="s">
-        <v>194</v>
-      </c>
+      <c r="D985" s="30" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E985" s="30"/>
+      <c r="F985" s="30"/>
+      <c r="G985" s="30"/>
+      <c r="H985" s="30" t="s">
+        <v>1672</v>
+      </c>
+      <c r="I985" s="3"/>
+      <c r="J985" s="1"/>
+      <c r="K985" s="1"/>
     </row>
     <row r="986" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C986" s="18">
-        <v>4</v>
-      </c>
-      <c r="D986" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="E986" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F986" s="4">
-        <v>2</v>
-      </c>
-      <c r="G986" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H986" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I986" s="4" t="s">
-        <v>1649</v>
-      </c>
-      <c r="J986" s="4"/>
-      <c r="K986" s="4" t="s">
-        <v>194</v>
-      </c>
+      <c r="D986" s="30" t="s">
+        <v>1673</v>
+      </c>
+      <c r="E986" s="30"/>
+      <c r="F986" s="30"/>
+      <c r="G986" s="30"/>
+      <c r="H986" s="30" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I986" s="3"/>
+      <c r="J986" s="1"/>
+      <c r="K986" s="1"/>
     </row>
     <row r="987" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C987" s="18">
-        <v>5</v>
-      </c>
-      <c r="D987" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="E987" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F987" s="4">
-        <v>2</v>
-      </c>
-      <c r="G987" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H987" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I987" s="5" t="s">
-        <v>1648</v>
-      </c>
-      <c r="K987" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="988" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C988" s="18">
-        <v>6</v>
-      </c>
-      <c r="D988" s="16" t="s">
-        <v>828</v>
-      </c>
-      <c r="E988" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F988" s="4">
-        <v>3</v>
-      </c>
-      <c r="G988" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H988" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I988" s="5" t="s">
-        <v>1653</v>
-      </c>
-      <c r="K988" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="989" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C989" s="18">
-        <v>7</v>
-      </c>
-      <c r="D989" s="16" t="s">
-        <v>834</v>
-      </c>
-      <c r="E989" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F989" s="4">
-        <v>3</v>
-      </c>
-      <c r="G989" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H989" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I989" s="5" t="s">
-        <v>1651</v>
-      </c>
-      <c r="K989" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="990" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C990" s="18">
-        <v>8</v>
-      </c>
-      <c r="D990" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="E990" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F990" s="4">
-        <v>3</v>
-      </c>
-      <c r="G990" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H990" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I990" s="4" t="s">
-        <v>1652</v>
-      </c>
-      <c r="J990" s="4"/>
-      <c r="K990" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="991" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C991" s="18">
-        <v>9</v>
-      </c>
-      <c r="D991" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="E991" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F991" s="4">
-        <v>3</v>
-      </c>
-      <c r="G991" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H991" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I991" s="4" t="s">
-        <v>1654</v>
-      </c>
-      <c r="J991" s="4"/>
-      <c r="K991" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="992" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C992" s="18">
-        <v>10</v>
-      </c>
-      <c r="D992" s="16" t="s">
-        <v>837</v>
-      </c>
-      <c r="E992" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F992" s="4">
-        <v>3</v>
-      </c>
-      <c r="G992" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H992" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I992" s="5" t="s">
-        <v>1657</v>
-      </c>
-      <c r="K992" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="993" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C993" s="18">
-        <v>11</v>
-      </c>
-      <c r="D993" s="16" t="s">
-        <v>832</v>
-      </c>
-      <c r="E993" s="4">
-        <v>2014</v>
-      </c>
-      <c r="F993" s="4">
-        <v>3</v>
-      </c>
-      <c r="G993" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H993" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I993" s="5" t="s">
-        <v>1656</v>
-      </c>
-      <c r="K993" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="994" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C994" s="18">
-        <v>12</v>
-      </c>
-      <c r="D994" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="E994" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F994" s="5">
-        <v>3</v>
-      </c>
-      <c r="G994" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H994" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I994" s="4" t="s">
-        <v>1655</v>
-      </c>
-      <c r="J994" s="4"/>
-      <c r="K994" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="995" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C995" s="18">
-        <v>13</v>
-      </c>
-      <c r="D995" s="37" t="s">
-        <v>840</v>
-      </c>
-      <c r="E995" s="4">
-        <v>2014</v>
-      </c>
-      <c r="G995" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H995" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I995" s="5" t="s">
-        <v>1658</v>
-      </c>
-      <c r="K995" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="996" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C996" s="18">
-        <v>14</v>
-      </c>
-      <c r="D996" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="E996" s="5">
-        <v>2014</v>
-      </c>
-      <c r="F996" s="5">
-        <v>3</v>
-      </c>
-      <c r="G996" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H996" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I996" s="6" t="s">
-        <v>1660</v>
-      </c>
-      <c r="J996" s="6"/>
-      <c r="K996" s="4" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="997" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C997" s="18">
-        <v>15</v>
-      </c>
-      <c r="D997" s="37" t="s">
-        <v>841</v>
-      </c>
-      <c r="E997" s="4">
-        <v>2014</v>
-      </c>
-      <c r="G997" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H997" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I997" s="5" t="s">
-        <v>1662</v>
-      </c>
-      <c r="K997" s="4" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="998" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C998" s="18">
-        <v>16</v>
-      </c>
-      <c r="D998" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="E998" s="5">
-        <v>2014</v>
-      </c>
-      <c r="G998" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="H998" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="I998" s="4" t="s">
-        <v>1659</v>
-      </c>
-      <c r="J998" s="4"/>
-      <c r="K998" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="999" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C999" s="18">
-        <v>17</v>
-      </c>
-      <c r="D999" s="16" t="s">
-        <v>423</v>
-      </c>
-      <c r="E999" s="5">
-        <v>2014</v>
-      </c>
-      <c r="G999" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="H999" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="I999" s="4" t="s">
-        <v>1661</v>
-      </c>
-      <c r="J999" s="4"/>
-      <c r="K999" s="4" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="1001" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1001" s="26" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="1002" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1002" s="26" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="1003" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1003" s="27" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="1004" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1004" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1004" s="16" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E1004" s="4"/>
-      <c r="F1004" s="4"/>
-      <c r="G1004" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H1004" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I1004" s="1" t="s">
-        <v>1663</v>
-      </c>
-    </row>
-    <row r="1005" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1005" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1005" s="27" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G1005" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H1005" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I1005" s="5" t="s">
-        <v>1664</v>
-      </c>
-    </row>
-    <row r="1006" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1006" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1006" s="16" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E1006" s="4"/>
-      <c r="F1006" s="4"/>
-      <c r="G1006" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H1006" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I1006" s="5" t="s">
-        <v>1665</v>
-      </c>
-    </row>
-    <row r="1007" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1007" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1007" s="16" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E1007" s="4"/>
-      <c r="F1007" s="4"/>
-      <c r="G1007" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H1007" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I1007" s="5" t="s">
-        <v>1666</v>
-      </c>
-    </row>
-    <row r="1008" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1008" s="16"/>
-      <c r="E1008" s="4"/>
-      <c r="F1008" s="4"/>
-      <c r="G1008" s="4"/>
-      <c r="H1008" s="4"/>
-    </row>
-    <row r="1009" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1009" s="2" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E1009" s="2"/>
-      <c r="F1009" s="2"/>
-      <c r="G1009" s="2"/>
-      <c r="H1009" s="2"/>
-      <c r="I1009" s="1"/>
-      <c r="J1009" s="1"/>
-      <c r="K1009" s="1"/>
-    </row>
-    <row r="1010" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1010" s="5">
-        <v>1</v>
-      </c>
-      <c r="D1010" s="27" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G1010" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H1010" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I1010" s="1" t="s">
-        <v>1667</v>
-      </c>
-      <c r="J1010" s="4"/>
-      <c r="K1010" s="4"/>
-    </row>
-    <row r="1011" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1011" s="5">
-        <v>2</v>
-      </c>
-      <c r="D1011" s="27" t="s">
-        <v>1000</v>
-      </c>
-      <c r="G1011" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H1011" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I1011" s="5" t="s">
-        <v>1668</v>
-      </c>
-      <c r="J1011" s="1"/>
-      <c r="K1011" s="1"/>
-    </row>
-    <row r="1012" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1012" s="5">
-        <v>3</v>
-      </c>
-      <c r="D1012" s="27" t="s">
-        <v>1669</v>
-      </c>
-      <c r="G1012" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="H1012" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="I1012" s="1" t="s">
-        <v>1670</v>
-      </c>
-      <c r="J1012" s="1"/>
-      <c r="K1012" s="1"/>
-    </row>
-    <row r="1013" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1013" s="5">
-        <v>4</v>
-      </c>
-      <c r="D1013" s="16" t="s">
-        <v>1671</v>
-      </c>
-      <c r="E1013" s="4"/>
-      <c r="F1013" s="4"/>
-      <c r="G1013" s="4" t="s">
-        <v>846</v>
-      </c>
-      <c r="H1013" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="I1013" s="5" t="s">
-        <v>1094</v>
-      </c>
-      <c r="J1013" s="1"/>
-      <c r="K1013" s="1"/>
-    </row>
-    <row r="1014" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1014" s="2"/>
-      <c r="E1014" s="2"/>
-      <c r="F1014" s="2"/>
-      <c r="G1014" s="2"/>
-      <c r="H1014" s="2"/>
-      <c r="I1014" s="1"/>
-      <c r="J1014" s="1"/>
-      <c r="K1014" s="1"/>
-    </row>
-    <row r="1015" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1015" s="2"/>
-      <c r="E1015" s="2"/>
-      <c r="F1015" s="2"/>
-      <c r="G1015" s="2"/>
-      <c r="H1015" s="2"/>
-      <c r="I1015" s="1"/>
-      <c r="J1015" s="1"/>
-      <c r="K1015" s="1"/>
-    </row>
-    <row r="1016" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1016" s="2"/>
-      <c r="E1016" s="2"/>
-      <c r="F1016" s="2"/>
-      <c r="G1016" s="2"/>
-      <c r="H1016" s="2"/>
-      <c r="I1016" s="1"/>
-      <c r="J1016" s="1"/>
-      <c r="K1016" s="1"/>
-    </row>
-    <row r="1017" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1017" s="2"/>
-      <c r="E1017" s="2"/>
-      <c r="F1017" s="2"/>
-      <c r="G1017" s="2"/>
-      <c r="H1017" s="2"/>
-      <c r="I1017" s="1"/>
-      <c r="J1017" s="1"/>
-      <c r="K1017" s="1"/>
-    </row>
-    <row r="1018" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1018" s="30" t="s">
-        <v>1672</v>
-      </c>
-      <c r="E1018" s="30"/>
-      <c r="F1018" s="30"/>
-      <c r="G1018" s="30"/>
-      <c r="H1018" s="30" t="s">
-        <v>1673</v>
-      </c>
-      <c r="I1018" s="3"/>
-      <c r="J1018" s="1"/>
-      <c r="K1018" s="1"/>
-    </row>
-    <row r="1019" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1019" s="30" t="s">
-        <v>1674</v>
-      </c>
-      <c r="E1019" s="30"/>
-      <c r="F1019" s="30"/>
-      <c r="G1019" s="30"/>
-      <c r="H1019" s="30" t="s">
-        <v>1675</v>
-      </c>
-      <c r="I1019" s="3"/>
-      <c r="J1019" s="1"/>
-      <c r="K1019" s="1"/>
-    </row>
-    <row r="1020" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1020" s="2"/>
-      <c r="E1020" s="2"/>
-      <c r="F1020" s="2"/>
-      <c r="G1020" s="2"/>
-      <c r="H1020" s="2"/>
-      <c r="I1020" s="1"/>
-      <c r="J1020" s="1"/>
-      <c r="K1020" s="1"/>
+      <c r="D987" s="2"/>
+      <c r="E987" s="2"/>
+      <c r="F987" s="2"/>
+      <c r="G987" s="2"/>
+      <c r="H987" s="2"/>
+      <c r="I987" s="1"/>
+      <c r="J987" s="1"/>
+      <c r="K987" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -33122,25 +32311,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="41" t="s">
         <v>856</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="30"/>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="42" t="s">
         <v>860</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="3"/>
       <c r="K2" s="30"/>
       <c r="L2" s="30"/>
@@ -33167,14 +32356,14 @@
     </row>
     <row r="4" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="30"/>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="42" t="s">
         <v>859</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
       <c r="J4" s="3"/>
       <c r="K4" s="30"/>
       <c r="L4" s="30"/>
@@ -36260,7 +35449,7 @@
       <c r="J126" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="K126" s="40"/>
+      <c r="K126" s="43"/>
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -36272,7 +35461,7 @@
       </c>
       <c r="G127" s="4"/>
       <c r="H127" s="4"/>
-      <c r="K127" s="40"/>
+      <c r="K127" s="43"/>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -36299,7 +35488,7 @@
       <c r="J128" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="K128" s="40"/>
+      <c r="K128" s="43"/>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -41102,7 +40291,7 @@
       <c r="J312" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="K312" s="40"/>
+      <c r="K312" s="43"/>
       <c r="L312" s="2"/>
       <c r="M312" s="2"/>
       <c r="N312" s="2"/>
@@ -41130,7 +40319,7 @@
       <c r="J313" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="K313" s="40"/>
+      <c r="K313" s="43"/>
       <c r="L313" s="2"/>
       <c r="M313" s="2"/>
       <c r="N313" s="2"/>
@@ -48502,28 +47691,28 @@
       <c r="N612" s="2"/>
     </row>
     <row r="613" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D613" s="42" t="s">
+      <c r="D613" s="41" t="s">
         <v>856</v>
       </c>
-      <c r="E613" s="42"/>
-      <c r="F613" s="42"/>
-      <c r="G613" s="42"/>
-      <c r="H613" s="42"/>
-      <c r="I613" s="42"/>
+      <c r="E613" s="41"/>
+      <c r="F613" s="41"/>
+      <c r="G613" s="41"/>
+      <c r="H613" s="41"/>
+      <c r="I613" s="41"/>
       <c r="K613" s="2"/>
       <c r="L613" s="2"/>
       <c r="M613" s="2"/>
       <c r="N613" s="2"/>
     </row>
     <row r="614" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D614" s="41" t="s">
+      <c r="D614" s="42" t="s">
         <v>860</v>
       </c>
-      <c r="E614" s="41"/>
-      <c r="F614" s="41"/>
-      <c r="G614" s="41"/>
-      <c r="H614" s="41"/>
-      <c r="I614" s="41"/>
+      <c r="E614" s="42"/>
+      <c r="F614" s="42"/>
+      <c r="G614" s="42"/>
+      <c r="H614" s="42"/>
+      <c r="I614" s="42"/>
       <c r="J614" s="3"/>
       <c r="K614" s="2"/>
       <c r="L614" s="2"/>
@@ -48548,14 +47737,14 @@
       <c r="N615" s="2"/>
     </row>
     <row r="616" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D616" s="41" t="s">
+      <c r="D616" s="42" t="s">
         <v>898</v>
       </c>
-      <c r="E616" s="41"/>
-      <c r="F616" s="41"/>
-      <c r="G616" s="41"/>
-      <c r="H616" s="41"/>
-      <c r="I616" s="41"/>
+      <c r="E616" s="42"/>
+      <c r="F616" s="42"/>
+      <c r="G616" s="42"/>
+      <c r="H616" s="42"/>
+      <c r="I616" s="42"/>
       <c r="J616" s="3"/>
       <c r="K616" s="2"/>
       <c r="L616" s="2"/>
@@ -58650,26 +57839,26 @@
       <c r="D2" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42" t="s">
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="43" t="s">
+      <c r="D3" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="E3" s="43" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -58687,36 +57876,36 @@
       <c r="J3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="L3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="M3" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="40" t="s">
+      <c r="O3" s="43" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="40"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="40"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="44"/>
       <c r="J4" s="44"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="40"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="43"/>
     </row>
     <row r="5" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="4">
@@ -61811,21 +61000,21 @@
       </c>
       <c r="J103" s="23"/>
       <c r="K103" s="23"/>
-      <c r="L103" s="42" t="s">
+      <c r="L103" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="M103" s="42"/>
-      <c r="N103" s="42"/>
+      <c r="M103" s="41"/>
+      <c r="N103" s="41"/>
       <c r="O103" s="19"/>
     </row>
     <row r="104" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="40" t="s">
+      <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="43" t="s">
+      <c r="D104" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="E104" s="40" t="s">
+      <c r="E104" s="43" t="s">
         <v>2</v>
       </c>
       <c r="F104" s="4" t="s">
@@ -61839,38 +61028,38 @@
       <c r="J104" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="K104" s="42" t="s">
+      <c r="K104" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="L104" s="42" t="s">
+      <c r="L104" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="M104" s="42" t="s">
+      <c r="M104" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="N104" s="42" t="s">
+      <c r="N104" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="O104" s="40" t="s">
+      <c r="O104" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="P104" s="40"/>
+      <c r="P104" s="43"/>
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C105" s="40"/>
-      <c r="D105" s="43"/>
-      <c r="E105" s="40"/>
+      <c r="C105" s="43"/>
+      <c r="D105" s="45"/>
+      <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
       <c r="I105" s="44"/>
       <c r="J105" s="44"/>
-      <c r="K105" s="42"/>
-      <c r="L105" s="42"/>
-      <c r="M105" s="42"/>
-      <c r="N105" s="42"/>
-      <c r="O105" s="40"/>
-      <c r="P105" s="40"/>
+      <c r="K105" s="41"/>
+      <c r="L105" s="41"/>
+      <c r="M105" s="41"/>
+      <c r="N105" s="41"/>
+      <c r="O105" s="43"/>
+      <c r="P105" s="43"/>
     </row>
     <row r="106" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C106" s="4">
@@ -66723,42 +65912,23 @@
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I261" s="44"/>
       <c r="J261" s="44"/>
-      <c r="K261" s="42"/>
-      <c r="L261" s="42"/>
-      <c r="M261" s="42"/>
-      <c r="N261" s="42"/>
-      <c r="O261" s="40"/>
+      <c r="K261" s="41"/>
+      <c r="L261" s="41"/>
+      <c r="M261" s="41"/>
+      <c r="N261" s="41"/>
+      <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I262" s="44"/>
       <c r="J262" s="44"/>
-      <c r="K262" s="42"/>
-      <c r="L262" s="42"/>
-      <c r="M262" s="42"/>
-      <c r="N262" s="42"/>
-      <c r="O262" s="40"/>
+      <c r="K262" s="41"/>
+      <c r="L262" s="41"/>
+      <c r="M262" s="41"/>
+      <c r="N262" s="41"/>
+      <c r="O262" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -66771,6 +65941,25 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFDBFFED-462E-4108-97BF-E631AB19B282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E9BF18-235D-4850-A754-33705AE0B057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11812" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11812" uniqueCount="1677">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -5063,6 +5063,9 @@
   </si>
   <si>
     <t>Эстафета</t>
+  </si>
+  <si>
+    <t>Шемчук Александр</t>
   </si>
 </sst>
 </file>
@@ -5293,11 +5296,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10934,7 +10937,7 @@
         <v>35</v>
       </c>
       <c r="D181" s="16" t="s">
-        <v>54</v>
+        <v>1676</v>
       </c>
       <c r="E181" s="4">
         <v>2016</v>
@@ -24920,7 +24923,7 @@
         <v>26</v>
       </c>
       <c r="D690" s="16" t="s">
-        <v>54</v>
+        <v>1676</v>
       </c>
       <c r="E690" s="4">
         <v>2016</v>
@@ -29884,7 +29887,7 @@
         <v>34</v>
       </c>
       <c r="D877" s="16" t="s">
-        <v>54</v>
+        <v>1676</v>
       </c>
       <c r="E877" s="4">
         <v>2016</v>
@@ -57831,7 +57834,7 @@
       <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="43" t="s">
@@ -57846,10 +57849,10 @@
       <c r="H3" s="4" t="s">
         <v>843</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="44" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="41" t="s">
@@ -57870,13 +57873,13 @@
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
+      <c r="D4" s="45"/>
       <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="41"/>
       <c r="L4" s="41"/>
       <c r="M4" s="41"/>
@@ -60987,7 +60990,7 @@
       <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="44" t="s">
+      <c r="D104" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E104" s="43" t="s">
@@ -60998,10 +61001,10 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="45" t="s">
+      <c r="I104" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J104" s="45" t="s">
+      <c r="J104" s="44" t="s">
         <v>8</v>
       </c>
       <c r="K104" s="41" t="s">
@@ -61023,13 +61026,13 @@
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="43"/>
-      <c r="D105" s="44"/>
+      <c r="D105" s="45"/>
       <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="45"/>
-      <c r="J105" s="45"/>
+      <c r="I105" s="44"/>
+      <c r="J105" s="44"/>
       <c r="K105" s="41"/>
       <c r="L105" s="41"/>
       <c r="M105" s="41"/>
@@ -65886,8 +65889,8 @@
       </c>
     </row>
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I261" s="45"/>
-      <c r="J261" s="45"/>
+      <c r="I261" s="44"/>
+      <c r="J261" s="44"/>
       <c r="K261" s="41"/>
       <c r="L261" s="41"/>
       <c r="M261" s="41"/>
@@ -65895,8 +65898,8 @@
       <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I262" s="45"/>
-      <c r="J262" s="45"/>
+      <c r="I262" s="44"/>
+      <c r="J262" s="44"/>
       <c r="K262" s="41"/>
       <c r="L262" s="41"/>
       <c r="M262" s="41"/>
@@ -65905,25 +65908,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -65936,6 +65920,25 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{465452CA-5D2C-4BF6-910A-CC5A22D2D122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441148AA-7CB3-4E4E-804D-F140BA823A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Итоговый протокол 1 день" sheetId="10" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11812" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11813" uniqueCount="1676">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -5285,19 +5285,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5626,26 +5626,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="42" t="s">
         <v>1406</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
       <c r="J1" s="18"/>
     </row>
     <row r="2" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="30"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="41" t="s">
         <v>859</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="30"/>
@@ -5674,14 +5674,14 @@
     </row>
     <row r="4" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="30"/>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="41" t="s">
         <v>858</v>
       </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="30"/>
@@ -7128,6 +7128,9 @@
       <c r="O52" s="2"/>
     </row>
     <row r="53" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C53" s="5">
+        <v>22</v>
+      </c>
       <c r="D53" s="16" t="s">
         <v>75</v>
       </c>
@@ -7154,9 +7157,7 @@
       <c r="O53" s="2"/>
     </row>
     <row r="54" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C54" s="4">
-        <v>1</v>
-      </c>
+      <c r="C54" s="4"/>
       <c r="D54" s="16" t="s">
         <v>1157</v>
       </c>
@@ -7171,7 +7172,7 @@
     </row>
     <row r="55" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="37" t="s">
         <v>68</v>
@@ -7202,7 +7203,7 @@
     </row>
     <row r="56" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" s="37" t="s">
         <v>292</v>
@@ -7233,7 +7234,7 @@
     </row>
     <row r="57" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57" s="37" t="s">
         <v>280</v>
@@ -7264,7 +7265,7 @@
     </row>
     <row r="58" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D58" s="16" t="s">
         <v>299</v>
@@ -7295,7 +7296,7 @@
     </row>
     <row r="59" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59" s="16" t="s">
         <v>298</v>
@@ -7326,7 +7327,7 @@
     </row>
     <row r="60" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D60" s="27" t="s">
         <v>636</v>
@@ -7356,7 +7357,7 @@
     </row>
     <row r="61" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C61" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="16" t="s">
         <v>296</v>
@@ -7387,7 +7388,7 @@
     </row>
     <row r="62" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" s="16" t="s">
         <v>325</v>
@@ -7417,7 +7418,7 @@
     </row>
     <row r="63" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C63" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D63" s="16" t="s">
         <v>544</v>
@@ -7450,7 +7451,7 @@
     </row>
     <row r="64" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C64" s="4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D64" s="16" t="s">
         <v>575</v>
@@ -7480,7 +7481,7 @@
     </row>
     <row r="65" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C65" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" s="16" t="s">
         <v>319</v>
@@ -7510,7 +7511,7 @@
     </row>
     <row r="66" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="4">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D66" s="16" t="s">
         <v>76</v>
@@ -7541,7 +7542,7 @@
     </row>
     <row r="67" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C67" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D67" s="16" t="s">
         <v>330</v>
@@ -7571,7 +7572,7 @@
     </row>
     <row r="68" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C68" s="4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D68" s="16" t="s">
         <v>552</v>
@@ -7601,7 +7602,7 @@
     </row>
     <row r="69" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C69" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D69" s="27" t="s">
         <v>656</v>
@@ -7628,7 +7629,7 @@
     </row>
     <row r="70" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C70" s="4">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D70" s="27" t="s">
         <v>652</v>
@@ -7655,7 +7656,7 @@
     </row>
     <row r="71" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C71" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D71" s="16" t="s">
         <v>335</v>
@@ -7683,7 +7684,7 @@
     </row>
     <row r="72" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D72" s="27" t="s">
         <v>588</v>
@@ -7710,7 +7711,7 @@
     </row>
     <row r="73" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C73" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D73" s="16" t="s">
         <v>579</v>
@@ -7737,7 +7738,7 @@
     </row>
     <row r="74" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" s="4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D74" s="27" t="s">
         <v>591</v>
@@ -7765,7 +7766,7 @@
     </row>
     <row r="75" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C75" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D75" s="27" t="s">
         <v>589</v>
@@ -7793,7 +7794,7 @@
     </row>
     <row r="76" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C76" s="4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D76" s="27" t="s">
         <v>627</v>
@@ -7820,7 +7821,7 @@
     </row>
     <row r="77" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C77" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D77" s="27" t="s">
         <v>633</v>
@@ -7847,7 +7848,7 @@
     </row>
     <row r="78" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C78" s="4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D78" s="27" t="s">
         <v>618</v>
@@ -7874,7 +7875,7 @@
     </row>
     <row r="79" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C79" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D79" s="16" t="s">
         <v>583</v>
@@ -7903,7 +7904,7 @@
     </row>
     <row r="80" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C80" s="4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D80" s="16" t="s">
         <v>581</v>
@@ -7930,7 +7931,7 @@
     </row>
     <row r="81" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C81" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D81" s="27" t="s">
         <v>630</v>
@@ -7957,7 +7958,7 @@
     </row>
     <row r="82" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C82" s="4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D82" s="27" t="s">
         <v>616</v>
@@ -7984,7 +7985,7 @@
     </row>
     <row r="83" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D83" s="27" t="s">
         <v>624</v>
@@ -8011,7 +8012,7 @@
     </row>
     <row r="84" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C84" s="4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D84" s="27" t="s">
         <v>610</v>
@@ -8038,7 +8039,7 @@
     </row>
     <row r="85" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C85" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D85" s="27" t="s">
         <v>621</v>
@@ -8065,7 +8066,7 @@
     </row>
     <row r="86" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D86" s="16" t="s">
         <v>585</v>
@@ -8092,7 +8093,7 @@
     </row>
     <row r="87" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C87" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D87" s="27" t="s">
         <v>613</v>
@@ -8119,7 +8120,7 @@
     </row>
     <row r="88" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="4">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D88" s="16" t="s">
         <v>66</v>
@@ -8146,7 +8147,7 @@
     </row>
     <row r="89" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C89" s="5">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D89" s="27" t="s">
         <v>605</v>
@@ -8173,7 +8174,7 @@
     </row>
     <row r="90" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C90" s="4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D90" s="27" t="s">
         <v>644</v>
@@ -8186,6 +8187,9 @@
       </c>
       <c r="H90" s="4" t="s">
         <v>844</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>1058</v>
       </c>
       <c r="K90" s="5" t="s">
         <v>609</v>
@@ -21571,25 +21575,25 @@
       <c r="K565" s="4"/>
     </row>
     <row r="566" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D566" s="41" t="s">
+      <c r="D566" s="42" t="s">
         <v>1406</v>
       </c>
-      <c r="E566" s="41"/>
-      <c r="F566" s="41"/>
-      <c r="G566" s="41"/>
-      <c r="H566" s="41"/>
-      <c r="I566" s="41"/>
+      <c r="E566" s="42"/>
+      <c r="F566" s="42"/>
+      <c r="G566" s="42"/>
+      <c r="H566" s="42"/>
+      <c r="I566" s="42"/>
       <c r="J566" s="18"/>
     </row>
     <row r="567" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D567" s="42" t="s">
+      <c r="D567" s="41" t="s">
         <v>859</v>
       </c>
-      <c r="E567" s="42"/>
-      <c r="F567" s="42"/>
-      <c r="G567" s="42"/>
-      <c r="H567" s="42"/>
-      <c r="I567" s="42"/>
+      <c r="E567" s="41"/>
+      <c r="F567" s="41"/>
+      <c r="G567" s="41"/>
+      <c r="H567" s="41"/>
+      <c r="I567" s="41"/>
       <c r="J567" s="3"/>
       <c r="K567" s="3"/>
       <c r="N567" s="2"/>
@@ -21612,14 +21616,14 @@
       <c r="O568" s="2"/>
     </row>
     <row r="569" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D569" s="42" t="s">
+      <c r="D569" s="41" t="s">
         <v>897</v>
       </c>
-      <c r="E569" s="42"/>
-      <c r="F569" s="42"/>
-      <c r="G569" s="42"/>
-      <c r="H569" s="42"/>
-      <c r="I569" s="42"/>
+      <c r="E569" s="41"/>
+      <c r="F569" s="41"/>
+      <c r="G569" s="41"/>
+      <c r="H569" s="41"/>
+      <c r="I569" s="41"/>
       <c r="J569" s="3"/>
       <c r="K569" s="3"/>
       <c r="N569" s="2"/>
@@ -23325,7 +23329,7 @@
     </row>
     <row r="633" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C633" s="18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D633" s="37" t="s">
         <v>831</v>
@@ -23356,7 +23360,7 @@
     </row>
     <row r="634" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C634" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D634" s="16" t="s">
         <v>256</v>
@@ -23418,7 +23422,7 @@
     </row>
     <row r="636" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C636" s="5">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D636" s="16" t="s">
         <v>237</v>
@@ -23449,7 +23453,7 @@
     </row>
     <row r="637" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C637" s="5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D637" s="16" t="s">
         <v>839</v>
@@ -23477,7 +23481,7 @@
     </row>
     <row r="638" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C638" s="5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D638" s="16" t="s">
         <v>418</v>
@@ -23505,7 +23509,7 @@
     </row>
     <row r="639" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C639" s="5">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D639" s="16" t="s">
         <v>268</v>
@@ -25583,7 +25587,7 @@
     </row>
     <row r="718" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C718" s="18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D718" s="37" t="s">
         <v>796</v>
@@ -25643,7 +25647,7 @@
     </row>
     <row r="720" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C720" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D720" s="16" t="s">
         <v>214</v>
@@ -25673,7 +25677,7 @@
     </row>
     <row r="721" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C721" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D721" s="16" t="s">
         <v>788</v>
@@ -25703,7 +25707,7 @@
     </row>
     <row r="722" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C722" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D722" s="16" t="s">
         <v>809</v>
@@ -25733,7 +25737,7 @@
     </row>
     <row r="723" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C723" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D723" s="16" t="s">
         <v>407</v>
@@ -25760,7 +25764,7 @@
     </row>
     <row r="724" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C724" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D724" s="16" t="s">
         <v>412</v>
@@ -32287,25 +32291,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="42" t="s">
         <v>855</v>
       </c>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="30"/>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="41" t="s">
         <v>859</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
       <c r="J2" s="3"/>
       <c r="K2" s="30"/>
       <c r="L2" s="30"/>
@@ -32332,14 +32336,14 @@
     </row>
     <row r="4" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="30"/>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="41" t="s">
         <v>858</v>
       </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
       <c r="J4" s="3"/>
       <c r="K4" s="30"/>
       <c r="L4" s="30"/>
@@ -47667,28 +47671,28 @@
       <c r="N612" s="2"/>
     </row>
     <row r="613" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D613" s="41" t="s">
+      <c r="D613" s="42" t="s">
         <v>855</v>
       </c>
-      <c r="E613" s="41"/>
-      <c r="F613" s="41"/>
-      <c r="G613" s="41"/>
-      <c r="H613" s="41"/>
-      <c r="I613" s="41"/>
+      <c r="E613" s="42"/>
+      <c r="F613" s="42"/>
+      <c r="G613" s="42"/>
+      <c r="H613" s="42"/>
+      <c r="I613" s="42"/>
       <c r="K613" s="2"/>
       <c r="L613" s="2"/>
       <c r="M613" s="2"/>
       <c r="N613" s="2"/>
     </row>
     <row r="614" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D614" s="42" t="s">
+      <c r="D614" s="41" t="s">
         <v>859</v>
       </c>
-      <c r="E614" s="42"/>
-      <c r="F614" s="42"/>
-      <c r="G614" s="42"/>
-      <c r="H614" s="42"/>
-      <c r="I614" s="42"/>
+      <c r="E614" s="41"/>
+      <c r="F614" s="41"/>
+      <c r="G614" s="41"/>
+      <c r="H614" s="41"/>
+      <c r="I614" s="41"/>
       <c r="J614" s="3"/>
       <c r="K614" s="2"/>
       <c r="L614" s="2"/>
@@ -47713,14 +47717,14 @@
       <c r="N615" s="2"/>
     </row>
     <row r="616" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D616" s="42" t="s">
+      <c r="D616" s="41" t="s">
         <v>897</v>
       </c>
-      <c r="E616" s="42"/>
-      <c r="F616" s="42"/>
-      <c r="G616" s="42"/>
-      <c r="H616" s="42"/>
-      <c r="I616" s="42"/>
+      <c r="E616" s="41"/>
+      <c r="F616" s="41"/>
+      <c r="G616" s="41"/>
+      <c r="H616" s="41"/>
+      <c r="I616" s="41"/>
       <c r="J616" s="3"/>
       <c r="K616" s="2"/>
       <c r="L616" s="2"/>
@@ -57815,23 +57819,23 @@
       <c r="D2" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41" t="s">
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="43" t="s">
@@ -57846,22 +57850,22 @@
       <c r="H3" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="41" t="s">
+      <c r="K3" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="41" t="s">
+      <c r="M3" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="42" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="43" t="s">
@@ -57870,17 +57874,17 @@
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
+      <c r="D4" s="45"/>
       <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
       <c r="O4" s="43"/>
     </row>
     <row r="5" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -60976,18 +60980,18 @@
       </c>
       <c r="J103" s="23"/>
       <c r="K103" s="23"/>
-      <c r="L103" s="41" t="s">
+      <c r="L103" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="M103" s="41"/>
-      <c r="N103" s="41"/>
+      <c r="M103" s="42"/>
+      <c r="N103" s="42"/>
       <c r="O103" s="19"/>
     </row>
     <row r="104" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="44" t="s">
+      <c r="D104" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E104" s="43" t="s">
@@ -60998,22 +61002,22 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="45" t="s">
+      <c r="I104" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J104" s="45" t="s">
+      <c r="J104" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="K104" s="41" t="s">
+      <c r="K104" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="L104" s="41" t="s">
+      <c r="L104" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="M104" s="41" t="s">
+      <c r="M104" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="N104" s="41" t="s">
+      <c r="N104" s="42" t="s">
         <v>6</v>
       </c>
       <c r="O104" s="43" t="s">
@@ -61023,17 +61027,17 @@
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="43"/>
-      <c r="D105" s="44"/>
+      <c r="D105" s="45"/>
       <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="45"/>
-      <c r="J105" s="45"/>
-      <c r="K105" s="41"/>
-      <c r="L105" s="41"/>
-      <c r="M105" s="41"/>
-      <c r="N105" s="41"/>
+      <c r="I105" s="44"/>
+      <c r="J105" s="44"/>
+      <c r="K105" s="42"/>
+      <c r="L105" s="42"/>
+      <c r="M105" s="42"/>
+      <c r="N105" s="42"/>
       <c r="O105" s="43"/>
       <c r="P105" s="43"/>
     </row>
@@ -65886,44 +65890,25 @@
       </c>
     </row>
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I261" s="45"/>
-      <c r="J261" s="45"/>
-      <c r="K261" s="41"/>
-      <c r="L261" s="41"/>
-      <c r="M261" s="41"/>
-      <c r="N261" s="41"/>
+      <c r="I261" s="44"/>
+      <c r="J261" s="44"/>
+      <c r="K261" s="42"/>
+      <c r="L261" s="42"/>
+      <c r="M261" s="42"/>
+      <c r="N261" s="42"/>
       <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I262" s="45"/>
-      <c r="J262" s="45"/>
-      <c r="K262" s="41"/>
-      <c r="L262" s="41"/>
-      <c r="M262" s="41"/>
-      <c r="N262" s="41"/>
+      <c r="I262" s="44"/>
+      <c r="J262" s="44"/>
+      <c r="K262" s="42"/>
+      <c r="L262" s="42"/>
+      <c r="M262" s="42"/>
+      <c r="N262" s="42"/>
       <c r="O262" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -65936,6 +65921,25 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441148AA-7CB3-4E4E-804D-F140BA823A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5ABDCE-BED3-4C07-9B96-2C28ED19E6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Итоговый протокол 1 день" sheetId="10" r:id="rId1"/>
+    <sheet name="Итоговый протокол" sheetId="10" r:id="rId1"/>
     <sheet name="Стартовый протокол" sheetId="9" r:id="rId2"/>
     <sheet name="Заявка" sheetId="7" r:id="rId3"/>
   </sheets>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11813" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11803" uniqueCount="1676">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -5285,19 +5285,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5626,26 +5626,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="41" t="s">
         <v>1406</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
       <c r="J1" s="18"/>
     </row>
     <row r="2" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="30"/>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="42" t="s">
         <v>859</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="30"/>
@@ -5674,14 +5674,14 @@
     </row>
     <row r="4" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="30"/>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="42" t="s">
         <v>858</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="30"/>
@@ -21575,25 +21575,25 @@
       <c r="K565" s="4"/>
     </row>
     <row r="566" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D566" s="42" t="s">
+      <c r="D566" s="41" t="s">
         <v>1406</v>
       </c>
-      <c r="E566" s="42"/>
-      <c r="F566" s="42"/>
-      <c r="G566" s="42"/>
-      <c r="H566" s="42"/>
-      <c r="I566" s="42"/>
+      <c r="E566" s="41"/>
+      <c r="F566" s="41"/>
+      <c r="G566" s="41"/>
+      <c r="H566" s="41"/>
+      <c r="I566" s="41"/>
       <c r="J566" s="18"/>
     </row>
     <row r="567" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D567" s="41" t="s">
+      <c r="D567" s="42" t="s">
         <v>859</v>
       </c>
-      <c r="E567" s="41"/>
-      <c r="F567" s="41"/>
-      <c r="G567" s="41"/>
-      <c r="H567" s="41"/>
-      <c r="I567" s="41"/>
+      <c r="E567" s="42"/>
+      <c r="F567" s="42"/>
+      <c r="G567" s="42"/>
+      <c r="H567" s="42"/>
+      <c r="I567" s="42"/>
       <c r="J567" s="3"/>
       <c r="K567" s="3"/>
       <c r="N567" s="2"/>
@@ -21616,14 +21616,14 @@
       <c r="O568" s="2"/>
     </row>
     <row r="569" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D569" s="41" t="s">
+      <c r="D569" s="42" t="s">
         <v>897</v>
       </c>
-      <c r="E569" s="41"/>
-      <c r="F569" s="41"/>
-      <c r="G569" s="41"/>
-      <c r="H569" s="41"/>
-      <c r="I569" s="41"/>
+      <c r="E569" s="42"/>
+      <c r="F569" s="42"/>
+      <c r="G569" s="42"/>
+      <c r="H569" s="42"/>
+      <c r="I569" s="42"/>
       <c r="J569" s="3"/>
       <c r="K569" s="3"/>
       <c r="N569" s="2"/>
@@ -31066,9 +31066,7 @@
       <c r="J926" s="5">
         <v>1</v>
       </c>
-      <c r="K926" s="10" t="s">
-        <v>193</v>
-      </c>
+      <c r="K926" s="10"/>
     </row>
     <row r="927" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C927" s="18">
@@ -31095,9 +31093,7 @@
       <c r="J927" s="5">
         <v>2</v>
       </c>
-      <c r="K927" s="10" t="s">
-        <v>193</v>
-      </c>
+      <c r="K927" s="10"/>
     </row>
     <row r="928" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C928" s="18">
@@ -31124,9 +31120,7 @@
       <c r="J928" s="5">
         <v>2</v>
       </c>
-      <c r="K928" s="10" t="s">
-        <v>193</v>
-      </c>
+      <c r="K928" s="10"/>
     </row>
     <row r="929" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C929" s="5">
@@ -31153,9 +31147,7 @@
       <c r="J929" s="5">
         <v>2</v>
       </c>
-      <c r="K929" s="4" t="s">
-        <v>790</v>
-      </c>
+      <c r="K929" s="4"/>
     </row>
     <row r="930" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C930" s="5">
@@ -31182,9 +31174,7 @@
       <c r="J930" s="5">
         <v>2</v>
       </c>
-      <c r="K930" s="4" t="s">
-        <v>790</v>
-      </c>
+      <c r="K930" s="4"/>
       <c r="M930" s="2"/>
       <c r="N930" s="2"/>
       <c r="O930" s="2"/>
@@ -31214,9 +31204,7 @@
       <c r="J931" s="5">
         <v>3</v>
       </c>
-      <c r="K931" s="4" t="s">
-        <v>193</v>
-      </c>
+      <c r="K931" s="4"/>
       <c r="M931" s="2"/>
       <c r="N931" s="2"/>
       <c r="O931" s="2"/>
@@ -31246,9 +31234,7 @@
       <c r="J932" s="5">
         <v>3</v>
       </c>
-      <c r="K932" s="4" t="s">
-        <v>790</v>
-      </c>
+      <c r="K932" s="4"/>
       <c r="M932" s="2"/>
       <c r="N932" s="2"/>
       <c r="O932" s="2"/>
@@ -31278,9 +31264,7 @@
       <c r="J933" s="5">
         <v>3</v>
       </c>
-      <c r="K933" s="4" t="s">
-        <v>790</v>
-      </c>
+      <c r="K933" s="4"/>
       <c r="M933" s="2"/>
       <c r="N933" s="2"/>
       <c r="O933" s="2"/>
@@ -31310,9 +31294,7 @@
       <c r="J934" s="5">
         <v>3</v>
       </c>
-      <c r="K934" s="4" t="s">
-        <v>790</v>
-      </c>
+      <c r="K934" s="4"/>
       <c r="M934" s="2"/>
       <c r="N934" s="2"/>
       <c r="O934" s="2"/>
@@ -31340,9 +31322,7 @@
       <c r="J935" s="5" t="s">
         <v>1018</v>
       </c>
-      <c r="K935" s="4" t="s">
-        <v>411</v>
-      </c>
+      <c r="K935" s="4"/>
       <c r="M935" s="2"/>
       <c r="N935" s="2"/>
       <c r="O935" s="2"/>
@@ -32291,25 +32271,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="41" t="s">
         <v>855</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
     </row>
     <row r="2" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="30"/>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="42" t="s">
         <v>859</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
       <c r="J2" s="3"/>
       <c r="K2" s="30"/>
       <c r="L2" s="30"/>
@@ -32336,14 +32316,14 @@
     </row>
     <row r="4" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="30"/>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="42" t="s">
         <v>858</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
       <c r="J4" s="3"/>
       <c r="K4" s="30"/>
       <c r="L4" s="30"/>
@@ -47671,28 +47651,28 @@
       <c r="N612" s="2"/>
     </row>
     <row r="613" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D613" s="42" t="s">
+      <c r="D613" s="41" t="s">
         <v>855</v>
       </c>
-      <c r="E613" s="42"/>
-      <c r="F613" s="42"/>
-      <c r="G613" s="42"/>
-      <c r="H613" s="42"/>
-      <c r="I613" s="42"/>
+      <c r="E613" s="41"/>
+      <c r="F613" s="41"/>
+      <c r="G613" s="41"/>
+      <c r="H613" s="41"/>
+      <c r="I613" s="41"/>
       <c r="K613" s="2"/>
       <c r="L613" s="2"/>
       <c r="M613" s="2"/>
       <c r="N613" s="2"/>
     </row>
     <row r="614" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D614" s="41" t="s">
+      <c r="D614" s="42" t="s">
         <v>859</v>
       </c>
-      <c r="E614" s="41"/>
-      <c r="F614" s="41"/>
-      <c r="G614" s="41"/>
-      <c r="H614" s="41"/>
-      <c r="I614" s="41"/>
+      <c r="E614" s="42"/>
+      <c r="F614" s="42"/>
+      <c r="G614" s="42"/>
+      <c r="H614" s="42"/>
+      <c r="I614" s="42"/>
       <c r="J614" s="3"/>
       <c r="K614" s="2"/>
       <c r="L614" s="2"/>
@@ -47717,14 +47697,14 @@
       <c r="N615" s="2"/>
     </row>
     <row r="616" spans="3:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D616" s="41" t="s">
+      <c r="D616" s="42" t="s">
         <v>897</v>
       </c>
-      <c r="E616" s="41"/>
-      <c r="F616" s="41"/>
-      <c r="G616" s="41"/>
-      <c r="H616" s="41"/>
-      <c r="I616" s="41"/>
+      <c r="E616" s="42"/>
+      <c r="F616" s="42"/>
+      <c r="G616" s="42"/>
+      <c r="H616" s="42"/>
+      <c r="I616" s="42"/>
       <c r="J616" s="3"/>
       <c r="K616" s="2"/>
       <c r="L616" s="2"/>
@@ -57819,23 +57799,23 @@
       <c r="D2" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42" t="s">
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
       <c r="O2" s="19"/>
     </row>
     <row r="3" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="44" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="43" t="s">
@@ -57850,22 +57830,22 @@
       <c r="H3" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="L3" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="M3" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="41" t="s">
         <v>6</v>
       </c>
       <c r="O3" s="43" t="s">
@@ -57874,17 +57854,17 @@
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="43"/>
-      <c r="D4" s="45"/>
+      <c r="D4" s="44"/>
       <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
       <c r="O4" s="43"/>
     </row>
     <row r="5" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -60980,18 +60960,18 @@
       </c>
       <c r="J103" s="23"/>
       <c r="K103" s="23"/>
-      <c r="L103" s="42" t="s">
+      <c r="L103" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="M103" s="42"/>
-      <c r="N103" s="42"/>
+      <c r="M103" s="41"/>
+      <c r="N103" s="41"/>
       <c r="O103" s="19"/>
     </row>
     <row r="104" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="45" t="s">
+      <c r="D104" s="44" t="s">
         <v>0</v>
       </c>
       <c r="E104" s="43" t="s">
@@ -61002,22 +60982,22 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="44" t="s">
+      <c r="I104" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="J104" s="44" t="s">
+      <c r="J104" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="K104" s="42" t="s">
+      <c r="K104" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="L104" s="42" t="s">
+      <c r="L104" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="M104" s="42" t="s">
+      <c r="M104" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="N104" s="42" t="s">
+      <c r="N104" s="41" t="s">
         <v>6</v>
       </c>
       <c r="O104" s="43" t="s">
@@ -61027,17 +61007,17 @@
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="43"/>
-      <c r="D105" s="45"/>
+      <c r="D105" s="44"/>
       <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="44"/>
-      <c r="J105" s="44"/>
-      <c r="K105" s="42"/>
-      <c r="L105" s="42"/>
-      <c r="M105" s="42"/>
-      <c r="N105" s="42"/>
+      <c r="I105" s="45"/>
+      <c r="J105" s="45"/>
+      <c r="K105" s="41"/>
+      <c r="L105" s="41"/>
+      <c r="M105" s="41"/>
+      <c r="N105" s="41"/>
       <c r="O105" s="43"/>
       <c r="P105" s="43"/>
     </row>
@@ -65890,25 +65870,44 @@
       </c>
     </row>
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I261" s="44"/>
-      <c r="J261" s="44"/>
-      <c r="K261" s="42"/>
-      <c r="L261" s="42"/>
-      <c r="M261" s="42"/>
-      <c r="N261" s="42"/>
+      <c r="I261" s="45"/>
+      <c r="J261" s="45"/>
+      <c r="K261" s="41"/>
+      <c r="L261" s="41"/>
+      <c r="M261" s="41"/>
+      <c r="N261" s="41"/>
       <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I262" s="44"/>
-      <c r="J262" s="44"/>
-      <c r="K262" s="42"/>
-      <c r="L262" s="42"/>
-      <c r="M262" s="42"/>
-      <c r="N262" s="42"/>
+      <c r="I262" s="45"/>
+      <c r="J262" s="45"/>
+      <c r="K262" s="41"/>
+      <c r="L262" s="41"/>
+      <c r="M262" s="41"/>
+      <c r="N262" s="41"/>
       <c r="O262" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -65921,25 +65920,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5ABDCE-BED3-4C07-9B96-2C28ED19E6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED72504-DDD7-4019-8560-D9E928534C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11803" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11802" uniqueCount="1676">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -5293,11 +5293,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5613,7 +5613,7 @@
     <col min="5" max="5" width="6.7109375" style="5" customWidth="1"/>
     <col min="6" max="6" width="6.42578125" style="5" customWidth="1"/>
     <col min="7" max="7" width="10.5703125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" style="5" customWidth="1"/>
     <col min="9" max="10" width="7" style="5" customWidth="1"/>
     <col min="11" max="11" width="25.140625" style="5" customWidth="1"/>
     <col min="12" max="12" width="10.140625" style="5" customWidth="1"/>
@@ -31051,9 +31051,7 @@
       <c r="E926" s="10">
         <v>2014</v>
       </c>
-      <c r="F926" s="10">
-        <v>1</v>
-      </c>
+      <c r="F926" s="10"/>
       <c r="G926" s="10" t="s">
         <v>845</v>
       </c>
@@ -31062,9 +31060,6 @@
       </c>
       <c r="I926" s="18" t="s">
         <v>1631</v>
-      </c>
-      <c r="J926" s="5">
-        <v>1</v>
       </c>
       <c r="K926" s="10"/>
     </row>
@@ -31078,9 +31073,7 @@
       <c r="E927" s="10">
         <v>2014</v>
       </c>
-      <c r="F927" s="10">
-        <v>1</v>
-      </c>
+      <c r="F927" s="10"/>
       <c r="G927" s="10" t="s">
         <v>845</v>
       </c>
@@ -31089,9 +31082,6 @@
       </c>
       <c r="I927" s="18" t="s">
         <v>1136</v>
-      </c>
-      <c r="J927" s="5">
-        <v>2</v>
       </c>
       <c r="K927" s="10"/>
     </row>
@@ -31105,9 +31095,7 @@
       <c r="E928" s="10">
         <v>2014</v>
       </c>
-      <c r="F928" s="10">
-        <v>2</v>
-      </c>
+      <c r="F928" s="10"/>
       <c r="G928" s="10" t="s">
         <v>845</v>
       </c>
@@ -31116,9 +31104,6 @@
       </c>
       <c r="I928" s="18" t="s">
         <v>1632</v>
-      </c>
-      <c r="J928" s="5">
-        <v>2</v>
       </c>
       <c r="K928" s="10"/>
     </row>
@@ -31132,9 +31117,7 @@
       <c r="E929" s="4">
         <v>2014</v>
       </c>
-      <c r="F929" s="4">
-        <v>1</v>
-      </c>
+      <c r="F929" s="4"/>
       <c r="G929" s="4" t="s">
         <v>843</v>
       </c>
@@ -31143,9 +31126,6 @@
       </c>
       <c r="I929" s="5" t="s">
         <v>1633</v>
-      </c>
-      <c r="J929" s="5">
-        <v>2</v>
       </c>
       <c r="K929" s="4"/>
     </row>
@@ -31159,9 +31139,7 @@
       <c r="E930" s="4">
         <v>2014</v>
       </c>
-      <c r="F930" s="4">
-        <v>2</v>
-      </c>
+      <c r="F930" s="4"/>
       <c r="G930" s="4" t="s">
         <v>843</v>
       </c>
@@ -31170,9 +31148,6 @@
       </c>
       <c r="I930" s="5" t="s">
         <v>1634</v>
-      </c>
-      <c r="J930" s="5">
-        <v>2</v>
       </c>
       <c r="K930" s="4"/>
       <c r="M930" s="2"/>
@@ -31189,9 +31164,6 @@
       <c r="E931" s="5">
         <v>2014</v>
       </c>
-      <c r="F931" s="5">
-        <v>2</v>
-      </c>
       <c r="G931" s="4" t="s">
         <v>845</v>
       </c>
@@ -31200,9 +31172,6 @@
       </c>
       <c r="I931" s="5" t="s">
         <v>1635</v>
-      </c>
-      <c r="J931" s="5">
-        <v>3</v>
       </c>
       <c r="K931" s="4"/>
       <c r="M931" s="2"/>
@@ -31219,9 +31188,7 @@
       <c r="E932" s="4">
         <v>2014</v>
       </c>
-      <c r="F932" s="4">
-        <v>2</v>
-      </c>
+      <c r="F932" s="4"/>
       <c r="G932" s="4" t="s">
         <v>843</v>
       </c>
@@ -31230,9 +31197,6 @@
       </c>
       <c r="I932" s="5" t="s">
         <v>1636</v>
-      </c>
-      <c r="J932" s="5">
-        <v>3</v>
       </c>
       <c r="K932" s="4"/>
       <c r="M932" s="2"/>
@@ -31249,9 +31213,7 @@
       <c r="E933" s="4">
         <v>2014</v>
       </c>
-      <c r="F933" s="4">
-        <v>2</v>
-      </c>
+      <c r="F933" s="4"/>
       <c r="G933" s="4" t="s">
         <v>843</v>
       </c>
@@ -31260,9 +31222,6 @@
       </c>
       <c r="I933" s="5" t="s">
         <v>1637</v>
-      </c>
-      <c r="J933" s="5">
-        <v>3</v>
       </c>
       <c r="K933" s="4"/>
       <c r="M933" s="2"/>
@@ -31279,9 +31238,7 @@
       <c r="E934" s="4">
         <v>2014</v>
       </c>
-      <c r="F934" s="4">
-        <v>2</v>
-      </c>
+      <c r="F934" s="4"/>
       <c r="G934" s="4" t="s">
         <v>843</v>
       </c>
@@ -31290,9 +31247,6 @@
       </c>
       <c r="I934" s="5" t="s">
         <v>1638</v>
-      </c>
-      <c r="J934" s="5">
-        <v>3</v>
       </c>
       <c r="K934" s="4"/>
       <c r="M934" s="2"/>
@@ -31318,9 +31272,6 @@
       </c>
       <c r="I935" s="5" t="s">
         <v>1639</v>
-      </c>
-      <c r="J935" s="5" t="s">
-        <v>1018</v>
       </c>
       <c r="K935" s="4"/>
       <c r="M935" s="2"/>
@@ -57815,7 +57766,7 @@
       <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="43" t="s">
@@ -57830,10 +57781,10 @@
       <c r="H3" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="44" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="41" t="s">
@@ -57854,13 +57805,13 @@
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
+      <c r="D4" s="45"/>
       <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="41"/>
       <c r="L4" s="41"/>
       <c r="M4" s="41"/>
@@ -60971,7 +60922,7 @@
       <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="44" t="s">
+      <c r="D104" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E104" s="43" t="s">
@@ -60982,10 +60933,10 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="45" t="s">
+      <c r="I104" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J104" s="45" t="s">
+      <c r="J104" s="44" t="s">
         <v>8</v>
       </c>
       <c r="K104" s="41" t="s">
@@ -61007,13 +60958,13 @@
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="43"/>
-      <c r="D105" s="44"/>
+      <c r="D105" s="45"/>
       <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="45"/>
-      <c r="J105" s="45"/>
+      <c r="I105" s="44"/>
+      <c r="J105" s="44"/>
       <c r="K105" s="41"/>
       <c r="L105" s="41"/>
       <c r="M105" s="41"/>
@@ -65870,8 +65821,8 @@
       </c>
     </row>
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I261" s="45"/>
-      <c r="J261" s="45"/>
+      <c r="I261" s="44"/>
+      <c r="J261" s="44"/>
       <c r="K261" s="41"/>
       <c r="L261" s="41"/>
       <c r="M261" s="41"/>
@@ -65879,8 +65830,8 @@
       <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I262" s="45"/>
-      <c r="J262" s="45"/>
+      <c r="I262" s="44"/>
+      <c r="J262" s="44"/>
       <c r="K262" s="41"/>
       <c r="L262" s="41"/>
       <c r="M262" s="41"/>
@@ -65889,25 +65840,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -65920,6 +65852,25 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED72504-DDD7-4019-8560-D9E928534C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32623FF-1D7F-43BD-802D-9BC6A4FF6C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11802" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11812" uniqueCount="1676">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -5293,11 +5293,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -31061,7 +31061,9 @@
       <c r="I926" s="18" t="s">
         <v>1631</v>
       </c>
-      <c r="K926" s="10"/>
+      <c r="K926" s="10" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="927" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C927" s="18">
@@ -31083,7 +31085,9 @@
       <c r="I927" s="18" t="s">
         <v>1136</v>
       </c>
-      <c r="K927" s="10"/>
+      <c r="K927" s="10" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="928" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C928" s="18">
@@ -31105,7 +31109,9 @@
       <c r="I928" s="18" t="s">
         <v>1632</v>
       </c>
-      <c r="K928" s="10"/>
+      <c r="K928" s="10" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="929" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C929" s="5">
@@ -31127,7 +31133,9 @@
       <c r="I929" s="5" t="s">
         <v>1633</v>
       </c>
-      <c r="K929" s="4"/>
+      <c r="K929" s="4" t="s">
+        <v>790</v>
+      </c>
     </row>
     <row r="930" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C930" s="5">
@@ -31149,7 +31157,9 @@
       <c r="I930" s="5" t="s">
         <v>1634</v>
       </c>
-      <c r="K930" s="4"/>
+      <c r="K930" s="4" t="s">
+        <v>790</v>
+      </c>
       <c r="M930" s="2"/>
       <c r="N930" s="2"/>
       <c r="O930" s="2"/>
@@ -31173,7 +31183,9 @@
       <c r="I931" s="5" t="s">
         <v>1635</v>
       </c>
-      <c r="K931" s="4"/>
+      <c r="K931" s="4" t="s">
+        <v>193</v>
+      </c>
       <c r="M931" s="2"/>
       <c r="N931" s="2"/>
       <c r="O931" s="2"/>
@@ -31198,7 +31210,9 @@
       <c r="I932" s="5" t="s">
         <v>1636</v>
       </c>
-      <c r="K932" s="4"/>
+      <c r="K932" s="4" t="s">
+        <v>790</v>
+      </c>
       <c r="M932" s="2"/>
       <c r="N932" s="2"/>
       <c r="O932" s="2"/>
@@ -31223,7 +31237,9 @@
       <c r="I933" s="5" t="s">
         <v>1637</v>
       </c>
-      <c r="K933" s="4"/>
+      <c r="K933" s="4" t="s">
+        <v>790</v>
+      </c>
       <c r="M933" s="2"/>
       <c r="N933" s="2"/>
       <c r="O933" s="2"/>
@@ -31248,7 +31264,9 @@
       <c r="I934" s="5" t="s">
         <v>1638</v>
       </c>
-      <c r="K934" s="4"/>
+      <c r="K934" s="4" t="s">
+        <v>790</v>
+      </c>
       <c r="M934" s="2"/>
       <c r="N934" s="2"/>
       <c r="O934" s="2"/>
@@ -31273,7 +31291,9 @@
       <c r="I935" s="5" t="s">
         <v>1639</v>
       </c>
-      <c r="K935" s="4"/>
+      <c r="K935" s="4" t="s">
+        <v>411</v>
+      </c>
       <c r="M935" s="2"/>
       <c r="N935" s="2"/>
       <c r="O935" s="2"/>
@@ -57766,7 +57786,7 @@
       <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="44" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="43" t="s">
@@ -57781,10 +57801,10 @@
       <c r="H3" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="41" t="s">
@@ -57805,13 +57825,13 @@
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="43"/>
-      <c r="D4" s="45"/>
+      <c r="D4" s="44"/>
       <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
       <c r="K4" s="41"/>
       <c r="L4" s="41"/>
       <c r="M4" s="41"/>
@@ -60922,7 +60942,7 @@
       <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="45" t="s">
+      <c r="D104" s="44" t="s">
         <v>0</v>
       </c>
       <c r="E104" s="43" t="s">
@@ -60933,10 +60953,10 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="44" t="s">
+      <c r="I104" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="J104" s="44" t="s">
+      <c r="J104" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K104" s="41" t="s">
@@ -60958,13 +60978,13 @@
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="43"/>
-      <c r="D105" s="45"/>
+      <c r="D105" s="44"/>
       <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="44"/>
-      <c r="J105" s="44"/>
+      <c r="I105" s="45"/>
+      <c r="J105" s="45"/>
       <c r="K105" s="41"/>
       <c r="L105" s="41"/>
       <c r="M105" s="41"/>
@@ -65821,8 +65841,8 @@
       </c>
     </row>
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I261" s="44"/>
-      <c r="J261" s="44"/>
+      <c r="I261" s="45"/>
+      <c r="J261" s="45"/>
       <c r="K261" s="41"/>
       <c r="L261" s="41"/>
       <c r="M261" s="41"/>
@@ -65830,8 +65850,8 @@
       <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I262" s="44"/>
-      <c r="J262" s="44"/>
+      <c r="I262" s="45"/>
+      <c r="J262" s="45"/>
       <c r="K262" s="41"/>
       <c r="L262" s="41"/>
       <c r="M262" s="41"/>
@@ -65840,6 +65860,25 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -65852,25 +65891,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32623FF-1D7F-43BD-802D-9BC6A4FF6C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB8A3D-BB44-4BEF-A987-07E33CA6FBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11812" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11813" uniqueCount="1676">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -5293,11 +5293,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -31025,6 +31025,9 @@
       <c r="J923" s="10" t="s">
         <v>3</v>
       </c>
+      <c r="K923" s="10" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="924" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D924" s="24" t="s">
@@ -57786,7 +57789,7 @@
       <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="43" t="s">
@@ -57801,10 +57804,10 @@
       <c r="H3" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="I3" s="45" t="s">
+      <c r="I3" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="45" t="s">
+      <c r="J3" s="44" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="41" t="s">
@@ -57825,13 +57828,13 @@
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="43"/>
-      <c r="D4" s="44"/>
+      <c r="D4" s="45"/>
       <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
       <c r="K4" s="41"/>
       <c r="L4" s="41"/>
       <c r="M4" s="41"/>
@@ -60942,7 +60945,7 @@
       <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="44" t="s">
+      <c r="D104" s="45" t="s">
         <v>0</v>
       </c>
       <c r="E104" s="43" t="s">
@@ -60953,10 +60956,10 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="45" t="s">
+      <c r="I104" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="J104" s="45" t="s">
+      <c r="J104" s="44" t="s">
         <v>8</v>
       </c>
       <c r="K104" s="41" t="s">
@@ -60978,13 +60981,13 @@
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="43"/>
-      <c r="D105" s="44"/>
+      <c r="D105" s="45"/>
       <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="45"/>
-      <c r="J105" s="45"/>
+      <c r="I105" s="44"/>
+      <c r="J105" s="44"/>
       <c r="K105" s="41"/>
       <c r="L105" s="41"/>
       <c r="M105" s="41"/>
@@ -65841,8 +65844,8 @@
       </c>
     </row>
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I261" s="45"/>
-      <c r="J261" s="45"/>
+      <c r="I261" s="44"/>
+      <c r="J261" s="44"/>
       <c r="K261" s="41"/>
       <c r="L261" s="41"/>
       <c r="M261" s="41"/>
@@ -65850,8 +65853,8 @@
       <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I262" s="45"/>
-      <c r="J262" s="45"/>
+      <c r="I262" s="44"/>
+      <c r="J262" s="44"/>
       <c r="K262" s="41"/>
       <c r="L262" s="41"/>
       <c r="M262" s="41"/>
@@ -65860,25 +65863,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -65891,6 +65875,25 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/zolotaia_osen_2026.xlsx
+++ b/data/zolotaia_osen_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13BB8A3D-BB44-4BEF-A987-07E33CA6FBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA208B95-B389-4C2D-AE0B-1E448577CC5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11813" uniqueCount="1676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11814" uniqueCount="1676">
   <si>
     <t>Фамилия, Имя</t>
   </si>
@@ -5293,11 +5293,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="2"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="3" t="s">
         <v>857</v>
       </c>
@@ -5724,7 +5724,7 @@
       <c r="D6" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -5739,7 +5739,7 @@
     <row r="7" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="7"/>
       <c r="D7" s="24"/>
-      <c r="E7" s="7"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -5756,7 +5756,7 @@
       <c r="D8" s="24" t="s">
         <v>1404</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -8236,7 +8236,7 @@
       <c r="D93" s="24" t="s">
         <v>890</v>
       </c>
-      <c r="E93" s="7"/>
+      <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -8248,7 +8248,7 @@
       <c r="D94" s="24" t="s">
         <v>895</v>
       </c>
-      <c r="E94" s="7"/>
+      <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="G94" s="4"/>
       <c r="H94" s="4"/>
@@ -12392,7 +12392,7 @@
       <c r="D234" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="E234" s="7"/>
+      <c r="E234" s="4"/>
       <c r="F234" s="4"/>
       <c r="G234" s="4"/>
       <c r="H234" s="4"/>
@@ -12404,7 +12404,7 @@
       <c r="D235" s="24" t="s">
         <v>895</v>
       </c>
-      <c r="E235" s="7"/>
+      <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="G235" s="4"/>
       <c r="H235" s="4"/>
@@ -13966,7 +13966,7 @@
       <c r="D290" s="24" t="s">
         <v>890</v>
       </c>
-      <c r="E290" s="7"/>
+      <c r="E290" s="4"/>
       <c r="F290" s="4"/>
       <c r="G290" s="4"/>
       <c r="H290" s="4"/>
@@ -13978,7 +13978,7 @@
       <c r="D291" s="24" t="s">
         <v>895</v>
       </c>
-      <c r="E291" s="7"/>
+      <c r="E291" s="4"/>
       <c r="F291" s="4"/>
       <c r="G291" s="4"/>
       <c r="H291" s="4"/>
@@ -16894,7 +16894,7 @@
       <c r="D396" s="24" t="s">
         <v>1006</v>
       </c>
-      <c r="E396" s="7"/>
+      <c r="E396" s="4"/>
       <c r="F396" s="4"/>
       <c r="G396" s="4"/>
       <c r="H396" s="4"/>
@@ -18826,7 +18826,7 @@
     </row>
     <row r="465" spans="3:15" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D465" s="24"/>
-      <c r="E465" s="7"/>
+      <c r="E465" s="4"/>
       <c r="F465" s="4"/>
       <c r="G465" s="4"/>
       <c r="H465" s="4"/>
@@ -18841,7 +18841,7 @@
       <c r="D466" s="24" t="s">
         <v>1006</v>
       </c>
-      <c r="E466" s="7"/>
+      <c r="E466" s="4"/>
       <c r="F466" s="4"/>
       <c r="G466" s="4"/>
       <c r="H466" s="4"/>
@@ -21605,7 +21605,7 @@
       </c>
       <c r="E568" s="3"/>
       <c r="F568" s="3"/>
-      <c r="G568" s="2"/>
+      <c r="G568" s="1"/>
       <c r="H568" s="3" t="s">
         <v>857</v>
       </c>
@@ -21661,7 +21661,7 @@
       <c r="D571" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="E571" s="7"/>
+      <c r="E571" s="4"/>
       <c r="F571" s="4"/>
       <c r="G571" s="4"/>
       <c r="H571" s="4"/>
@@ -21675,7 +21675,7 @@
       <c r="D572" s="24" t="s">
         <v>1410</v>
       </c>
-      <c r="E572" s="7"/>
+      <c r="E572" s="4"/>
       <c r="F572" s="4"/>
       <c r="G572" s="4"/>
       <c r="H572" s="4"/>
@@ -23245,7 +23245,7 @@
       <c r="D629" s="24" t="s">
         <v>890</v>
       </c>
-      <c r="E629" s="7"/>
+      <c r="E629" s="4"/>
       <c r="F629" s="4"/>
       <c r="G629" s="4"/>
       <c r="H629" s="4"/>
@@ -23259,7 +23259,7 @@
       <c r="D630" s="24" t="s">
         <v>1404</v>
       </c>
-      <c r="E630" s="7"/>
+      <c r="E630" s="4"/>
       <c r="F630" s="4"/>
       <c r="G630" s="4"/>
       <c r="H630" s="4"/>
@@ -25503,7 +25503,7 @@
       <c r="D714" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="E714" s="7"/>
+      <c r="E714" s="4"/>
       <c r="F714" s="4"/>
       <c r="G714" s="4"/>
       <c r="H714" s="4"/>
@@ -25516,7 +25516,7 @@
       <c r="D715" s="24" t="s">
         <v>895</v>
       </c>
-      <c r="E715" s="7"/>
+      <c r="E715" s="4"/>
       <c r="F715" s="4"/>
       <c r="G715" s="4"/>
       <c r="H715" s="4"/>
@@ -27673,7 +27673,7 @@
       <c r="D797" s="24" t="s">
         <v>890</v>
       </c>
-      <c r="E797" s="7"/>
+      <c r="E797" s="4"/>
       <c r="F797" s="4"/>
       <c r="G797" s="4"/>
       <c r="H797" s="4"/>
@@ -27686,7 +27686,7 @@
       <c r="D798" s="24" t="s">
         <v>895</v>
       </c>
-      <c r="E798" s="7"/>
+      <c r="E798" s="4"/>
       <c r="F798" s="4"/>
       <c r="G798" s="4"/>
       <c r="H798" s="4"/>
@@ -31033,7 +31033,7 @@
       <c r="D924" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="E924" s="7"/>
+      <c r="E924" s="4"/>
       <c r="F924" s="4"/>
       <c r="G924" s="4"/>
       <c r="H924" s="4"/>
@@ -31054,7 +31054,9 @@
       <c r="E926" s="10">
         <v>2014</v>
       </c>
-      <c r="F926" s="10"/>
+      <c r="F926" s="10">
+        <v>1</v>
+      </c>
       <c r="G926" s="10" t="s">
         <v>845</v>
       </c>
@@ -31063,6 +31065,9 @@
       </c>
       <c r="I926" s="18" t="s">
         <v>1631</v>
+      </c>
+      <c r="J926" s="5">
+        <v>1</v>
       </c>
       <c r="K926" s="10" t="s">
         <v>193</v>
@@ -31078,7 +31083,9 @@
       <c r="E927" s="10">
         <v>2014</v>
       </c>
-      <c r="F927" s="10"/>
+      <c r="F927" s="10">
+        <v>1</v>
+      </c>
       <c r="G927" s="10" t="s">
         <v>845</v>
       </c>
@@ -31087,6 +31094,9 @@
       </c>
       <c r="I927" s="18" t="s">
         <v>1136</v>
+      </c>
+      <c r="J927" s="5">
+        <v>2</v>
       </c>
       <c r="K927" s="10" t="s">
         <v>193</v>
@@ -31102,7 +31112,9 @@
       <c r="E928" s="10">
         <v>2014</v>
       </c>
-      <c r="F928" s="10"/>
+      <c r="F928" s="10">
+        <v>2</v>
+      </c>
       <c r="G928" s="10" t="s">
         <v>845</v>
       </c>
@@ -31111,6 +31123,9 @@
       </c>
       <c r="I928" s="18" t="s">
         <v>1632</v>
+      </c>
+      <c r="J928" s="5">
+        <v>2</v>
       </c>
       <c r="K928" s="10" t="s">
         <v>193</v>
@@ -31126,7 +31141,9 @@
       <c r="E929" s="4">
         <v>2014</v>
       </c>
-      <c r="F929" s="4"/>
+      <c r="F929" s="4">
+        <v>1</v>
+      </c>
       <c r="G929" s="4" t="s">
         <v>843</v>
       </c>
@@ -31135,6 +31152,9 @@
       </c>
       <c r="I929" s="5" t="s">
         <v>1633</v>
+      </c>
+      <c r="J929" s="5">
+        <v>2</v>
       </c>
       <c r="K929" s="4" t="s">
         <v>790</v>
@@ -31150,7 +31170,9 @@
       <c r="E930" s="4">
         <v>2014</v>
       </c>
-      <c r="F930" s="4"/>
+      <c r="F930" s="4">
+        <v>2</v>
+      </c>
       <c r="G930" s="4" t="s">
         <v>843</v>
       </c>
@@ -31159,6 +31181,9 @@
       </c>
       <c r="I930" s="5" t="s">
         <v>1634</v>
+      </c>
+      <c r="J930" s="5">
+        <v>2</v>
       </c>
       <c r="K930" s="4" t="s">
         <v>790</v>
@@ -31177,6 +31202,9 @@
       <c r="E931" s="5">
         <v>2014</v>
       </c>
+      <c r="F931" s="5">
+        <v>2</v>
+      </c>
       <c r="G931" s="4" t="s">
         <v>845</v>
       </c>
@@ -31185,6 +31213,9 @@
       </c>
       <c r="I931" s="5" t="s">
         <v>1635</v>
+      </c>
+      <c r="J931" s="5">
+        <v>3</v>
       </c>
       <c r="K931" s="4" t="s">
         <v>193</v>
@@ -31203,7 +31234,9 @@
       <c r="E932" s="4">
         <v>2014</v>
       </c>
-      <c r="F932" s="4"/>
+      <c r="F932" s="4">
+        <v>2</v>
+      </c>
       <c r="G932" s="4" t="s">
         <v>843</v>
       </c>
@@ -31212,6 +31245,9 @@
       </c>
       <c r="I932" s="5" t="s">
         <v>1636</v>
+      </c>
+      <c r="J932" s="5">
+        <v>3</v>
       </c>
       <c r="K932" s="4" t="s">
         <v>790</v>
@@ -31230,7 +31266,9 @@
       <c r="E933" s="4">
         <v>2014</v>
       </c>
-      <c r="F933" s="4"/>
+      <c r="F933" s="4">
+        <v>2</v>
+      </c>
       <c r="G933" s="4" t="s">
         <v>843</v>
       </c>
@@ -31239,6 +31277,9 @@
       </c>
       <c r="I933" s="5" t="s">
         <v>1637</v>
+      </c>
+      <c r="J933" s="5">
+        <v>3</v>
       </c>
       <c r="K933" s="4" t="s">
         <v>790</v>
@@ -31257,7 +31298,9 @@
       <c r="E934" s="4">
         <v>2014</v>
       </c>
-      <c r="F934" s="4"/>
+      <c r="F934" s="4">
+        <v>2</v>
+      </c>
       <c r="G934" s="4" t="s">
         <v>843</v>
       </c>
@@ -31266,6 +31309,9 @@
       </c>
       <c r="I934" s="5" t="s">
         <v>1638</v>
+      </c>
+      <c r="J934" s="5">
+        <v>3</v>
       </c>
       <c r="K934" s="4" t="s">
         <v>790</v>
@@ -31293,6 +31339,9 @@
       </c>
       <c r="I935" s="5" t="s">
         <v>1639</v>
+      </c>
+      <c r="J935" s="5" t="s">
+        <v>1018</v>
       </c>
       <c r="K935" s="4" t="s">
         <v>411</v>
@@ -31357,7 +31406,7 @@
       <c r="D941" s="24" t="s">
         <v>890</v>
       </c>
-      <c r="E941" s="7"/>
+      <c r="E941" s="4"/>
       <c r="F941" s="4"/>
       <c r="G941" s="4"/>
       <c r="H941" s="4"/>
@@ -32042,9 +32091,9 @@
       <c r="D973" s="2" t="s">
         <v>1157</v>
       </c>
-      <c r="E973" s="2"/>
-      <c r="F973" s="2"/>
-      <c r="G973" s="2"/>
+      <c r="E973" s="1"/>
+      <c r="F973" s="1"/>
+      <c r="G973" s="1"/>
       <c r="H973" s="2"/>
       <c r="I973" s="1"/>
       <c r="J973" s="1"/>
@@ -32130,9 +32179,9 @@
     </row>
     <row r="978" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D978" s="2"/>
-      <c r="E978" s="2"/>
-      <c r="F978" s="2"/>
-      <c r="G978" s="2"/>
+      <c r="E978" s="1"/>
+      <c r="F978" s="1"/>
+      <c r="G978" s="1"/>
       <c r="H978" s="2"/>
       <c r="I978" s="1"/>
       <c r="J978" s="1"/>
@@ -32140,9 +32189,9 @@
     </row>
     <row r="979" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D979" s="2"/>
-      <c r="E979" s="2"/>
-      <c r="F979" s="2"/>
-      <c r="G979" s="2"/>
+      <c r="E979" s="1"/>
+      <c r="F979" s="1"/>
+      <c r="G979" s="1"/>
       <c r="H979" s="2"/>
       <c r="I979" s="1"/>
       <c r="J979" s="1"/>
@@ -32150,9 +32199,9 @@
     </row>
     <row r="980" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D980" s="2"/>
-      <c r="E980" s="2"/>
-      <c r="F980" s="2"/>
-      <c r="G980" s="2"/>
+      <c r="E980" s="1"/>
+      <c r="F980" s="1"/>
+      <c r="G980" s="1"/>
       <c r="H980" s="2"/>
       <c r="I980" s="1"/>
       <c r="J980" s="1"/>
@@ -32160,9 +32209,9 @@
     </row>
     <row r="981" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D981" s="2"/>
-      <c r="E981" s="2"/>
-      <c r="F981" s="2"/>
-      <c r="G981" s="2"/>
+      <c r="E981" s="1"/>
+      <c r="F981" s="1"/>
+      <c r="G981" s="1"/>
       <c r="H981" s="2"/>
       <c r="I981" s="1"/>
       <c r="J981" s="1"/>
@@ -32172,9 +32221,9 @@
       <c r="D982" s="30" t="s">
         <v>1669</v>
       </c>
-      <c r="E982" s="30"/>
-      <c r="F982" s="30"/>
-      <c r="G982" s="30"/>
+      <c r="E982" s="3"/>
+      <c r="F982" s="3"/>
+      <c r="G982" s="3"/>
       <c r="H982" s="30" t="s">
         <v>1670</v>
       </c>
@@ -32186,9 +32235,9 @@
       <c r="D983" s="30" t="s">
         <v>1671</v>
       </c>
-      <c r="E983" s="30"/>
-      <c r="F983" s="30"/>
-      <c r="G983" s="30"/>
+      <c r="E983" s="3"/>
+      <c r="F983" s="3"/>
+      <c r="G983" s="3"/>
       <c r="H983" s="30" t="s">
         <v>1672</v>
       </c>
@@ -32198,9 +32247,9 @@
     </row>
     <row r="984" spans="3:11" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D984" s="2"/>
-      <c r="E984" s="2"/>
-      <c r="F984" s="2"/>
-      <c r="G984" s="2"/>
+      <c r="E984" s="1"/>
+      <c r="F984" s="1"/>
+      <c r="G984" s="1"/>
       <c r="H984" s="2"/>
       <c r="I984" s="1"/>
       <c r="J984" s="1"/>
@@ -57789,7 +57838,7 @@
       <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="45" t="s">
+      <c r="D3" s="44" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="43" t="s">
@@ -57804,10 +57853,10 @@
       <c r="H3" s="4" t="s">
         <v>842</v>
       </c>
-      <c r="I3" s="44" t="s">
+      <c r="I3" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K3" s="41" t="s">
@@ -57828,13 +57877,13 @@
     </row>
     <row r="4" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="43"/>
-      <c r="D4" s="45"/>
+      <c r="D4" s="44"/>
       <c r="E4" s="43"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
       <c r="K4" s="41"/>
       <c r="L4" s="41"/>
       <c r="M4" s="41"/>
@@ -60945,7 +60994,7 @@
       <c r="C104" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="45" t="s">
+      <c r="D104" s="44" t="s">
         <v>0</v>
       </c>
       <c r="E104" s="43" t="s">
@@ -60956,10 +61005,10 @@
       </c>
       <c r="G104" s="4"/>
       <c r="H104" s="4"/>
-      <c r="I104" s="44" t="s">
+      <c r="I104" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="J104" s="44" t="s">
+      <c r="J104" s="45" t="s">
         <v>8</v>
       </c>
       <c r="K104" s="41" t="s">
@@ -60981,13 +61030,13 @@
     </row>
     <row r="105" spans="3:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="43"/>
-      <c r="D105" s="45"/>
+      <c r="D105" s="44"/>
       <c r="E105" s="43"/>
       <c r="F105" s="4"/>
       <c r="G105" s="4"/>
       <c r="H105" s="4"/>
-      <c r="I105" s="44"/>
-      <c r="J105" s="44"/>
+      <c r="I105" s="45"/>
+      <c r="J105" s="45"/>
       <c r="K105" s="41"/>
       <c r="L105" s="41"/>
       <c r="M105" s="41"/>
@@ -65844,8 +65893,8 @@
       </c>
     </row>
     <row r="261" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I261" s="44"/>
-      <c r="J261" s="44"/>
+      <c r="I261" s="45"/>
+      <c r="J261" s="45"/>
       <c r="K261" s="41"/>
       <c r="L261" s="41"/>
       <c r="M261" s="41"/>
@@ -65853,8 +65902,8 @@
       <c r="O261" s="43"/>
     </row>
     <row r="262" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I262" s="44"/>
-      <c r="J262" s="44"/>
+      <c r="I262" s="45"/>
+      <c r="J262" s="45"/>
       <c r="K262" s="41"/>
       <c r="L262" s="41"/>
       <c r="M262" s="41"/>
@@ -65863,6 +65912,25 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="O261:O262"/>
+    <mergeCell ref="M104:M105"/>
+    <mergeCell ref="N104:N105"/>
+    <mergeCell ref="O104:O105"/>
+    <mergeCell ref="P104:P105"/>
+    <mergeCell ref="N261:N262"/>
+    <mergeCell ref="I261:I262"/>
+    <mergeCell ref="J261:J262"/>
+    <mergeCell ref="K261:K262"/>
+    <mergeCell ref="L261:L262"/>
+    <mergeCell ref="M261:M262"/>
+    <mergeCell ref="L103:N103"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="I104:I105"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="L104:L105"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="L2:N2"/>
@@ -65875,25 +65943,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="L103:N103"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="D104:D105"/>
-    <mergeCell ref="E104:E105"/>
-    <mergeCell ref="I104:I105"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="L104:L105"/>
-    <mergeCell ref="I261:I262"/>
-    <mergeCell ref="J261:J262"/>
-    <mergeCell ref="K261:K262"/>
-    <mergeCell ref="L261:L262"/>
-    <mergeCell ref="M261:M262"/>
-    <mergeCell ref="O261:O262"/>
-    <mergeCell ref="M104:M105"/>
-    <mergeCell ref="N104:N105"/>
-    <mergeCell ref="O104:O105"/>
-    <mergeCell ref="P104:P105"/>
-    <mergeCell ref="N261:N262"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="3.937007874015748E-2" top="0.74803149606299213" bottom="0.55118110236220474" header="0.31496062992125984" footer="0.11811023622047245"/>
   <pageSetup paperSize="9" scale="95" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
